--- a/PM_092.xlsx
+++ b/PM_092.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\1. TCKT_PCVT\2.SCL\2026\Báo cáo\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="Z:\TUAN HOC A.I\1. TCKT_PCVT\4. Công nghệ AI\KT SCL\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{298DDB8B-3D55-4527-A226-2A59937B3999}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{937510B4-8285-42FF-8E17-8B3A854FDBE4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{AC1AAD16-9061-42F9-B216-D7E5AB78D483}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1059" uniqueCount="144">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1061" uniqueCount="144">
   <si>
     <t>TỔNG CÔNG TY ĐIỆN LỰC THÀNH PHỐ HỒ CHÍ MINH TNHH</t>
   </si>
@@ -1769,10 +1769,6 @@
     <xf numFmtId="0" fontId="25" fillId="33" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="21" fillId="33" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
@@ -1782,8 +1778,11 @@
     <xf numFmtId="0" fontId="21" fillId="33" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="33" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf numFmtId="0" fontId="21" fillId="34" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="34" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="33" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -1793,12 +1792,6 @@
     </xf>
     <xf numFmtId="0" fontId="21" fillId="33" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="34" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="34" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="34" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
@@ -1812,6 +1805,13 @@
     <xf numFmtId="0" fontId="21" fillId="34" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="33" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -2187,7 +2187,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DC097D15-D4E4-46F1-B3C8-4A7361019462}">
-  <dimension ref="A1:H265"/>
+  <dimension ref="A1:H267"/>
   <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="35.19921875" bestFit="1" customWidth="1"/>
@@ -2249,98 +2249,98 @@
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A12" s="21" t="s">
+      <c r="A12" s="34" t="s">
         <v>9</v>
       </c>
-      <c r="B12" s="22"/>
-      <c r="C12" s="22"/>
-      <c r="D12" s="22"/>
-      <c r="E12" s="22"/>
-      <c r="F12" s="22"/>
-      <c r="G12" s="22"/>
-      <c r="H12" s="22"/>
+      <c r="B12" s="35"/>
+      <c r="C12" s="35"/>
+      <c r="D12" s="35"/>
+      <c r="E12" s="35"/>
+      <c r="F12" s="35"/>
+      <c r="G12" s="35"/>
+      <c r="H12" s="35"/>
     </row>
     <row r="13" spans="1:8" ht="30.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="32" t="s">
+      <c r="A13" s="29" t="s">
         <v>10</v>
       </c>
-      <c r="B13" s="32" t="s">
+      <c r="B13" s="29" t="s">
         <v>11</v>
       </c>
-      <c r="C13" s="32" t="s">
+      <c r="C13" s="29" t="s">
         <v>12</v>
       </c>
-      <c r="D13" s="32" t="s">
+      <c r="D13" s="29" t="s">
         <v>13</v>
       </c>
-      <c r="E13" s="34" t="s">
+      <c r="E13" s="31" t="s">
         <v>14</v>
       </c>
-      <c r="F13" s="35"/>
-      <c r="G13" s="30" t="s">
+      <c r="F13" s="32"/>
+      <c r="G13" s="24" t="s">
         <v>15</v>
       </c>
-      <c r="H13" s="30" t="s">
+      <c r="H13" s="24" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="14" spans="1:8" ht="28.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="33"/>
-      <c r="B14" s="33"/>
-      <c r="C14" s="33"/>
-      <c r="D14" s="33"/>
+      <c r="A14" s="30"/>
+      <c r="B14" s="30"/>
+      <c r="C14" s="30"/>
+      <c r="D14" s="30"/>
       <c r="E14" s="5" t="s">
         <v>17</v>
       </c>
       <c r="F14" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="G14" s="31"/>
-      <c r="H14" s="31"/>
+      <c r="G14" s="25"/>
+      <c r="H14" s="25"/>
     </row>
     <row r="15" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="27" t="s">
+      <c r="A15" s="26" t="s">
         <v>19</v>
       </c>
-      <c r="B15" s="28"/>
-      <c r="C15" s="28"/>
-      <c r="D15" s="28"/>
-      <c r="E15" s="28"/>
-      <c r="F15" s="28"/>
-      <c r="G15" s="28"/>
-      <c r="H15" s="29"/>
+      <c r="B15" s="27"/>
+      <c r="C15" s="27"/>
+      <c r="D15" s="27"/>
+      <c r="E15" s="27"/>
+      <c r="F15" s="27"/>
+      <c r="G15" s="27"/>
+      <c r="H15" s="28"/>
     </row>
     <row r="16" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="27" t="s">
+      <c r="A16" s="26" t="s">
         <v>20</v>
       </c>
-      <c r="B16" s="28"/>
-      <c r="C16" s="28"/>
-      <c r="D16" s="28"/>
-      <c r="E16" s="28"/>
-      <c r="F16" s="28"/>
-      <c r="G16" s="28"/>
-      <c r="H16" s="29"/>
+      <c r="B16" s="27"/>
+      <c r="C16" s="27"/>
+      <c r="D16" s="27"/>
+      <c r="E16" s="27"/>
+      <c r="F16" s="27"/>
+      <c r="G16" s="27"/>
+      <c r="H16" s="28"/>
     </row>
     <row r="17" spans="1:8" ht="18.149999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="27" t="s">
+      <c r="A17" s="26" t="s">
         <v>21</v>
       </c>
-      <c r="B17" s="28"/>
-      <c r="C17" s="28"/>
-      <c r="D17" s="28"/>
-      <c r="E17" s="28"/>
-      <c r="F17" s="28"/>
-      <c r="G17" s="28"/>
-      <c r="H17" s="29"/>
+      <c r="B17" s="27"/>
+      <c r="C17" s="27"/>
+      <c r="D17" s="27"/>
+      <c r="E17" s="27"/>
+      <c r="F17" s="27"/>
+      <c r="G17" s="27"/>
+      <c r="H17" s="28"/>
     </row>
     <row r="18" spans="1:8" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="23" t="s">
+      <c r="A18" s="21" t="s">
         <v>22</v>
       </c>
-      <c r="B18" s="24"/>
-      <c r="C18" s="24"/>
-      <c r="D18" s="25"/>
+      <c r="B18" s="22"/>
+      <c r="C18" s="22"/>
+      <c r="D18" s="23"/>
       <c r="E18" s="7"/>
       <c r="F18" s="7"/>
       <c r="G18" s="7"/>
@@ -2899,12 +2899,12 @@
       </c>
     </row>
     <row r="42" spans="1:8" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="23" t="s">
+      <c r="A42" s="21" t="s">
         <v>30</v>
       </c>
-      <c r="B42" s="24"/>
-      <c r="C42" s="24"/>
-      <c r="D42" s="25"/>
+      <c r="B42" s="22"/>
+      <c r="C42" s="22"/>
+      <c r="D42" s="23"/>
       <c r="E42" s="13">
         <v>103128028</v>
       </c>
@@ -2913,12 +2913,12 @@
       <c r="H42" s="7"/>
     </row>
     <row r="43" spans="1:8" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A43" s="23" t="s">
+      <c r="A43" s="21" t="s">
         <v>31</v>
       </c>
-      <c r="B43" s="24"/>
-      <c r="C43" s="24"/>
-      <c r="D43" s="25"/>
+      <c r="B43" s="22"/>
+      <c r="C43" s="22"/>
+      <c r="D43" s="23"/>
       <c r="E43" s="13">
         <v>103128028</v>
       </c>
@@ -2927,24 +2927,24 @@
       <c r="H43" s="7"/>
     </row>
     <row r="44" spans="1:8" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A44" s="23" t="s">
+      <c r="A44" s="21" t="s">
         <v>32</v>
       </c>
-      <c r="B44" s="24"/>
-      <c r="C44" s="24"/>
-      <c r="D44" s="25"/>
+      <c r="B44" s="22"/>
+      <c r="C44" s="22"/>
+      <c r="D44" s="23"/>
       <c r="E44" s="7"/>
       <c r="F44" s="7"/>
       <c r="G44" s="7"/>
       <c r="H44" s="7"/>
     </row>
     <row r="45" spans="1:8" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A45" s="23" t="s">
+      <c r="A45" s="21" t="s">
         <v>33</v>
       </c>
-      <c r="B45" s="24"/>
-      <c r="C45" s="24"/>
-      <c r="D45" s="25"/>
+      <c r="B45" s="22"/>
+      <c r="C45" s="22"/>
+      <c r="D45" s="23"/>
       <c r="E45" s="13">
         <v>103128028</v>
       </c>
@@ -2953,12 +2953,12 @@
       <c r="H45" s="7"/>
     </row>
     <row r="46" spans="1:8" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A46" s="23" t="s">
+      <c r="A46" s="21" t="s">
         <v>34</v>
       </c>
-      <c r="B46" s="24"/>
-      <c r="C46" s="24"/>
-      <c r="D46" s="25"/>
+      <c r="B46" s="22"/>
+      <c r="C46" s="22"/>
+      <c r="D46" s="23"/>
       <c r="E46" s="13">
         <v>103128028</v>
       </c>
@@ -2967,24 +2967,24 @@
       <c r="H46" s="7"/>
     </row>
     <row r="47" spans="1:8" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A47" s="23" t="s">
+      <c r="A47" s="21" t="s">
         <v>35</v>
       </c>
-      <c r="B47" s="24"/>
-      <c r="C47" s="24"/>
-      <c r="D47" s="25"/>
+      <c r="B47" s="22"/>
+      <c r="C47" s="22"/>
+      <c r="D47" s="23"/>
       <c r="E47" s="7"/>
       <c r="F47" s="7"/>
       <c r="G47" s="7"/>
       <c r="H47" s="7"/>
     </row>
     <row r="48" spans="1:8" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A48" s="23" t="s">
+      <c r="A48" s="21" t="s">
         <v>36</v>
       </c>
-      <c r="B48" s="24"/>
-      <c r="C48" s="24"/>
-      <c r="D48" s="25"/>
+      <c r="B48" s="22"/>
+      <c r="C48" s="22"/>
+      <c r="D48" s="23"/>
       <c r="E48" s="13">
         <v>103128028</v>
       </c>
@@ -2993,12 +2993,12 @@
       <c r="H48" s="7"/>
     </row>
     <row r="49" spans="1:8" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A49" s="23" t="s">
+      <c r="A49" s="21" t="s">
         <v>37</v>
       </c>
-      <c r="B49" s="24"/>
-      <c r="C49" s="24"/>
-      <c r="D49" s="25"/>
+      <c r="B49" s="22"/>
+      <c r="C49" s="22"/>
+      <c r="D49" s="23"/>
       <c r="E49" s="13">
         <v>103128028</v>
       </c>
@@ -3007,48 +3007,48 @@
       <c r="H49" s="7"/>
     </row>
     <row r="50" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A50" s="27" t="s">
+      <c r="A50" s="26" t="s">
         <v>38</v>
       </c>
-      <c r="B50" s="28"/>
-      <c r="C50" s="28"/>
-      <c r="D50" s="28"/>
-      <c r="E50" s="28"/>
-      <c r="F50" s="28"/>
-      <c r="G50" s="28"/>
-      <c r="H50" s="29"/>
+      <c r="B50" s="27"/>
+      <c r="C50" s="27"/>
+      <c r="D50" s="27"/>
+      <c r="E50" s="27"/>
+      <c r="F50" s="27"/>
+      <c r="G50" s="27"/>
+      <c r="H50" s="28"/>
     </row>
     <row r="51" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A51" s="27" t="s">
+      <c r="A51" s="26" t="s">
         <v>39</v>
       </c>
-      <c r="B51" s="28"/>
-      <c r="C51" s="28"/>
-      <c r="D51" s="28"/>
-      <c r="E51" s="28"/>
-      <c r="F51" s="28"/>
-      <c r="G51" s="28"/>
-      <c r="H51" s="29"/>
+      <c r="B51" s="27"/>
+      <c r="C51" s="27"/>
+      <c r="D51" s="27"/>
+      <c r="E51" s="27"/>
+      <c r="F51" s="27"/>
+      <c r="G51" s="27"/>
+      <c r="H51" s="28"/>
     </row>
     <row r="52" spans="1:8" ht="18.149999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A52" s="27" t="s">
+      <c r="A52" s="26" t="s">
         <v>40</v>
       </c>
-      <c r="B52" s="28"/>
-      <c r="C52" s="28"/>
-      <c r="D52" s="28"/>
-      <c r="E52" s="28"/>
-      <c r="F52" s="28"/>
-      <c r="G52" s="28"/>
-      <c r="H52" s="29"/>
+      <c r="B52" s="27"/>
+      <c r="C52" s="27"/>
+      <c r="D52" s="27"/>
+      <c r="E52" s="27"/>
+      <c r="F52" s="27"/>
+      <c r="G52" s="27"/>
+      <c r="H52" s="28"/>
     </row>
     <row r="53" spans="1:8" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A53" s="23" t="s">
+      <c r="A53" s="21" t="s">
         <v>22</v>
       </c>
-      <c r="B53" s="24"/>
-      <c r="C53" s="24"/>
-      <c r="D53" s="25"/>
+      <c r="B53" s="22"/>
+      <c r="C53" s="22"/>
+      <c r="D53" s="23"/>
       <c r="E53" s="7"/>
       <c r="F53" s="7"/>
       <c r="G53" s="7"/>
@@ -6775,12 +6775,12 @@
       </c>
     </row>
     <row r="209" spans="1:8" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A209" s="23" t="s">
+      <c r="A209" s="21" t="s">
         <v>30</v>
       </c>
-      <c r="B209" s="24"/>
-      <c r="C209" s="24"/>
-      <c r="D209" s="25"/>
+      <c r="B209" s="22"/>
+      <c r="C209" s="22"/>
+      <c r="D209" s="23"/>
       <c r="E209" s="13">
         <v>1475408160</v>
       </c>
@@ -6791,12 +6791,12 @@
       <c r="H209" s="7"/>
     </row>
     <row r="210" spans="1:8" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A210" s="23" t="s">
+      <c r="A210" s="21" t="s">
         <v>31</v>
       </c>
-      <c r="B210" s="24"/>
-      <c r="C210" s="24"/>
-      <c r="D210" s="25"/>
+      <c r="B210" s="22"/>
+      <c r="C210" s="22"/>
+      <c r="D210" s="23"/>
       <c r="E210" s="13">
         <v>1445729378</v>
       </c>
@@ -6805,24 +6805,24 @@
       <c r="H210" s="7"/>
     </row>
     <row r="211" spans="1:8" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A211" s="23" t="s">
+      <c r="A211" s="21" t="s">
         <v>32</v>
       </c>
-      <c r="B211" s="24"/>
-      <c r="C211" s="24"/>
-      <c r="D211" s="25"/>
+      <c r="B211" s="22"/>
+      <c r="C211" s="22"/>
+      <c r="D211" s="23"/>
       <c r="E211" s="7"/>
       <c r="F211" s="7"/>
       <c r="G211" s="7"/>
       <c r="H211" s="7"/>
     </row>
     <row r="212" spans="1:8" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A212" s="23" t="s">
+      <c r="A212" s="21" t="s">
         <v>33</v>
       </c>
-      <c r="B212" s="24"/>
-      <c r="C212" s="24"/>
-      <c r="D212" s="25"/>
+      <c r="B212" s="22"/>
+      <c r="C212" s="22"/>
+      <c r="D212" s="23"/>
       <c r="E212" s="13">
         <v>1475408160</v>
       </c>
@@ -6833,12 +6833,12 @@
       <c r="H212" s="7"/>
     </row>
     <row r="213" spans="1:8" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A213" s="23" t="s">
+      <c r="A213" s="21" t="s">
         <v>34</v>
       </c>
-      <c r="B213" s="24"/>
-      <c r="C213" s="24"/>
-      <c r="D213" s="25"/>
+      <c r="B213" s="22"/>
+      <c r="C213" s="22"/>
+      <c r="D213" s="23"/>
       <c r="E213" s="13">
         <v>1445729378</v>
       </c>
@@ -6847,24 +6847,24 @@
       <c r="H213" s="7"/>
     </row>
     <row r="214" spans="1:8" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A214" s="23" t="s">
+      <c r="A214" s="21" t="s">
         <v>35</v>
       </c>
-      <c r="B214" s="24"/>
-      <c r="C214" s="24"/>
-      <c r="D214" s="25"/>
+      <c r="B214" s="22"/>
+      <c r="C214" s="22"/>
+      <c r="D214" s="23"/>
       <c r="E214" s="7"/>
       <c r="F214" s="7"/>
       <c r="G214" s="7"/>
       <c r="H214" s="7"/>
     </row>
     <row r="215" spans="1:8" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A215" s="23" t="s">
+      <c r="A215" s="21" t="s">
         <v>36</v>
       </c>
-      <c r="B215" s="24"/>
-      <c r="C215" s="24"/>
-      <c r="D215" s="25"/>
+      <c r="B215" s="22"/>
+      <c r="C215" s="22"/>
+      <c r="D215" s="23"/>
       <c r="E215" s="13">
         <v>1475408160</v>
       </c>
@@ -6875,12 +6875,12 @@
       <c r="H215" s="7"/>
     </row>
     <row r="216" spans="1:8" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A216" s="23" t="s">
+      <c r="A216" s="21" t="s">
         <v>37</v>
       </c>
-      <c r="B216" s="24"/>
-      <c r="C216" s="24"/>
-      <c r="D216" s="25"/>
+      <c r="B216" s="22"/>
+      <c r="C216" s="22"/>
+      <c r="D216" s="23"/>
       <c r="E216" s="13">
         <v>1445729378</v>
       </c>
@@ -6889,48 +6889,48 @@
       <c r="H216" s="7"/>
     </row>
     <row r="217" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A217" s="27" t="s">
+      <c r="A217" s="26" t="s">
         <v>130</v>
       </c>
-      <c r="B217" s="28"/>
-      <c r="C217" s="28"/>
-      <c r="D217" s="28"/>
-      <c r="E217" s="28"/>
-      <c r="F217" s="28"/>
-      <c r="G217" s="28"/>
-      <c r="H217" s="29"/>
+      <c r="B217" s="27"/>
+      <c r="C217" s="27"/>
+      <c r="D217" s="27"/>
+      <c r="E217" s="27"/>
+      <c r="F217" s="27"/>
+      <c r="G217" s="27"/>
+      <c r="H217" s="28"/>
     </row>
     <row r="218" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A218" s="27" t="s">
+      <c r="A218" s="26" t="s">
         <v>131</v>
       </c>
-      <c r="B218" s="28"/>
-      <c r="C218" s="28"/>
-      <c r="D218" s="28"/>
-      <c r="E218" s="28"/>
-      <c r="F218" s="28"/>
-      <c r="G218" s="28"/>
-      <c r="H218" s="29"/>
+      <c r="B218" s="27"/>
+      <c r="C218" s="27"/>
+      <c r="D218" s="27"/>
+      <c r="E218" s="27"/>
+      <c r="F218" s="27"/>
+      <c r="G218" s="27"/>
+      <c r="H218" s="28"/>
     </row>
     <row r="219" spans="1:8" ht="18.149999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A219" s="27" t="s">
+      <c r="A219" s="26" t="s">
         <v>40</v>
       </c>
-      <c r="B219" s="28"/>
-      <c r="C219" s="28"/>
-      <c r="D219" s="28"/>
-      <c r="E219" s="28"/>
-      <c r="F219" s="28"/>
-      <c r="G219" s="28"/>
-      <c r="H219" s="29"/>
+      <c r="B219" s="27"/>
+      <c r="C219" s="27"/>
+      <c r="D219" s="27"/>
+      <c r="E219" s="27"/>
+      <c r="F219" s="27"/>
+      <c r="G219" s="27"/>
+      <c r="H219" s="28"/>
     </row>
     <row r="220" spans="1:8" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A220" s="23" t="s">
+      <c r="A220" s="21" t="s">
         <v>22</v>
       </c>
-      <c r="B220" s="24"/>
-      <c r="C220" s="24"/>
-      <c r="D220" s="25"/>
+      <c r="B220" s="22"/>
+      <c r="C220" s="22"/>
+      <c r="D220" s="23"/>
       <c r="E220" s="7"/>
       <c r="F220" s="7"/>
       <c r="G220" s="7"/>
@@ -7369,12 +7369,12 @@
       </c>
     </row>
     <row r="239" spans="1:8" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A239" s="23" t="s">
+      <c r="A239" s="21" t="s">
         <v>30</v>
       </c>
-      <c r="B239" s="24"/>
-      <c r="C239" s="24"/>
-      <c r="D239" s="25"/>
+      <c r="B239" s="22"/>
+      <c r="C239" s="22"/>
+      <c r="D239" s="23"/>
       <c r="E239" s="13">
         <v>172480327</v>
       </c>
@@ -7383,12 +7383,12 @@
       <c r="H239" s="7"/>
     </row>
     <row r="240" spans="1:8" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A240" s="23" t="s">
+      <c r="A240" s="21" t="s">
         <v>31</v>
       </c>
-      <c r="B240" s="24"/>
-      <c r="C240" s="24"/>
-      <c r="D240" s="25"/>
+      <c r="B240" s="22"/>
+      <c r="C240" s="22"/>
+      <c r="D240" s="23"/>
       <c r="E240" s="13">
         <v>172480327</v>
       </c>
@@ -7397,164 +7397,162 @@
       <c r="H240" s="7"/>
     </row>
     <row r="241" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A241" s="27" t="s">
+      <c r="A241" s="26" t="s">
+        <v>19</v>
+      </c>
+      <c r="B241" s="27"/>
+      <c r="C241" s="27"/>
+      <c r="D241" s="27"/>
+      <c r="E241" s="27"/>
+      <c r="F241" s="27"/>
+      <c r="G241" s="27"/>
+      <c r="H241" s="28"/>
+    </row>
+    <row r="242" spans="1:8" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A242" s="26" t="s">
+        <v>20</v>
+      </c>
+      <c r="B242" s="27"/>
+      <c r="C242" s="27"/>
+      <c r="D242" s="27"/>
+      <c r="E242" s="27"/>
+      <c r="F242" s="27"/>
+      <c r="G242" s="27"/>
+      <c r="H242" s="28"/>
+    </row>
+    <row r="243" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A243" s="26" t="s">
         <v>21</v>
       </c>
-      <c r="B241" s="28"/>
-      <c r="C241" s="28"/>
-      <c r="D241" s="28"/>
-      <c r="E241" s="28"/>
-      <c r="F241" s="28"/>
-      <c r="G241" s="28"/>
-      <c r="H241" s="29"/>
-    </row>
-    <row r="242" spans="1:8" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A242" s="23" t="s">
+      <c r="B243" s="27"/>
+      <c r="C243" s="27"/>
+      <c r="D243" s="27"/>
+      <c r="E243" s="27"/>
+      <c r="F243" s="27"/>
+      <c r="G243" s="27"/>
+      <c r="H243" s="28"/>
+    </row>
+    <row r="244" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A244" s="21" t="s">
         <v>22</v>
       </c>
-      <c r="B242" s="24"/>
-      <c r="C242" s="24"/>
-      <c r="D242" s="25"/>
-      <c r="E242" s="7"/>
-      <c r="F242" s="7"/>
-      <c r="G242" s="7"/>
-      <c r="H242" s="7"/>
-    </row>
-    <row r="243" spans="1:8" ht="24.6" x14ac:dyDescent="0.3">
-      <c r="A243" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="B243" s="10">
+      <c r="B244" s="22"/>
+      <c r="C244" s="22"/>
+      <c r="D244" s="23"/>
+      <c r="E244" s="7"/>
+      <c r="F244" s="7"/>
+      <c r="G244" s="7"/>
+      <c r="H244" s="7"/>
+    </row>
+    <row r="245" spans="1:8" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A245" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="B245" s="10">
         <v>46141</v>
       </c>
-      <c r="C243" s="11" t="s">
+      <c r="C245" s="11" t="s">
         <v>136</v>
       </c>
-      <c r="D243" s="9" t="s">
+      <c r="D245" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="E243" s="12">
+      <c r="E245" s="12">
         <v>280600</v>
       </c>
-      <c r="F243" s="8"/>
-      <c r="G243" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="H243" s="9" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="244" spans="1:8" ht="24.6" x14ac:dyDescent="0.3">
-      <c r="A244" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="B244" s="10">
+      <c r="F245" s="8"/>
+      <c r="G245" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="H245" s="9" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="246" spans="1:8" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A246" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="B246" s="10">
         <v>46141</v>
       </c>
-      <c r="C244" s="11" t="s">
+      <c r="C246" s="11" t="s">
         <v>136</v>
       </c>
-      <c r="D244" s="9" t="s">
+      <c r="D246" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="E244" s="12">
+      <c r="E246" s="12">
         <v>5617204</v>
       </c>
-      <c r="F244" s="8"/>
-      <c r="G244" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="H244" s="9" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="245" spans="1:8" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A245" s="23" t="s">
+      <c r="F246" s="8"/>
+      <c r="G246" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="H246" s="9" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="247" spans="1:8" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A247" s="21" t="s">
         <v>30</v>
       </c>
-      <c r="B245" s="24"/>
-      <c r="C245" s="24"/>
-      <c r="D245" s="25"/>
-      <c r="E245" s="13">
+      <c r="B247" s="22"/>
+      <c r="C247" s="22"/>
+      <c r="D247" s="23"/>
+      <c r="E247" s="13">
         <v>5897804</v>
       </c>
-      <c r="F245" s="7"/>
-      <c r="G245" s="7"/>
-      <c r="H245" s="7"/>
-    </row>
-    <row r="246" spans="1:8" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A246" s="23" t="s">
-        <v>31</v>
-      </c>
-      <c r="B246" s="24"/>
-      <c r="C246" s="24"/>
-      <c r="D246" s="25"/>
-      <c r="E246" s="13">
-        <v>5897804</v>
-      </c>
-      <c r="F246" s="7"/>
-      <c r="G246" s="7"/>
-      <c r="H246" s="7"/>
-    </row>
-    <row r="247" spans="1:8" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A247" s="23" t="s">
-        <v>32</v>
-      </c>
-      <c r="B247" s="24"/>
-      <c r="C247" s="24"/>
-      <c r="D247" s="25"/>
-      <c r="E247" s="7"/>
       <c r="F247" s="7"/>
       <c r="G247" s="7"/>
       <c r="H247" s="7"/>
     </row>
     <row r="248" spans="1:8" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A248" s="23" t="s">
-        <v>33</v>
-      </c>
-      <c r="B248" s="24"/>
-      <c r="C248" s="24"/>
-      <c r="D248" s="25"/>
+      <c r="A248" s="21" t="s">
+        <v>31</v>
+      </c>
+      <c r="B248" s="22"/>
+      <c r="C248" s="22"/>
+      <c r="D248" s="23"/>
       <c r="E248" s="13">
-        <v>178378131</v>
+        <v>5897804</v>
       </c>
       <c r="F248" s="7"/>
       <c r="G248" s="7"/>
       <c r="H248" s="7"/>
     </row>
     <row r="249" spans="1:8" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A249" s="23" t="s">
-        <v>34</v>
-      </c>
-      <c r="B249" s="24"/>
-      <c r="C249" s="24"/>
-      <c r="D249" s="25"/>
-      <c r="E249" s="13">
-        <v>178378131</v>
-      </c>
+      <c r="A249" s="21" t="s">
+        <v>32</v>
+      </c>
+      <c r="B249" s="22"/>
+      <c r="C249" s="22"/>
+      <c r="D249" s="23"/>
+      <c r="E249" s="7"/>
       <c r="F249" s="7"/>
       <c r="G249" s="7"/>
       <c r="H249" s="7"/>
     </row>
     <row r="250" spans="1:8" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A250" s="23" t="s">
-        <v>35</v>
-      </c>
-      <c r="B250" s="24"/>
-      <c r="C250" s="24"/>
-      <c r="D250" s="25"/>
-      <c r="E250" s="7"/>
+      <c r="A250" s="21" t="s">
+        <v>33</v>
+      </c>
+      <c r="B250" s="22"/>
+      <c r="C250" s="22"/>
+      <c r="D250" s="23"/>
+      <c r="E250" s="13">
+        <v>178378131</v>
+      </c>
       <c r="F250" s="7"/>
       <c r="G250" s="7"/>
       <c r="H250" s="7"/>
     </row>
     <row r="251" spans="1:8" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A251" s="23" t="s">
-        <v>36</v>
-      </c>
-      <c r="B251" s="24"/>
-      <c r="C251" s="24"/>
-      <c r="D251" s="25"/>
+      <c r="A251" s="21" t="s">
+        <v>34</v>
+      </c>
+      <c r="B251" s="22"/>
+      <c r="C251" s="22"/>
+      <c r="D251" s="23"/>
       <c r="E251" s="13">
         <v>178378131</v>
       </c>
@@ -7563,96 +7561,159 @@
       <c r="H251" s="7"/>
     </row>
     <row r="252" spans="1:8" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A252" s="23" t="s">
-        <v>37</v>
-      </c>
-      <c r="B252" s="24"/>
-      <c r="C252" s="24"/>
-      <c r="D252" s="25"/>
-      <c r="E252" s="13">
-        <v>178378131</v>
-      </c>
+      <c r="A252" s="21" t="s">
+        <v>35</v>
+      </c>
+      <c r="B252" s="22"/>
+      <c r="C252" s="22"/>
+      <c r="D252" s="23"/>
+      <c r="E252" s="7"/>
       <c r="F252" s="7"/>
       <c r="G252" s="7"/>
       <c r="H252" s="7"/>
     </row>
     <row r="253" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A253" s="15"/>
+      <c r="A253" s="21" t="s">
+        <v>36</v>
+      </c>
+      <c r="B253" s="22"/>
+      <c r="C253" s="22"/>
+      <c r="D253" s="23"/>
+      <c r="E253" s="13">
+        <v>178378131</v>
+      </c>
+      <c r="F253" s="7"/>
+      <c r="G253" s="7"/>
+      <c r="H253" s="7"/>
     </row>
     <row r="254" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A254" s="15"/>
+      <c r="A254" s="21" t="s">
+        <v>37</v>
+      </c>
+      <c r="B254" s="22"/>
+      <c r="C254" s="22"/>
+      <c r="D254" s="23"/>
+      <c r="E254" s="13">
+        <v>178378131</v>
+      </c>
+      <c r="F254" s="7"/>
+      <c r="G254" s="7"/>
+      <c r="H254" s="7"/>
     </row>
     <row r="255" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A255" s="15"/>
     </row>
     <row r="256" spans="1:8" ht="11.55" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A256" s="16" t="s">
-        <v>22</v>
-      </c>
-      <c r="B256" s="7"/>
-      <c r="C256" s="7"/>
-      <c r="D256" s="7"/>
-      <c r="E256" s="7"/>
+      <c r="A256" s="15"/>
     </row>
     <row r="257" spans="1:5" ht="11.55" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A257" s="16" t="s">
-        <v>30</v>
-      </c>
-      <c r="B257" s="13">
-        <v>1756914319</v>
-      </c>
-      <c r="C257" s="13">
-        <v>29678782</v>
-      </c>
-      <c r="D257" s="7"/>
-      <c r="E257" s="7"/>
+      <c r="A257" s="15"/>
     </row>
     <row r="258" spans="1:5" ht="11.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A258" s="16" t="s">
-        <v>31</v>
-      </c>
-      <c r="B258" s="13">
-        <v>1727235537</v>
-      </c>
+        <v>22</v>
+      </c>
+      <c r="B258" s="7"/>
       <c r="C258" s="7"/>
       <c r="D258" s="7"/>
       <c r="E258" s="7"/>
     </row>
-    <row r="261" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A261" s="26"/>
-      <c r="B261" s="26"/>
-      <c r="C261" s="17" t="s">
+    <row r="259" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A259" s="16" t="s">
+        <v>30</v>
+      </c>
+      <c r="B259" s="13">
+        <v>1756914319</v>
+      </c>
+      <c r="C259" s="13">
+        <v>29678782</v>
+      </c>
+      <c r="D259" s="7"/>
+      <c r="E259" s="7"/>
+    </row>
+    <row r="260" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A260" s="16" t="s">
+        <v>31</v>
+      </c>
+      <c r="B260" s="13">
+        <v>1727235537</v>
+      </c>
+      <c r="C260" s="7"/>
+      <c r="D260" s="7"/>
+      <c r="E260" s="7"/>
+    </row>
+    <row r="261" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="262" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="263" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A263" s="33"/>
+      <c r="B263" s="33"/>
+      <c r="C263" s="17" t="s">
         <v>137</v>
       </c>
     </row>
-    <row r="262" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A262" s="4" t="s">
+    <row r="264" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A264" s="4" t="s">
         <v>138</v>
       </c>
-      <c r="B262" s="1"/>
-      <c r="C262" s="4" t="s">
+      <c r="B264" s="1"/>
+      <c r="C264" s="4" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="263" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A263" s="18" t="s">
+    <row r="265" spans="1:5" ht="12.15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A265" s="18" t="s">
         <v>140</v>
       </c>
-      <c r="B263" s="6"/>
-      <c r="C263" s="18" t="s">
+      <c r="B265" s="6"/>
+      <c r="C265" s="18" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="265" spans="1:5" ht="12.15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A265" s="19" t="s">
+    <row r="267" spans="1:5" ht="20.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A267" s="19" t="s">
         <v>142</v>
       </c>
-      <c r="B265" s="20" t="s">
+      <c r="B267" s="20" t="s">
         <v>143</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="49">
+  <mergeCells count="51">
+    <mergeCell ref="A242:H242"/>
+    <mergeCell ref="A12:H12"/>
+    <mergeCell ref="A250:D250"/>
+    <mergeCell ref="A251:D251"/>
+    <mergeCell ref="A252:D252"/>
+    <mergeCell ref="A253:D253"/>
+    <mergeCell ref="A216:D216"/>
+    <mergeCell ref="A217:H217"/>
+    <mergeCell ref="A218:H218"/>
+    <mergeCell ref="A219:H219"/>
+    <mergeCell ref="A220:D220"/>
+    <mergeCell ref="A239:D239"/>
+    <mergeCell ref="A210:D210"/>
+    <mergeCell ref="A211:D211"/>
+    <mergeCell ref="A212:D212"/>
+    <mergeCell ref="A213:D213"/>
+    <mergeCell ref="A214:D214"/>
+    <mergeCell ref="A254:D254"/>
+    <mergeCell ref="A263:B263"/>
+    <mergeCell ref="A240:D240"/>
+    <mergeCell ref="A243:H243"/>
+    <mergeCell ref="A244:D244"/>
+    <mergeCell ref="A247:D247"/>
+    <mergeCell ref="A248:D248"/>
+    <mergeCell ref="A249:D249"/>
+    <mergeCell ref="A241:H241"/>
+    <mergeCell ref="A46:D46"/>
+    <mergeCell ref="A47:D47"/>
+    <mergeCell ref="A215:D215"/>
+    <mergeCell ref="A49:D49"/>
+    <mergeCell ref="A50:H50"/>
+    <mergeCell ref="A51:H51"/>
+    <mergeCell ref="A52:H52"/>
+    <mergeCell ref="A53:D53"/>
+    <mergeCell ref="A209:D209"/>
     <mergeCell ref="A48:D48"/>
     <mergeCell ref="H13:H14"/>
     <mergeCell ref="A15:H15"/>
@@ -7669,39 +7730,6 @@
     <mergeCell ref="A43:D43"/>
     <mergeCell ref="A44:D44"/>
     <mergeCell ref="A45:D45"/>
-    <mergeCell ref="A46:D46"/>
-    <mergeCell ref="A47:D47"/>
-    <mergeCell ref="A215:D215"/>
-    <mergeCell ref="A49:D49"/>
-    <mergeCell ref="A50:H50"/>
-    <mergeCell ref="A51:H51"/>
-    <mergeCell ref="A52:H52"/>
-    <mergeCell ref="A53:D53"/>
-    <mergeCell ref="A209:D209"/>
-    <mergeCell ref="A252:D252"/>
-    <mergeCell ref="A261:B261"/>
-    <mergeCell ref="A240:D240"/>
-    <mergeCell ref="A241:H241"/>
-    <mergeCell ref="A242:D242"/>
-    <mergeCell ref="A245:D245"/>
-    <mergeCell ref="A246:D246"/>
-    <mergeCell ref="A247:D247"/>
-    <mergeCell ref="A12:H12"/>
-    <mergeCell ref="A248:D248"/>
-    <mergeCell ref="A249:D249"/>
-    <mergeCell ref="A250:D250"/>
-    <mergeCell ref="A251:D251"/>
-    <mergeCell ref="A216:D216"/>
-    <mergeCell ref="A217:H217"/>
-    <mergeCell ref="A218:H218"/>
-    <mergeCell ref="A219:H219"/>
-    <mergeCell ref="A220:D220"/>
-    <mergeCell ref="A239:D239"/>
-    <mergeCell ref="A210:D210"/>
-    <mergeCell ref="A211:D211"/>
-    <mergeCell ref="A212:D212"/>
-    <mergeCell ref="A213:D213"/>
-    <mergeCell ref="A214:D214"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/PM_092.xlsx
+++ b/PM_092.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="Z:\TUAN HOC A.I\1. TCKT_PCVT\4. Công nghệ AI\KT SCL\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{937510B4-8285-42FF-8E17-8B3A854FDBE4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED5E2A54-56B2-46BF-96EE-032D3107D2EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{AC1AAD16-9061-42F9-B216-D7E5AB78D483}"/>
   </bookViews>
@@ -1770,6 +1770,19 @@
       <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="33" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="33" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="33" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="21" fillId="33" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="33" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1778,20 +1791,14 @@
     <xf numFmtId="0" fontId="21" fillId="33" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="33" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="21" fillId="34" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="34" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="33" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="33" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="33" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="34" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
@@ -1805,13 +1812,6 @@
     <xf numFmtId="0" fontId="21" fillId="34" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="33" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -2249,98 +2249,98 @@
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A12" s="34" t="s">
+      <c r="A12" s="24" t="s">
         <v>9</v>
       </c>
-      <c r="B12" s="35"/>
-      <c r="C12" s="35"/>
-      <c r="D12" s="35"/>
-      <c r="E12" s="35"/>
-      <c r="F12" s="35"/>
-      <c r="G12" s="35"/>
-      <c r="H12" s="35"/>
+      <c r="B12" s="25"/>
+      <c r="C12" s="25"/>
+      <c r="D12" s="25"/>
+      <c r="E12" s="25"/>
+      <c r="F12" s="25"/>
+      <c r="G12" s="25"/>
+      <c r="H12" s="25"/>
     </row>
     <row r="13" spans="1:8" ht="30.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="29" t="s">
+      <c r="A13" s="32" t="s">
         <v>10</v>
       </c>
-      <c r="B13" s="29" t="s">
+      <c r="B13" s="32" t="s">
         <v>11</v>
       </c>
-      <c r="C13" s="29" t="s">
+      <c r="C13" s="32" t="s">
         <v>12</v>
       </c>
-      <c r="D13" s="29" t="s">
+      <c r="D13" s="32" t="s">
         <v>13</v>
       </c>
-      <c r="E13" s="31" t="s">
+      <c r="E13" s="34" t="s">
         <v>14</v>
       </c>
-      <c r="F13" s="32"/>
-      <c r="G13" s="24" t="s">
+      <c r="F13" s="35"/>
+      <c r="G13" s="30" t="s">
         <v>15</v>
       </c>
-      <c r="H13" s="24" t="s">
+      <c r="H13" s="30" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="14" spans="1:8" ht="28.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="30"/>
-      <c r="B14" s="30"/>
-      <c r="C14" s="30"/>
-      <c r="D14" s="30"/>
+      <c r="A14" s="33"/>
+      <c r="B14" s="33"/>
+      <c r="C14" s="33"/>
+      <c r="D14" s="33"/>
       <c r="E14" s="5" t="s">
         <v>17</v>
       </c>
       <c r="F14" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="G14" s="25"/>
-      <c r="H14" s="25"/>
+      <c r="G14" s="31"/>
+      <c r="H14" s="31"/>
     </row>
     <row r="15" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="26" t="s">
+      <c r="A15" s="21" t="s">
         <v>19</v>
       </c>
-      <c r="B15" s="27"/>
-      <c r="C15" s="27"/>
-      <c r="D15" s="27"/>
-      <c r="E15" s="27"/>
-      <c r="F15" s="27"/>
-      <c r="G15" s="27"/>
-      <c r="H15" s="28"/>
+      <c r="B15" s="22"/>
+      <c r="C15" s="22"/>
+      <c r="D15" s="22"/>
+      <c r="E15" s="22"/>
+      <c r="F15" s="22"/>
+      <c r="G15" s="22"/>
+      <c r="H15" s="23"/>
     </row>
     <row r="16" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="26" t="s">
+      <c r="A16" s="21" t="s">
         <v>20</v>
       </c>
-      <c r="B16" s="27"/>
-      <c r="C16" s="27"/>
-      <c r="D16" s="27"/>
-      <c r="E16" s="27"/>
-      <c r="F16" s="27"/>
-      <c r="G16" s="27"/>
-      <c r="H16" s="28"/>
+      <c r="B16" s="22"/>
+      <c r="C16" s="22"/>
+      <c r="D16" s="22"/>
+      <c r="E16" s="22"/>
+      <c r="F16" s="22"/>
+      <c r="G16" s="22"/>
+      <c r="H16" s="23"/>
     </row>
     <row r="17" spans="1:8" ht="18.149999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="26" t="s">
+      <c r="A17" s="21" t="s">
         <v>21</v>
       </c>
-      <c r="B17" s="27"/>
-      <c r="C17" s="27"/>
-      <c r="D17" s="27"/>
-      <c r="E17" s="27"/>
-      <c r="F17" s="27"/>
-      <c r="G17" s="27"/>
-      <c r="H17" s="28"/>
+      <c r="B17" s="22"/>
+      <c r="C17" s="22"/>
+      <c r="D17" s="22"/>
+      <c r="E17" s="22"/>
+      <c r="F17" s="22"/>
+      <c r="G17" s="22"/>
+      <c r="H17" s="23"/>
     </row>
     <row r="18" spans="1:8" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="21" t="s">
+      <c r="A18" s="26" t="s">
         <v>22</v>
       </c>
-      <c r="B18" s="22"/>
-      <c r="C18" s="22"/>
-      <c r="D18" s="23"/>
+      <c r="B18" s="27"/>
+      <c r="C18" s="27"/>
+      <c r="D18" s="28"/>
       <c r="E18" s="7"/>
       <c r="F18" s="7"/>
       <c r="G18" s="7"/>
@@ -2899,12 +2899,12 @@
       </c>
     </row>
     <row r="42" spans="1:8" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="21" t="s">
+      <c r="A42" s="26" t="s">
         <v>30</v>
       </c>
-      <c r="B42" s="22"/>
-      <c r="C42" s="22"/>
-      <c r="D42" s="23"/>
+      <c r="B42" s="27"/>
+      <c r="C42" s="27"/>
+      <c r="D42" s="28"/>
       <c r="E42" s="13">
         <v>103128028</v>
       </c>
@@ -2913,12 +2913,12 @@
       <c r="H42" s="7"/>
     </row>
     <row r="43" spans="1:8" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A43" s="21" t="s">
+      <c r="A43" s="26" t="s">
         <v>31</v>
       </c>
-      <c r="B43" s="22"/>
-      <c r="C43" s="22"/>
-      <c r="D43" s="23"/>
+      <c r="B43" s="27"/>
+      <c r="C43" s="27"/>
+      <c r="D43" s="28"/>
       <c r="E43" s="13">
         <v>103128028</v>
       </c>
@@ -2927,24 +2927,24 @@
       <c r="H43" s="7"/>
     </row>
     <row r="44" spans="1:8" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A44" s="21" t="s">
+      <c r="A44" s="26" t="s">
         <v>32</v>
       </c>
-      <c r="B44" s="22"/>
-      <c r="C44" s="22"/>
-      <c r="D44" s="23"/>
+      <c r="B44" s="27"/>
+      <c r="C44" s="27"/>
+      <c r="D44" s="28"/>
       <c r="E44" s="7"/>
       <c r="F44" s="7"/>
       <c r="G44" s="7"/>
       <c r="H44" s="7"/>
     </row>
     <row r="45" spans="1:8" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A45" s="21" t="s">
+      <c r="A45" s="26" t="s">
         <v>33</v>
       </c>
-      <c r="B45" s="22"/>
-      <c r="C45" s="22"/>
-      <c r="D45" s="23"/>
+      <c r="B45" s="27"/>
+      <c r="C45" s="27"/>
+      <c r="D45" s="28"/>
       <c r="E45" s="13">
         <v>103128028</v>
       </c>
@@ -2953,12 +2953,12 @@
       <c r="H45" s="7"/>
     </row>
     <row r="46" spans="1:8" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A46" s="21" t="s">
+      <c r="A46" s="26" t="s">
         <v>34</v>
       </c>
-      <c r="B46" s="22"/>
-      <c r="C46" s="22"/>
-      <c r="D46" s="23"/>
+      <c r="B46" s="27"/>
+      <c r="C46" s="27"/>
+      <c r="D46" s="28"/>
       <c r="E46" s="13">
         <v>103128028</v>
       </c>
@@ -2967,24 +2967,24 @@
       <c r="H46" s="7"/>
     </row>
     <row r="47" spans="1:8" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A47" s="21" t="s">
+      <c r="A47" s="26" t="s">
         <v>35</v>
       </c>
-      <c r="B47" s="22"/>
-      <c r="C47" s="22"/>
-      <c r="D47" s="23"/>
+      <c r="B47" s="27"/>
+      <c r="C47" s="27"/>
+      <c r="D47" s="28"/>
       <c r="E47" s="7"/>
       <c r="F47" s="7"/>
       <c r="G47" s="7"/>
       <c r="H47" s="7"/>
     </row>
     <row r="48" spans="1:8" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A48" s="21" t="s">
+      <c r="A48" s="26" t="s">
         <v>36</v>
       </c>
-      <c r="B48" s="22"/>
-      <c r="C48" s="22"/>
-      <c r="D48" s="23"/>
+      <c r="B48" s="27"/>
+      <c r="C48" s="27"/>
+      <c r="D48" s="28"/>
       <c r="E48" s="13">
         <v>103128028</v>
       </c>
@@ -2993,12 +2993,12 @@
       <c r="H48" s="7"/>
     </row>
     <row r="49" spans="1:8" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A49" s="21" t="s">
+      <c r="A49" s="26" t="s">
         <v>37</v>
       </c>
-      <c r="B49" s="22"/>
-      <c r="C49" s="22"/>
-      <c r="D49" s="23"/>
+      <c r="B49" s="27"/>
+      <c r="C49" s="27"/>
+      <c r="D49" s="28"/>
       <c r="E49" s="13">
         <v>103128028</v>
       </c>
@@ -3007,48 +3007,48 @@
       <c r="H49" s="7"/>
     </row>
     <row r="50" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A50" s="26" t="s">
+      <c r="A50" s="21" t="s">
         <v>38</v>
       </c>
-      <c r="B50" s="27"/>
-      <c r="C50" s="27"/>
-      <c r="D50" s="27"/>
-      <c r="E50" s="27"/>
-      <c r="F50" s="27"/>
-      <c r="G50" s="27"/>
-      <c r="H50" s="28"/>
+      <c r="B50" s="22"/>
+      <c r="C50" s="22"/>
+      <c r="D50" s="22"/>
+      <c r="E50" s="22"/>
+      <c r="F50" s="22"/>
+      <c r="G50" s="22"/>
+      <c r="H50" s="23"/>
     </row>
     <row r="51" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A51" s="26" t="s">
+      <c r="A51" s="21" t="s">
         <v>39</v>
       </c>
-      <c r="B51" s="27"/>
-      <c r="C51" s="27"/>
-      <c r="D51" s="27"/>
-      <c r="E51" s="27"/>
-      <c r="F51" s="27"/>
-      <c r="G51" s="27"/>
-      <c r="H51" s="28"/>
+      <c r="B51" s="22"/>
+      <c r="C51" s="22"/>
+      <c r="D51" s="22"/>
+      <c r="E51" s="22"/>
+      <c r="F51" s="22"/>
+      <c r="G51" s="22"/>
+      <c r="H51" s="23"/>
     </row>
     <row r="52" spans="1:8" ht="18.149999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A52" s="26" t="s">
+      <c r="A52" s="21" t="s">
         <v>40</v>
       </c>
-      <c r="B52" s="27"/>
-      <c r="C52" s="27"/>
-      <c r="D52" s="27"/>
-      <c r="E52" s="27"/>
-      <c r="F52" s="27"/>
-      <c r="G52" s="27"/>
-      <c r="H52" s="28"/>
+      <c r="B52" s="22"/>
+      <c r="C52" s="22"/>
+      <c r="D52" s="22"/>
+      <c r="E52" s="22"/>
+      <c r="F52" s="22"/>
+      <c r="G52" s="22"/>
+      <c r="H52" s="23"/>
     </row>
     <row r="53" spans="1:8" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A53" s="21" t="s">
+      <c r="A53" s="26" t="s">
         <v>22</v>
       </c>
-      <c r="B53" s="22"/>
-      <c r="C53" s="22"/>
-      <c r="D53" s="23"/>
+      <c r="B53" s="27"/>
+      <c r="C53" s="27"/>
+      <c r="D53" s="28"/>
       <c r="E53" s="7"/>
       <c r="F53" s="7"/>
       <c r="G53" s="7"/>
@@ -6775,12 +6775,12 @@
       </c>
     </row>
     <row r="209" spans="1:8" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A209" s="21" t="s">
+      <c r="A209" s="26" t="s">
         <v>30</v>
       </c>
-      <c r="B209" s="22"/>
-      <c r="C209" s="22"/>
-      <c r="D209" s="23"/>
+      <c r="B209" s="27"/>
+      <c r="C209" s="27"/>
+      <c r="D209" s="28"/>
       <c r="E209" s="13">
         <v>1475408160</v>
       </c>
@@ -6791,12 +6791,12 @@
       <c r="H209" s="7"/>
     </row>
     <row r="210" spans="1:8" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A210" s="21" t="s">
+      <c r="A210" s="26" t="s">
         <v>31</v>
       </c>
-      <c r="B210" s="22"/>
-      <c r="C210" s="22"/>
-      <c r="D210" s="23"/>
+      <c r="B210" s="27"/>
+      <c r="C210" s="27"/>
+      <c r="D210" s="28"/>
       <c r="E210" s="13">
         <v>1445729378</v>
       </c>
@@ -6805,24 +6805,24 @@
       <c r="H210" s="7"/>
     </row>
     <row r="211" spans="1:8" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A211" s="21" t="s">
+      <c r="A211" s="26" t="s">
         <v>32</v>
       </c>
-      <c r="B211" s="22"/>
-      <c r="C211" s="22"/>
-      <c r="D211" s="23"/>
+      <c r="B211" s="27"/>
+      <c r="C211" s="27"/>
+      <c r="D211" s="28"/>
       <c r="E211" s="7"/>
       <c r="F211" s="7"/>
       <c r="G211" s="7"/>
       <c r="H211" s="7"/>
     </row>
     <row r="212" spans="1:8" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A212" s="21" t="s">
+      <c r="A212" s="26" t="s">
         <v>33</v>
       </c>
-      <c r="B212" s="22"/>
-      <c r="C212" s="22"/>
-      <c r="D212" s="23"/>
+      <c r="B212" s="27"/>
+      <c r="C212" s="27"/>
+      <c r="D212" s="28"/>
       <c r="E212" s="13">
         <v>1475408160</v>
       </c>
@@ -6833,12 +6833,12 @@
       <c r="H212" s="7"/>
     </row>
     <row r="213" spans="1:8" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A213" s="21" t="s">
+      <c r="A213" s="26" t="s">
         <v>34</v>
       </c>
-      <c r="B213" s="22"/>
-      <c r="C213" s="22"/>
-      <c r="D213" s="23"/>
+      <c r="B213" s="27"/>
+      <c r="C213" s="27"/>
+      <c r="D213" s="28"/>
       <c r="E213" s="13">
         <v>1445729378</v>
       </c>
@@ -6847,24 +6847,24 @@
       <c r="H213" s="7"/>
     </row>
     <row r="214" spans="1:8" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A214" s="21" t="s">
+      <c r="A214" s="26" t="s">
         <v>35</v>
       </c>
-      <c r="B214" s="22"/>
-      <c r="C214" s="22"/>
-      <c r="D214" s="23"/>
+      <c r="B214" s="27"/>
+      <c r="C214" s="27"/>
+      <c r="D214" s="28"/>
       <c r="E214" s="7"/>
       <c r="F214" s="7"/>
       <c r="G214" s="7"/>
       <c r="H214" s="7"/>
     </row>
     <row r="215" spans="1:8" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A215" s="21" t="s">
+      <c r="A215" s="26" t="s">
         <v>36</v>
       </c>
-      <c r="B215" s="22"/>
-      <c r="C215" s="22"/>
-      <c r="D215" s="23"/>
+      <c r="B215" s="27"/>
+      <c r="C215" s="27"/>
+      <c r="D215" s="28"/>
       <c r="E215" s="13">
         <v>1475408160</v>
       </c>
@@ -6875,12 +6875,12 @@
       <c r="H215" s="7"/>
     </row>
     <row r="216" spans="1:8" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A216" s="21" t="s">
+      <c r="A216" s="26" t="s">
         <v>37</v>
       </c>
-      <c r="B216" s="22"/>
-      <c r="C216" s="22"/>
-      <c r="D216" s="23"/>
+      <c r="B216" s="27"/>
+      <c r="C216" s="27"/>
+      <c r="D216" s="28"/>
       <c r="E216" s="13">
         <v>1445729378</v>
       </c>
@@ -6889,48 +6889,48 @@
       <c r="H216" s="7"/>
     </row>
     <row r="217" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A217" s="26" t="s">
+      <c r="A217" s="21" t="s">
         <v>130</v>
       </c>
-      <c r="B217" s="27"/>
-      <c r="C217" s="27"/>
-      <c r="D217" s="27"/>
-      <c r="E217" s="27"/>
-      <c r="F217" s="27"/>
-      <c r="G217" s="27"/>
-      <c r="H217" s="28"/>
+      <c r="B217" s="22"/>
+      <c r="C217" s="22"/>
+      <c r="D217" s="22"/>
+      <c r="E217" s="22"/>
+      <c r="F217" s="22"/>
+      <c r="G217" s="22"/>
+      <c r="H217" s="23"/>
     </row>
     <row r="218" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A218" s="26" t="s">
+      <c r="A218" s="21" t="s">
         <v>131</v>
       </c>
-      <c r="B218" s="27"/>
-      <c r="C218" s="27"/>
-      <c r="D218" s="27"/>
-      <c r="E218" s="27"/>
-      <c r="F218" s="27"/>
-      <c r="G218" s="27"/>
-      <c r="H218" s="28"/>
+      <c r="B218" s="22"/>
+      <c r="C218" s="22"/>
+      <c r="D218" s="22"/>
+      <c r="E218" s="22"/>
+      <c r="F218" s="22"/>
+      <c r="G218" s="22"/>
+      <c r="H218" s="23"/>
     </row>
     <row r="219" spans="1:8" ht="18.149999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A219" s="26" t="s">
+      <c r="A219" s="21" t="s">
         <v>40</v>
       </c>
-      <c r="B219" s="27"/>
-      <c r="C219" s="27"/>
-      <c r="D219" s="27"/>
-      <c r="E219" s="27"/>
-      <c r="F219" s="27"/>
-      <c r="G219" s="27"/>
-      <c r="H219" s="28"/>
+      <c r="B219" s="22"/>
+      <c r="C219" s="22"/>
+      <c r="D219" s="22"/>
+      <c r="E219" s="22"/>
+      <c r="F219" s="22"/>
+      <c r="G219" s="22"/>
+      <c r="H219" s="23"/>
     </row>
     <row r="220" spans="1:8" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A220" s="21" t="s">
+      <c r="A220" s="26" t="s">
         <v>22</v>
       </c>
-      <c r="B220" s="22"/>
-      <c r="C220" s="22"/>
-      <c r="D220" s="23"/>
+      <c r="B220" s="27"/>
+      <c r="C220" s="27"/>
+      <c r="D220" s="28"/>
       <c r="E220" s="7"/>
       <c r="F220" s="7"/>
       <c r="G220" s="7"/>
@@ -7369,12 +7369,12 @@
       </c>
     </row>
     <row r="239" spans="1:8" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A239" s="21" t="s">
+      <c r="A239" s="26" t="s">
         <v>30</v>
       </c>
-      <c r="B239" s="22"/>
-      <c r="C239" s="22"/>
-      <c r="D239" s="23"/>
+      <c r="B239" s="27"/>
+      <c r="C239" s="27"/>
+      <c r="D239" s="28"/>
       <c r="E239" s="13">
         <v>172480327</v>
       </c>
@@ -7383,12 +7383,12 @@
       <c r="H239" s="7"/>
     </row>
     <row r="240" spans="1:8" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A240" s="21" t="s">
+      <c r="A240" s="26" t="s">
         <v>31</v>
       </c>
-      <c r="B240" s="22"/>
-      <c r="C240" s="22"/>
-      <c r="D240" s="23"/>
+      <c r="B240" s="27"/>
+      <c r="C240" s="27"/>
+      <c r="D240" s="28"/>
       <c r="E240" s="13">
         <v>172480327</v>
       </c>
@@ -7397,48 +7397,48 @@
       <c r="H240" s="7"/>
     </row>
     <row r="241" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A241" s="26" t="s">
+      <c r="A241" s="21" t="s">
         <v>19</v>
       </c>
-      <c r="B241" s="27"/>
-      <c r="C241" s="27"/>
-      <c r="D241" s="27"/>
-      <c r="E241" s="27"/>
-      <c r="F241" s="27"/>
-      <c r="G241" s="27"/>
-      <c r="H241" s="28"/>
+      <c r="B241" s="22"/>
+      <c r="C241" s="22"/>
+      <c r="D241" s="22"/>
+      <c r="E241" s="22"/>
+      <c r="F241" s="22"/>
+      <c r="G241" s="22"/>
+      <c r="H241" s="23"/>
     </row>
     <row r="242" spans="1:8" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A242" s="26" t="s">
+      <c r="A242" s="21" t="s">
         <v>20</v>
       </c>
-      <c r="B242" s="27"/>
-      <c r="C242" s="27"/>
-      <c r="D242" s="27"/>
-      <c r="E242" s="27"/>
-      <c r="F242" s="27"/>
-      <c r="G242" s="27"/>
-      <c r="H242" s="28"/>
+      <c r="B242" s="22"/>
+      <c r="C242" s="22"/>
+      <c r="D242" s="22"/>
+      <c r="E242" s="22"/>
+      <c r="F242" s="22"/>
+      <c r="G242" s="22"/>
+      <c r="H242" s="23"/>
     </row>
     <row r="243" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A243" s="26" t="s">
+      <c r="A243" s="21" t="s">
         <v>21</v>
       </c>
-      <c r="B243" s="27"/>
-      <c r="C243" s="27"/>
-      <c r="D243" s="27"/>
-      <c r="E243" s="27"/>
-      <c r="F243" s="27"/>
-      <c r="G243" s="27"/>
-      <c r="H243" s="28"/>
+      <c r="B243" s="22"/>
+      <c r="C243" s="22"/>
+      <c r="D243" s="22"/>
+      <c r="E243" s="22"/>
+      <c r="F243" s="22"/>
+      <c r="G243" s="22"/>
+      <c r="H243" s="23"/>
     </row>
     <row r="244" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A244" s="21" t="s">
+      <c r="A244" s="26" t="s">
         <v>22</v>
       </c>
-      <c r="B244" s="22"/>
-      <c r="C244" s="22"/>
-      <c r="D244" s="23"/>
+      <c r="B244" s="27"/>
+      <c r="C244" s="27"/>
+      <c r="D244" s="28"/>
       <c r="E244" s="7"/>
       <c r="F244" s="7"/>
       <c r="G244" s="7"/>
@@ -7493,12 +7493,12 @@
       </c>
     </row>
     <row r="247" spans="1:8" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A247" s="21" t="s">
+      <c r="A247" s="26" t="s">
         <v>30</v>
       </c>
-      <c r="B247" s="22"/>
-      <c r="C247" s="22"/>
-      <c r="D247" s="23"/>
+      <c r="B247" s="27"/>
+      <c r="C247" s="27"/>
+      <c r="D247" s="28"/>
       <c r="E247" s="13">
         <v>5897804</v>
       </c>
@@ -7507,12 +7507,12 @@
       <c r="H247" s="7"/>
     </row>
     <row r="248" spans="1:8" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A248" s="21" t="s">
+      <c r="A248" s="26" t="s">
         <v>31</v>
       </c>
-      <c r="B248" s="22"/>
-      <c r="C248" s="22"/>
-      <c r="D248" s="23"/>
+      <c r="B248" s="27"/>
+      <c r="C248" s="27"/>
+      <c r="D248" s="28"/>
       <c r="E248" s="13">
         <v>5897804</v>
       </c>
@@ -7521,24 +7521,24 @@
       <c r="H248" s="7"/>
     </row>
     <row r="249" spans="1:8" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A249" s="21" t="s">
+      <c r="A249" s="26" t="s">
         <v>32</v>
       </c>
-      <c r="B249" s="22"/>
-      <c r="C249" s="22"/>
-      <c r="D249" s="23"/>
+      <c r="B249" s="27"/>
+      <c r="C249" s="27"/>
+      <c r="D249" s="28"/>
       <c r="E249" s="7"/>
       <c r="F249" s="7"/>
       <c r="G249" s="7"/>
       <c r="H249" s="7"/>
     </row>
     <row r="250" spans="1:8" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A250" s="21" t="s">
+      <c r="A250" s="26" t="s">
         <v>33</v>
       </c>
-      <c r="B250" s="22"/>
-      <c r="C250" s="22"/>
-      <c r="D250" s="23"/>
+      <c r="B250" s="27"/>
+      <c r="C250" s="27"/>
+      <c r="D250" s="28"/>
       <c r="E250" s="13">
         <v>178378131</v>
       </c>
@@ -7547,12 +7547,12 @@
       <c r="H250" s="7"/>
     </row>
     <row r="251" spans="1:8" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A251" s="21" t="s">
+      <c r="A251" s="26" t="s">
         <v>34</v>
       </c>
-      <c r="B251" s="22"/>
-      <c r="C251" s="22"/>
-      <c r="D251" s="23"/>
+      <c r="B251" s="27"/>
+      <c r="C251" s="27"/>
+      <c r="D251" s="28"/>
       <c r="E251" s="13">
         <v>178378131</v>
       </c>
@@ -7561,24 +7561,24 @@
       <c r="H251" s="7"/>
     </row>
     <row r="252" spans="1:8" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A252" s="21" t="s">
+      <c r="A252" s="26" t="s">
         <v>35</v>
       </c>
-      <c r="B252" s="22"/>
-      <c r="C252" s="22"/>
-      <c r="D252" s="23"/>
+      <c r="B252" s="27"/>
+      <c r="C252" s="27"/>
+      <c r="D252" s="28"/>
       <c r="E252" s="7"/>
       <c r="F252" s="7"/>
       <c r="G252" s="7"/>
       <c r="H252" s="7"/>
     </row>
     <row r="253" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A253" s="21" t="s">
+      <c r="A253" s="26" t="s">
         <v>36</v>
       </c>
-      <c r="B253" s="22"/>
-      <c r="C253" s="22"/>
-      <c r="D253" s="23"/>
+      <c r="B253" s="27"/>
+      <c r="C253" s="27"/>
+      <c r="D253" s="28"/>
       <c r="E253" s="13">
         <v>178378131</v>
       </c>
@@ -7587,12 +7587,12 @@
       <c r="H253" s="7"/>
     </row>
     <row r="254" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A254" s="21" t="s">
+      <c r="A254" s="26" t="s">
         <v>37</v>
       </c>
-      <c r="B254" s="22"/>
-      <c r="C254" s="22"/>
-      <c r="D254" s="23"/>
+      <c r="B254" s="27"/>
+      <c r="C254" s="27"/>
+      <c r="D254" s="28"/>
       <c r="E254" s="13">
         <v>178378131</v>
       </c>
@@ -7645,8 +7645,8 @@
     <row r="261" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="262" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="263" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A263" s="33"/>
-      <c r="B263" s="33"/>
+      <c r="A263" s="29"/>
+      <c r="B263" s="29"/>
       <c r="C263" s="17" t="s">
         <v>137</v>
       </c>
@@ -7679,38 +7679,9 @@
     </row>
   </sheetData>
   <mergeCells count="51">
-    <mergeCell ref="A242:H242"/>
-    <mergeCell ref="A12:H12"/>
-    <mergeCell ref="A250:D250"/>
-    <mergeCell ref="A251:D251"/>
-    <mergeCell ref="A252:D252"/>
-    <mergeCell ref="A253:D253"/>
-    <mergeCell ref="A216:D216"/>
-    <mergeCell ref="A217:H217"/>
-    <mergeCell ref="A218:H218"/>
-    <mergeCell ref="A219:H219"/>
-    <mergeCell ref="A220:D220"/>
-    <mergeCell ref="A239:D239"/>
-    <mergeCell ref="A210:D210"/>
-    <mergeCell ref="A211:D211"/>
-    <mergeCell ref="A212:D212"/>
-    <mergeCell ref="A213:D213"/>
-    <mergeCell ref="A214:D214"/>
-    <mergeCell ref="A254:D254"/>
-    <mergeCell ref="A263:B263"/>
-    <mergeCell ref="A240:D240"/>
-    <mergeCell ref="A243:H243"/>
-    <mergeCell ref="A244:D244"/>
-    <mergeCell ref="A247:D247"/>
-    <mergeCell ref="A248:D248"/>
-    <mergeCell ref="A249:D249"/>
-    <mergeCell ref="A241:H241"/>
-    <mergeCell ref="A46:D46"/>
-    <mergeCell ref="A47:D47"/>
-    <mergeCell ref="A215:D215"/>
-    <mergeCell ref="A49:D49"/>
-    <mergeCell ref="A50:H50"/>
-    <mergeCell ref="A51:H51"/>
+    <mergeCell ref="A43:D43"/>
+    <mergeCell ref="A44:D44"/>
+    <mergeCell ref="A45:D45"/>
     <mergeCell ref="A52:H52"/>
     <mergeCell ref="A53:D53"/>
     <mergeCell ref="A209:D209"/>
@@ -7727,9 +7698,38 @@
     <mergeCell ref="D13:D14"/>
     <mergeCell ref="E13:F13"/>
     <mergeCell ref="G13:G14"/>
-    <mergeCell ref="A43:D43"/>
-    <mergeCell ref="A44:D44"/>
-    <mergeCell ref="A45:D45"/>
+    <mergeCell ref="A254:D254"/>
+    <mergeCell ref="A263:B263"/>
+    <mergeCell ref="A240:D240"/>
+    <mergeCell ref="A243:H243"/>
+    <mergeCell ref="A244:D244"/>
+    <mergeCell ref="A247:D247"/>
+    <mergeCell ref="A248:D248"/>
+    <mergeCell ref="A249:D249"/>
+    <mergeCell ref="A241:H241"/>
+    <mergeCell ref="A253:D253"/>
+    <mergeCell ref="A216:D216"/>
+    <mergeCell ref="A217:H217"/>
+    <mergeCell ref="A218:H218"/>
+    <mergeCell ref="A219:H219"/>
+    <mergeCell ref="A220:D220"/>
+    <mergeCell ref="A239:D239"/>
+    <mergeCell ref="A242:H242"/>
+    <mergeCell ref="A12:H12"/>
+    <mergeCell ref="A250:D250"/>
+    <mergeCell ref="A251:D251"/>
+    <mergeCell ref="A252:D252"/>
+    <mergeCell ref="A210:D210"/>
+    <mergeCell ref="A211:D211"/>
+    <mergeCell ref="A212:D212"/>
+    <mergeCell ref="A213:D213"/>
+    <mergeCell ref="A214:D214"/>
+    <mergeCell ref="A46:D46"/>
+    <mergeCell ref="A47:D47"/>
+    <mergeCell ref="A215:D215"/>
+    <mergeCell ref="A49:D49"/>
+    <mergeCell ref="A50:H50"/>
+    <mergeCell ref="A51:H51"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/PM_092.xlsx
+++ b/PM_092.xlsx
@@ -5,22 +5,22 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="Z:\TUAN HOC A.I\1. TCKT_PCVT\4. Công nghệ AI\KT SCL\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="Z:\Cty ĐL VungTau\1. TCKT_PCVT\4. Công nghệ AI\KT SCL\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED5E2A54-56B2-46BF-96EE-032D3107D2EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{E342D4AF-B82E-46B8-8191-F93D78A7C2A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{AC1AAD16-9061-42F9-B216-D7E5AB78D483}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{30992FE7-125A-4E5F-A1B9-33FAE73AF57A}"/>
   </bookViews>
   <sheets>
-    <sheet name="EVN_PM_092_________Sổ_chi_ti_03" sheetId="2" r:id="rId1"/>
+    <sheet name="EVN_PM_092_________Sổ_chi_ti_28" sheetId="2" r:id="rId1"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1061" uniqueCount="144">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1495" uniqueCount="174">
   <si>
     <t>TỔNG CÔNG TY ĐIỆN LỰC THÀNH PHỐ HỒ CHÍ MINH TNHH</t>
   </si>
@@ -43,7 +43,7 @@
     <t>Tài khoản: 2413 - Xây dựng cơ bản dở dang – Sửa chữa lớn TSCĐ</t>
   </si>
   <si>
-    <t>Từ ngày: 01-01-2026 đến ngày 30-04-2026</t>
+    <t>Từ ngày: 01-01-2026 đến ngày 28-05-2026</t>
   </si>
   <si>
     <t>Trạng thái: Tất cả</t>
@@ -111,7 +111,7 @@
     <t>VTAD2605001- Xuất Vtư cấp cho Cty Quang Vũ thi công Ctr SCL DD THT TBA 2026</t>
   </si>
   <si>
-    <t>Draft</t>
+    <t>Final</t>
   </si>
   <si>
     <t>THANH5DT.HCM.VTA</t>
@@ -145,6 +145,96 @@
     </r>
   </si>
   <si>
+    <r>
+      <t>'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>03.VH6.41.0013</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>03.VH6.41.0015</t>
+    </r>
+  </si>
+  <si>
+    <t>VTAD2605001-Xuất Vtư cấp cho Cty Quang Vũ thi công SCL:Ctr DD TBA 2026, theo VB 353/KTAT ngày 8.5.26</t>
+  </si>
+  <si>
+    <t>Draft</t>
+  </si>
+  <si>
+    <r>
+      <t>'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>03.VH6.41.0016</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>03.VH6.41.0017</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>03.VH6.41.0018</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>03.VH6.41.0019</t>
+    </r>
+  </si>
+  <si>
     <t>Cộng phát sinh</t>
   </si>
   <si>
@@ -195,9 +285,6 @@
     <t>VTAD2606001 Xuất SCL TU, TI trung hạ thế</t>
   </si>
   <si>
-    <t>Final</t>
-  </si>
-  <si>
     <r>
       <t>'</t>
     </r>
@@ -1028,6 +1115,187 @@
     </r>
   </si>
   <si>
+    <r>
+      <t>'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>03.VH4.41.0031</t>
+    </r>
+  </si>
+  <si>
+    <t>Xuất TI hạ thế SCL T5-2026</t>
+  </si>
+  <si>
+    <r>
+      <t>'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>03.VH4.41.0032</t>
+    </r>
+  </si>
+  <si>
+    <t>VTDA2606001 Xuất TI hạ thế SCL T5-2026</t>
+  </si>
+  <si>
+    <r>
+      <t>'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>03.VH4.41.0033</t>
+    </r>
+  </si>
+  <si>
+    <t>VTAD2606001 Xuất TU, TI  SCL tháng 5/2026</t>
+  </si>
+  <si>
+    <r>
+      <t>'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>03.VH4.41.0035</t>
+    </r>
+  </si>
+  <si>
+    <t>VTAD2606001 Xuất TU, TI thay SCL T5-2026</t>
+  </si>
+  <si>
+    <r>
+      <t>'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>01.VH4.12.0044</t>
+    </r>
+  </si>
+  <si>
+    <t>VTDA2606001 nhập thu hồi TU, TI Sửa chữa Lớn 2026</t>
+  </si>
+  <si>
+    <r>
+      <t>'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>01.VH8.12.0056</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>01.VH4.12.0045</t>
+    </r>
+  </si>
+  <si>
+    <t>VTAD2606001 Nhập thu hồi TU SCL T5-2026</t>
+  </si>
+  <si>
+    <r>
+      <t>'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>03.VH4.41.0036</t>
+    </r>
+  </si>
+  <si>
+    <t>VTAD2606001 Xuất TU thay SCL T5-2026</t>
+  </si>
+  <si>
+    <r>
+      <t>'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>03.VH4.41.0037</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>03.VH4.41.0038</t>
+    </r>
+  </si>
+  <si>
+    <t>VTAD2606001 Xuất TU SCL T5-2026</t>
+  </si>
+  <si>
+    <r>
+      <t>'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>03.VH4.41.0039</t>
+    </r>
+  </si>
+  <si>
+    <t>VTAD2606001 Xuất TU, TI SCL T5-2026</t>
+  </si>
+  <si>
     <t>Công trình: VTAD2606002 - SCL TSCĐ Thay thế LBFCO,FCO,LA ngăn ngừa sự cố 2026</t>
   </si>
   <si>
@@ -1078,8 +1346,28 @@
         <rFont val="Times New Roman"/>
         <family val="1"/>
       </rPr>
-      <t>03.VH6.41.0013</t>
-    </r>
+      <t>03.VH6.41.0014</t>
+    </r>
+  </si>
+  <si>
+    <t>VTAD2606002-Xuất Vtư phục vụ Ctr SCL FCO,LA 2026 cấp cho đội QLLĐ thi công ngày 08,09.6.26 theo TTr 297/KTAT, 23.04.26</t>
+  </si>
+  <si>
+    <r>
+      <t>'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>01.VH6.11.0002</t>
+    </r>
+  </si>
+  <si>
+    <t>VTAD2606002-Nhập Vtư trả lại kho VHJ (PX 02.VH6.41.0006/24.04.26; 07.VHJ.56.0001/24.04.26)</t>
   </si>
   <si>
     <t>TP. Hồ Chí Minh, Ngày …. tháng …. năm …..</t>
@@ -1097,7 +1385,7 @@
     <t>(Ký, họ tên, đóng dấu)</t>
   </si>
   <si>
-    <t>EVN_PM_092_TT200, người in: TUAN2HM.HCM.VTA, ngày in: 03/05/2026 19:20:41</t>
+    <t>EVN_PM_092_TT200, người in: TUAN2HM.HCM.VTA, ngày in: 28/05/2026 13:51:41</t>
   </si>
   <si>
     <t>Trang 1/1</t>
@@ -1753,53 +2041,6 @@
     <xf numFmtId="0" fontId="20" fillId="33" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="21" fillId="33" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="33" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="33" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="33" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="33" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="33" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="33" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="33" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="21" fillId="33" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="33" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="33" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="33" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="34" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="34" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="21" fillId="34" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
@@ -1812,6 +2053,53 @@
     <xf numFmtId="0" fontId="21" fillId="34" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="21" fillId="34" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="34" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="33" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="33" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="33" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="33" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="33" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="33" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="21" fillId="33" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="33" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="33" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="33" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="33" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="33" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -2186,8 +2474,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DC097D15-D4E4-46F1-B3C8-4A7361019462}">
-  <dimension ref="A1:H267"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CCA9FD56-726E-48EF-A90C-91BDA08946E1}">
+  <dimension ref="A1:H349"/>
   <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="35.19921875" bestFit="1" customWidth="1"/>
@@ -2233,7 +2521,7 @@
     <row r="7" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="1"/>
     </row>
-    <row r="8" spans="1:8" ht="29.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="4" t="s">
         <v>6</v>
       </c>
@@ -2249,54 +2537,54 @@
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A12" s="24" t="s">
+      <c r="A12" s="34" t="s">
         <v>9</v>
       </c>
-      <c r="B12" s="25"/>
-      <c r="C12" s="25"/>
-      <c r="D12" s="25"/>
-      <c r="E12" s="25"/>
-      <c r="F12" s="25"/>
-      <c r="G12" s="25"/>
-      <c r="H12" s="25"/>
+      <c r="B12" s="35"/>
+      <c r="C12" s="35"/>
+      <c r="D12" s="35"/>
+      <c r="E12" s="35"/>
+      <c r="F12" s="35"/>
+      <c r="G12" s="35"/>
+      <c r="H12" s="35"/>
     </row>
     <row r="13" spans="1:8" ht="30.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="32" t="s">
+      <c r="A13" s="15" t="s">
         <v>10</v>
       </c>
-      <c r="B13" s="32" t="s">
+      <c r="B13" s="15" t="s">
         <v>11</v>
       </c>
-      <c r="C13" s="32" t="s">
+      <c r="C13" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="D13" s="32" t="s">
+      <c r="D13" s="15" t="s">
         <v>13</v>
       </c>
-      <c r="E13" s="34" t="s">
+      <c r="E13" s="17" t="s">
         <v>14</v>
       </c>
-      <c r="F13" s="35"/>
-      <c r="G13" s="30" t="s">
+      <c r="F13" s="18"/>
+      <c r="G13" s="19" t="s">
         <v>15</v>
       </c>
-      <c r="H13" s="30" t="s">
+      <c r="H13" s="19" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="14" spans="1:8" ht="28.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="33"/>
-      <c r="B14" s="33"/>
-      <c r="C14" s="33"/>
-      <c r="D14" s="33"/>
+      <c r="A14" s="16"/>
+      <c r="B14" s="16"/>
+      <c r="C14" s="16"/>
+      <c r="D14" s="16"/>
       <c r="E14" s="5" t="s">
         <v>17</v>
       </c>
       <c r="F14" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="G14" s="31"/>
-      <c r="H14" s="31"/>
+      <c r="G14" s="20"/>
+      <c r="H14" s="20"/>
     </row>
     <row r="15" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="21" t="s">
@@ -2335,12 +2623,12 @@
       <c r="H17" s="23"/>
     </row>
     <row r="18" spans="1:8" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="26" t="s">
+      <c r="A18" s="24" t="s">
         <v>22</v>
       </c>
-      <c r="B18" s="27"/>
-      <c r="C18" s="27"/>
-      <c r="D18" s="28"/>
+      <c r="B18" s="25"/>
+      <c r="C18" s="25"/>
+      <c r="D18" s="26"/>
       <c r="E18" s="7"/>
       <c r="F18" s="7"/>
       <c r="G18" s="7"/>
@@ -2360,7 +2648,7 @@
         <v>25</v>
       </c>
       <c r="E19" s="12">
-        <v>16500000</v>
+        <v>3885000</v>
       </c>
       <c r="F19" s="8"/>
       <c r="G19" s="9" t="s">
@@ -2384,7 +2672,7 @@
         <v>25</v>
       </c>
       <c r="E20" s="12">
-        <v>2000000</v>
+        <v>1030000</v>
       </c>
       <c r="F20" s="8"/>
       <c r="G20" s="9" t="s">
@@ -2408,7 +2696,7 @@
         <v>25</v>
       </c>
       <c r="E21" s="12">
-        <v>3885000</v>
+        <v>4796000</v>
       </c>
       <c r="F21" s="8"/>
       <c r="G21" s="9" t="s">
@@ -2432,7 +2720,7 @@
         <v>25</v>
       </c>
       <c r="E22" s="12">
-        <v>2238435</v>
+        <v>46891</v>
       </c>
       <c r="F22" s="8"/>
       <c r="G22" s="9" t="s">
@@ -2456,7 +2744,7 @@
         <v>25</v>
       </c>
       <c r="E23" s="12">
-        <v>4796000</v>
+        <v>2000000</v>
       </c>
       <c r="F23" s="8"/>
       <c r="G23" s="9" t="s">
@@ -2480,7 +2768,7 @@
         <v>25</v>
       </c>
       <c r="E24" s="12">
-        <v>46891</v>
+        <v>16500000</v>
       </c>
       <c r="F24" s="8"/>
       <c r="G24" s="9" t="s">
@@ -2504,7 +2792,7 @@
         <v>25</v>
       </c>
       <c r="E25" s="12">
-        <v>1030000</v>
+        <v>2238435</v>
       </c>
       <c r="F25" s="8"/>
       <c r="G25" s="9" t="s">
@@ -2528,7 +2816,7 @@
         <v>25</v>
       </c>
       <c r="E26" s="12">
-        <v>3089430</v>
+        <v>68738</v>
       </c>
       <c r="F26" s="8"/>
       <c r="G26" s="9" t="s">
@@ -2552,7 +2840,7 @@
         <v>25</v>
       </c>
       <c r="E27" s="12">
-        <v>1369600</v>
+        <v>7913269</v>
       </c>
       <c r="F27" s="8"/>
       <c r="G27" s="9" t="s">
@@ -2576,7 +2864,7 @@
         <v>25</v>
       </c>
       <c r="E28" s="12">
-        <v>203993</v>
+        <v>3089430</v>
       </c>
       <c r="F28" s="8"/>
       <c r="G28" s="9" t="s">
@@ -2600,7 +2888,7 @@
         <v>25</v>
       </c>
       <c r="E29" s="12">
-        <v>68738</v>
+        <v>203993</v>
       </c>
       <c r="F29" s="8"/>
       <c r="G29" s="9" t="s">
@@ -2624,7 +2912,7 @@
         <v>25</v>
       </c>
       <c r="E30" s="12">
-        <v>2373531</v>
+        <v>1369600</v>
       </c>
       <c r="F30" s="8"/>
       <c r="G30" s="9" t="s">
@@ -2648,7 +2936,7 @@
         <v>25</v>
       </c>
       <c r="E31" s="12">
-        <v>23011765</v>
+        <v>144536</v>
       </c>
       <c r="F31" s="8"/>
       <c r="G31" s="9" t="s">
@@ -2672,7 +2960,7 @@
         <v>25</v>
       </c>
       <c r="E32" s="12">
-        <v>7913269</v>
+        <v>23011765</v>
       </c>
       <c r="F32" s="8"/>
       <c r="G32" s="9" t="s">
@@ -2696,7 +2984,7 @@
         <v>25</v>
       </c>
       <c r="E33" s="12">
-        <v>144536</v>
+        <v>2373531</v>
       </c>
       <c r="F33" s="8"/>
       <c r="G33" s="9" t="s">
@@ -2720,7 +3008,7 @@
         <v>25</v>
       </c>
       <c r="E34" s="12">
-        <v>831481</v>
+        <v>176400</v>
       </c>
       <c r="F34" s="8"/>
       <c r="G34" s="9" t="s">
@@ -2744,7 +3032,7 @@
         <v>25</v>
       </c>
       <c r="E35" s="12">
-        <v>17588974</v>
+        <v>498711</v>
       </c>
       <c r="F35" s="8"/>
       <c r="G35" s="9" t="s">
@@ -2768,7 +3056,7 @@
         <v>25</v>
       </c>
       <c r="E36" s="12">
-        <v>254478</v>
+        <v>5200000</v>
       </c>
       <c r="F36" s="8"/>
       <c r="G36" s="9" t="s">
@@ -2792,7 +3080,7 @@
         <v>25</v>
       </c>
       <c r="E37" s="12">
-        <v>637047</v>
+        <v>17588974</v>
       </c>
       <c r="F37" s="8"/>
       <c r="G37" s="9" t="s">
@@ -2840,7 +3128,7 @@
         <v>25</v>
       </c>
       <c r="E39" s="12">
-        <v>5200000</v>
+        <v>254478</v>
       </c>
       <c r="F39" s="8"/>
       <c r="G39" s="9" t="s">
@@ -2864,7 +3152,7 @@
         <v>25</v>
       </c>
       <c r="E40" s="12">
-        <v>176400</v>
+        <v>831481</v>
       </c>
       <c r="F40" s="8"/>
       <c r="G40" s="9" t="s">
@@ -2888,7 +3176,7 @@
         <v>25</v>
       </c>
       <c r="E41" s="12">
-        <v>498711</v>
+        <v>637047</v>
       </c>
       <c r="F41" s="8"/>
       <c r="G41" s="9" t="s">
@@ -2899,180 +3187,312 @@
       </c>
     </row>
     <row r="42" spans="1:8" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="26" t="s">
+      <c r="A42" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="B42" s="10">
+        <v>46141</v>
+      </c>
+      <c r="C42" s="11" t="s">
         <v>30</v>
       </c>
-      <c r="B42" s="27"/>
-      <c r="C42" s="27"/>
-      <c r="D42" s="28"/>
-      <c r="E42" s="13">
-        <v>103128028</v>
-      </c>
-      <c r="F42" s="7"/>
-      <c r="G42" s="7"/>
-      <c r="H42" s="7"/>
+      <c r="D42" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="E42" s="12">
+        <v>280600</v>
+      </c>
+      <c r="F42" s="8"/>
+      <c r="G42" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="H42" s="9" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="43" spans="1:8" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A43" s="26" t="s">
+      <c r="A43" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="B43" s="10">
+        <v>46141</v>
+      </c>
+      <c r="C43" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="D43" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="E43" s="12">
+        <v>5617204</v>
+      </c>
+      <c r="F43" s="8"/>
+      <c r="G43" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="H43" s="9" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A44" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="B44" s="10">
+        <v>46155</v>
+      </c>
+      <c r="C44" s="11" t="s">
         <v>31</v>
       </c>
-      <c r="B43" s="27"/>
-      <c r="C43" s="27"/>
-      <c r="D43" s="28"/>
-      <c r="E43" s="13">
-        <v>103128028</v>
-      </c>
-      <c r="F43" s="7"/>
-      <c r="G43" s="7"/>
-      <c r="H43" s="7"/>
-    </row>
-    <row r="44" spans="1:8" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A44" s="26" t="s">
+      <c r="D44" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="B44" s="27"/>
-      <c r="C44" s="27"/>
-      <c r="D44" s="28"/>
-      <c r="E44" s="7"/>
-      <c r="F44" s="7"/>
-      <c r="G44" s="7"/>
-      <c r="H44" s="7"/>
+      <c r="E44" s="12">
+        <v>4850000</v>
+      </c>
+      <c r="F44" s="8"/>
+      <c r="G44" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="H44" s="9" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="45" spans="1:8" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A45" s="26" t="s">
+      <c r="A45" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="B45" s="10">
+        <v>46155</v>
+      </c>
+      <c r="C45" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="D45" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="E45" s="12">
+        <v>13800000</v>
+      </c>
+      <c r="F45" s="8"/>
+      <c r="G45" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="B45" s="27"/>
-      <c r="C45" s="27"/>
-      <c r="D45" s="28"/>
-      <c r="E45" s="13">
-        <v>103128028</v>
-      </c>
-      <c r="F45" s="7"/>
-      <c r="G45" s="7"/>
-      <c r="H45" s="7"/>
+      <c r="H45" s="9" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="46" spans="1:8" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A46" s="26" t="s">
+      <c r="A46" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="B46" s="10">
+        <v>46155</v>
+      </c>
+      <c r="C46" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="D46" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="E46" s="12">
+        <v>4365600</v>
+      </c>
+      <c r="F46" s="8"/>
+      <c r="G46" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="H46" s="9" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A47" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="B47" s="10">
+        <v>46155</v>
+      </c>
+      <c r="C47" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="D47" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="E47" s="12">
+        <v>24148825</v>
+      </c>
+      <c r="F47" s="8"/>
+      <c r="G47" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="H47" s="9" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A48" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="B48" s="10">
+        <v>46155</v>
+      </c>
+      <c r="C48" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="D48" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="E48" s="12">
+        <v>5617204</v>
+      </c>
+      <c r="F48" s="8"/>
+      <c r="G48" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="H48" s="9" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A49" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="B49" s="10">
+        <v>46155</v>
+      </c>
+      <c r="C49" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="D49" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="E49" s="12">
+        <v>16500000</v>
+      </c>
+      <c r="F49" s="8"/>
+      <c r="G49" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="H49" s="9" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A50" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="B50" s="10">
+        <v>46155</v>
+      </c>
+      <c r="C50" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="D50" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="E50" s="12">
+        <v>1533983</v>
+      </c>
+      <c r="F50" s="8"/>
+      <c r="G50" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="H50" s="9" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A51" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="B51" s="10">
+        <v>46155</v>
+      </c>
+      <c r="C51" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="D51" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="E51" s="12">
+        <v>6500000</v>
+      </c>
+      <c r="F51" s="8"/>
+      <c r="G51" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="H51" s="9" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A52" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="B52" s="10">
+        <v>46155</v>
+      </c>
+      <c r="C52" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="B46" s="27"/>
-      <c r="C46" s="27"/>
-      <c r="D46" s="28"/>
-      <c r="E46" s="13">
-        <v>103128028</v>
-      </c>
-      <c r="F46" s="7"/>
-      <c r="G46" s="7"/>
-      <c r="H46" s="7"/>
-    </row>
-    <row r="47" spans="1:8" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A47" s="26" t="s">
-        <v>35</v>
-      </c>
-      <c r="B47" s="27"/>
-      <c r="C47" s="27"/>
-      <c r="D47" s="28"/>
-      <c r="E47" s="7"/>
-      <c r="F47" s="7"/>
-      <c r="G47" s="7"/>
-      <c r="H47" s="7"/>
-    </row>
-    <row r="48" spans="1:8" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A48" s="26" t="s">
-        <v>36</v>
-      </c>
-      <c r="B48" s="27"/>
-      <c r="C48" s="27"/>
-      <c r="D48" s="28"/>
-      <c r="E48" s="13">
-        <v>103128028</v>
-      </c>
-      <c r="F48" s="7"/>
-      <c r="G48" s="7"/>
-      <c r="H48" s="7"/>
-    </row>
-    <row r="49" spans="1:8" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A49" s="26" t="s">
-        <v>37</v>
-      </c>
-      <c r="B49" s="27"/>
-      <c r="C49" s="27"/>
-      <c r="D49" s="28"/>
-      <c r="E49" s="13">
-        <v>103128028</v>
-      </c>
-      <c r="F49" s="7"/>
-      <c r="G49" s="7"/>
-      <c r="H49" s="7"/>
-    </row>
-    <row r="50" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A50" s="21" t="s">
-        <v>38</v>
-      </c>
-      <c r="B50" s="22"/>
-      <c r="C50" s="22"/>
-      <c r="D50" s="22"/>
-      <c r="E50" s="22"/>
-      <c r="F50" s="22"/>
-      <c r="G50" s="22"/>
-      <c r="H50" s="23"/>
-    </row>
-    <row r="51" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A51" s="21" t="s">
-        <v>39</v>
-      </c>
-      <c r="B51" s="22"/>
-      <c r="C51" s="22"/>
-      <c r="D51" s="22"/>
-      <c r="E51" s="22"/>
-      <c r="F51" s="22"/>
-      <c r="G51" s="22"/>
-      <c r="H51" s="23"/>
-    </row>
-    <row r="52" spans="1:8" ht="18.149999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A52" s="21" t="s">
-        <v>40</v>
-      </c>
-      <c r="B52" s="22"/>
-      <c r="C52" s="22"/>
-      <c r="D52" s="22"/>
-      <c r="E52" s="22"/>
-      <c r="F52" s="22"/>
-      <c r="G52" s="22"/>
-      <c r="H52" s="23"/>
+      <c r="D52" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="E52" s="12">
+        <v>6179833</v>
+      </c>
+      <c r="F52" s="8"/>
+      <c r="G52" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="H52" s="9" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="53" spans="1:8" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A53" s="26" t="s">
-        <v>22</v>
-      </c>
-      <c r="B53" s="27"/>
-      <c r="C53" s="27"/>
-      <c r="D53" s="28"/>
-      <c r="E53" s="7"/>
-      <c r="F53" s="7"/>
-      <c r="G53" s="7"/>
-      <c r="H53" s="7"/>
+      <c r="A53" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="B53" s="10">
+        <v>46155</v>
+      </c>
+      <c r="C53" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="D53" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="E53" s="12">
+        <v>1620000</v>
+      </c>
+      <c r="F53" s="8"/>
+      <c r="G53" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="H53" s="9" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="54" spans="1:8" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A54" s="9" t="s">
         <v>23</v>
       </c>
       <c r="B54" s="10">
-        <v>46049</v>
+        <v>46155</v>
       </c>
       <c r="C54" s="11" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="D54" s="9" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="E54" s="12">
-        <v>25078749</v>
+        <v>332833</v>
       </c>
       <c r="F54" s="8"/>
       <c r="G54" s="9" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="H54" s="9" t="s">
         <v>27</v>
@@ -3083,20 +3503,20 @@
         <v>23</v>
       </c>
       <c r="B55" s="10">
-        <v>46049</v>
+        <v>46155</v>
       </c>
       <c r="C55" s="11" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="D55" s="9" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="E55" s="12">
-        <v>1661736</v>
+        <v>7007519</v>
       </c>
       <c r="F55" s="8"/>
       <c r="G55" s="9" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="H55" s="9" t="s">
         <v>27</v>
@@ -3107,20 +3527,20 @@
         <v>23</v>
       </c>
       <c r="B56" s="10">
-        <v>46049</v>
+        <v>46155</v>
       </c>
       <c r="C56" s="11" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="D56" s="9" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="E56" s="12">
-        <v>226782</v>
+        <v>144536</v>
       </c>
       <c r="F56" s="8"/>
       <c r="G56" s="9" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="H56" s="9" t="s">
         <v>27</v>
@@ -3131,20 +3551,20 @@
         <v>23</v>
       </c>
       <c r="B57" s="10">
-        <v>46050</v>
+        <v>46155</v>
       </c>
       <c r="C57" s="11" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="D57" s="9" t="s">
-        <v>45</v>
+        <v>32</v>
       </c>
       <c r="E57" s="12">
-        <v>752742</v>
+        <v>112500</v>
       </c>
       <c r="F57" s="8"/>
       <c r="G57" s="9" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="H57" s="9" t="s">
         <v>27</v>
@@ -3155,20 +3575,20 @@
         <v>23</v>
       </c>
       <c r="B58" s="10">
-        <v>46050</v>
+        <v>46155</v>
       </c>
       <c r="C58" s="11" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="D58" s="9" t="s">
-        <v>45</v>
+        <v>32</v>
       </c>
       <c r="E58" s="12">
-        <v>1522307</v>
+        <v>1994844</v>
       </c>
       <c r="F58" s="8"/>
       <c r="G58" s="9" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="H58" s="9" t="s">
         <v>27</v>
@@ -3179,20 +3599,20 @@
         <v>23</v>
       </c>
       <c r="B59" s="10">
-        <v>46050</v>
+        <v>46155</v>
       </c>
       <c r="C59" s="11" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="D59" s="9" t="s">
-        <v>45</v>
+        <v>32</v>
       </c>
       <c r="E59" s="12">
-        <v>3363677</v>
+        <v>69035294</v>
       </c>
       <c r="F59" s="8"/>
       <c r="G59" s="9" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="H59" s="9" t="s">
         <v>27</v>
@@ -3203,20 +3623,20 @@
         <v>23</v>
       </c>
       <c r="B60" s="10">
-        <v>46050</v>
+        <v>46155</v>
       </c>
       <c r="C60" s="11" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="D60" s="9" t="s">
-        <v>45</v>
+        <v>32</v>
       </c>
       <c r="E60" s="12">
-        <v>2602365</v>
+        <v>468000</v>
       </c>
       <c r="F60" s="8"/>
       <c r="G60" s="9" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="H60" s="9" t="s">
         <v>27</v>
@@ -3227,20 +3647,20 @@
         <v>23</v>
       </c>
       <c r="B61" s="10">
-        <v>46050</v>
+        <v>46155</v>
       </c>
       <c r="C61" s="11" t="s">
-        <v>44</v>
+        <v>35</v>
       </c>
       <c r="D61" s="9" t="s">
-        <v>45</v>
+        <v>32</v>
       </c>
       <c r="E61" s="12">
-        <v>9373531</v>
+        <v>617400</v>
       </c>
       <c r="F61" s="8"/>
       <c r="G61" s="9" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="H61" s="9" t="s">
         <v>27</v>
@@ -3251,20 +3671,20 @@
         <v>23</v>
       </c>
       <c r="B62" s="10">
-        <v>46050</v>
+        <v>46155</v>
       </c>
       <c r="C62" s="11" t="s">
-        <v>44</v>
+        <v>35</v>
       </c>
       <c r="D62" s="9" t="s">
-        <v>45</v>
+        <v>32</v>
       </c>
       <c r="E62" s="12">
-        <v>1308084</v>
+        <v>2974800</v>
       </c>
       <c r="F62" s="8"/>
       <c r="G62" s="9" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="H62" s="9" t="s">
         <v>27</v>
@@ -3275,20 +3695,20 @@
         <v>23</v>
       </c>
       <c r="B63" s="10">
-        <v>46050</v>
+        <v>46155</v>
       </c>
       <c r="C63" s="11" t="s">
-        <v>44</v>
+        <v>35</v>
       </c>
       <c r="D63" s="9" t="s">
-        <v>45</v>
+        <v>32</v>
       </c>
       <c r="E63" s="12">
-        <v>1203636</v>
+        <v>550617</v>
       </c>
       <c r="F63" s="8"/>
       <c r="G63" s="9" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="H63" s="9" t="s">
         <v>27</v>
@@ -3299,20 +3719,20 @@
         <v>23</v>
       </c>
       <c r="B64" s="10">
-        <v>46050</v>
+        <v>46155</v>
       </c>
       <c r="C64" s="11" t="s">
-        <v>44</v>
+        <v>35</v>
       </c>
       <c r="D64" s="9" t="s">
-        <v>45</v>
+        <v>32</v>
       </c>
       <c r="E64" s="12">
-        <v>226782</v>
+        <v>511593</v>
       </c>
       <c r="F64" s="8"/>
       <c r="G64" s="9" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="H64" s="9" t="s">
         <v>27</v>
@@ -3323,20 +3743,20 @@
         <v>23</v>
       </c>
       <c r="B65" s="10">
-        <v>46050</v>
+        <v>46155</v>
       </c>
       <c r="C65" s="11" t="s">
-        <v>44</v>
+        <v>35</v>
       </c>
       <c r="D65" s="9" t="s">
-        <v>45</v>
+        <v>32</v>
       </c>
       <c r="E65" s="12">
-        <v>1458662</v>
+        <v>1526869</v>
       </c>
       <c r="F65" s="8"/>
       <c r="G65" s="9" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="H65" s="9" t="s">
         <v>27</v>
@@ -3347,20 +3767,20 @@
         <v>23</v>
       </c>
       <c r="B66" s="10">
-        <v>46052</v>
+        <v>46155</v>
       </c>
       <c r="C66" s="11" t="s">
-        <v>46</v>
+        <v>35</v>
       </c>
       <c r="D66" s="9" t="s">
-        <v>45</v>
+        <v>32</v>
       </c>
       <c r="E66" s="12">
-        <v>1203636</v>
+        <v>2046554</v>
       </c>
       <c r="F66" s="8"/>
       <c r="G66" s="9" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="H66" s="9" t="s">
         <v>27</v>
@@ -3371,20 +3791,20 @@
         <v>23</v>
       </c>
       <c r="B67" s="10">
-        <v>46055</v>
+        <v>46155</v>
       </c>
       <c r="C67" s="11" t="s">
-        <v>47</v>
+        <v>35</v>
       </c>
       <c r="D67" s="9" t="s">
-        <v>48</v>
+        <v>32</v>
       </c>
       <c r="E67" s="12">
-        <v>4837767</v>
+        <v>509543</v>
       </c>
       <c r="F67" s="8"/>
       <c r="G67" s="9" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="H67" s="9" t="s">
         <v>27</v>
@@ -3395,20 +3815,20 @@
         <v>23</v>
       </c>
       <c r="B68" s="10">
-        <v>46055</v>
+        <v>46155</v>
       </c>
       <c r="C68" s="11" t="s">
-        <v>47</v>
+        <v>35</v>
       </c>
       <c r="D68" s="9" t="s">
-        <v>48</v>
+        <v>32</v>
       </c>
       <c r="E68" s="12">
-        <v>29678743</v>
+        <v>3875416</v>
       </c>
       <c r="F68" s="8"/>
       <c r="G68" s="9" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="H68" s="9" t="s">
         <v>27</v>
@@ -3419,20 +3839,20 @@
         <v>23</v>
       </c>
       <c r="B69" s="10">
-        <v>46055</v>
+        <v>46155</v>
       </c>
       <c r="C69" s="11" t="s">
-        <v>47</v>
+        <v>35</v>
       </c>
       <c r="D69" s="9" t="s">
-        <v>48</v>
+        <v>32</v>
       </c>
       <c r="E69" s="12">
-        <v>46268766</v>
+        <v>62817764</v>
       </c>
       <c r="F69" s="8"/>
       <c r="G69" s="9" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="H69" s="9" t="s">
         <v>27</v>
@@ -3443,20 +3863,20 @@
         <v>23</v>
       </c>
       <c r="B70" s="10">
-        <v>46055</v>
+        <v>46155</v>
       </c>
       <c r="C70" s="11" t="s">
-        <v>47</v>
+        <v>35</v>
       </c>
       <c r="D70" s="9" t="s">
-        <v>48</v>
+        <v>32</v>
       </c>
       <c r="E70" s="12">
-        <v>452700000</v>
+        <v>45000</v>
       </c>
       <c r="F70" s="8"/>
       <c r="G70" s="9" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="H70" s="9" t="s">
         <v>27</v>
@@ -3467,20 +3887,20 @@
         <v>23</v>
       </c>
       <c r="B71" s="10">
-        <v>46055</v>
+        <v>46155</v>
       </c>
       <c r="C71" s="11" t="s">
-        <v>47</v>
+        <v>36</v>
       </c>
       <c r="D71" s="9" t="s">
-        <v>48</v>
+        <v>32</v>
       </c>
       <c r="E71" s="12">
-        <v>24302032</v>
+        <v>514903</v>
       </c>
       <c r="F71" s="8"/>
       <c r="G71" s="9" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="H71" s="9" t="s">
         <v>27</v>
@@ -3491,20 +3911,20 @@
         <v>23</v>
       </c>
       <c r="B72" s="10">
-        <v>46055</v>
+        <v>46155</v>
       </c>
       <c r="C72" s="11" t="s">
-        <v>47</v>
+        <v>36</v>
       </c>
       <c r="D72" s="9" t="s">
-        <v>48</v>
+        <v>32</v>
       </c>
       <c r="E72" s="12">
-        <v>58071188</v>
+        <v>12694203</v>
       </c>
       <c r="F72" s="8"/>
       <c r="G72" s="9" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="H72" s="9" t="s">
         <v>27</v>
@@ -3515,20 +3935,20 @@
         <v>23</v>
       </c>
       <c r="B73" s="10">
-        <v>46055</v>
+        <v>46155</v>
       </c>
       <c r="C73" s="11" t="s">
-        <v>49</v>
+        <v>36</v>
       </c>
       <c r="D73" s="9" t="s">
-        <v>48</v>
-      </c>
-      <c r="E73" s="14">
-        <v>3</v>
+        <v>32</v>
+      </c>
+      <c r="E73" s="12">
+        <v>17276200</v>
       </c>
       <c r="F73" s="8"/>
       <c r="G73" s="9" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="H73" s="9" t="s">
         <v>27</v>
@@ -3539,20 +3959,20 @@
         <v>23</v>
       </c>
       <c r="B74" s="10">
-        <v>46055</v>
+        <v>46162</v>
       </c>
       <c r="C74" s="11" t="s">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="D74" s="9" t="s">
-        <v>48</v>
+        <v>32</v>
       </c>
       <c r="E74" s="12">
-        <v>29935698</v>
+        <v>5505600</v>
       </c>
       <c r="F74" s="8"/>
       <c r="G74" s="9" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="H74" s="9" t="s">
         <v>27</v>
@@ -3563,20 +3983,20 @@
         <v>23</v>
       </c>
       <c r="B75" s="10">
-        <v>46055</v>
+        <v>46162</v>
       </c>
       <c r="C75" s="11" t="s">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="D75" s="9" t="s">
-        <v>48</v>
-      </c>
-      <c r="E75" s="14">
-        <v>3</v>
+        <v>32</v>
+      </c>
+      <c r="E75" s="12">
+        <v>9160000</v>
       </c>
       <c r="F75" s="8"/>
       <c r="G75" s="9" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="H75" s="9" t="s">
         <v>27</v>
@@ -3587,332 +4007,200 @@
         <v>23</v>
       </c>
       <c r="B76" s="10">
-        <v>46057</v>
+        <v>46162</v>
       </c>
       <c r="C76" s="11" t="s">
-        <v>50</v>
+        <v>37</v>
       </c>
       <c r="D76" s="9" t="s">
-        <v>51</v>
+        <v>32</v>
       </c>
       <c r="E76" s="12">
-        <v>784850</v>
+        <v>4787165</v>
       </c>
       <c r="F76" s="8"/>
       <c r="G76" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="H76" s="9" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="77" spans="1:8" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A77" s="24" t="s">
+        <v>38</v>
+      </c>
+      <c r="B77" s="25"/>
+      <c r="C77" s="25"/>
+      <c r="D77" s="26"/>
+      <c r="E77" s="13">
+        <v>398650430</v>
+      </c>
+      <c r="F77" s="7"/>
+      <c r="G77" s="7"/>
+      <c r="H77" s="7"/>
+    </row>
+    <row r="78" spans="1:8" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A78" s="24" t="s">
+        <v>39</v>
+      </c>
+      <c r="B78" s="25"/>
+      <c r="C78" s="25"/>
+      <c r="D78" s="26"/>
+      <c r="E78" s="13">
+        <v>398650430</v>
+      </c>
+      <c r="F78" s="7"/>
+      <c r="G78" s="7"/>
+      <c r="H78" s="7"/>
+    </row>
+    <row r="79" spans="1:8" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A79" s="24" t="s">
+        <v>40</v>
+      </c>
+      <c r="B79" s="25"/>
+      <c r="C79" s="25"/>
+      <c r="D79" s="26"/>
+      <c r="E79" s="7"/>
+      <c r="F79" s="7"/>
+      <c r="G79" s="7"/>
+      <c r="H79" s="7"/>
+    </row>
+    <row r="80" spans="1:8" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A80" s="24" t="s">
+        <v>41</v>
+      </c>
+      <c r="B80" s="25"/>
+      <c r="C80" s="25"/>
+      <c r="D80" s="26"/>
+      <c r="E80" s="13">
+        <v>398650430</v>
+      </c>
+      <c r="F80" s="7"/>
+      <c r="G80" s="7"/>
+      <c r="H80" s="7"/>
+    </row>
+    <row r="81" spans="1:8" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A81" s="24" t="s">
+        <v>42</v>
+      </c>
+      <c r="B81" s="25"/>
+      <c r="C81" s="25"/>
+      <c r="D81" s="26"/>
+      <c r="E81" s="13">
+        <v>398650430</v>
+      </c>
+      <c r="F81" s="7"/>
+      <c r="G81" s="7"/>
+      <c r="H81" s="7"/>
+    </row>
+    <row r="82" spans="1:8" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A82" s="24" t="s">
         <v>43</v>
       </c>
-      <c r="H76" s="9" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="77" spans="1:8" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A77" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="B77" s="10">
-        <v>46057</v>
-      </c>
-      <c r="C77" s="11" t="s">
-        <v>50</v>
-      </c>
-      <c r="D77" s="9" t="s">
-        <v>51</v>
-      </c>
-      <c r="E77" s="12">
-        <v>982851</v>
-      </c>
-      <c r="F77" s="8"/>
-      <c r="G77" s="9" t="s">
-        <v>43</v>
-      </c>
-      <c r="H77" s="9" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="78" spans="1:8" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A78" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="B78" s="10">
-        <v>46057</v>
-      </c>
-      <c r="C78" s="11" t="s">
-        <v>50</v>
-      </c>
-      <c r="D78" s="9" t="s">
-        <v>51</v>
-      </c>
-      <c r="E78" s="12">
-        <v>1458662</v>
-      </c>
-      <c r="F78" s="8"/>
-      <c r="G78" s="9" t="s">
-        <v>43</v>
-      </c>
-      <c r="H78" s="9" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="79" spans="1:8" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A79" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="B79" s="10">
-        <v>46057</v>
-      </c>
-      <c r="C79" s="11" t="s">
-        <v>50</v>
-      </c>
-      <c r="D79" s="9" t="s">
-        <v>51</v>
-      </c>
-      <c r="E79" s="12">
-        <v>302400</v>
-      </c>
-      <c r="F79" s="8"/>
-      <c r="G79" s="9" t="s">
-        <v>43</v>
-      </c>
-      <c r="H79" s="9" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="80" spans="1:8" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A80" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="B80" s="10">
-        <v>46057</v>
-      </c>
-      <c r="C80" s="11" t="s">
-        <v>50</v>
-      </c>
-      <c r="D80" s="9" t="s">
-        <v>51</v>
-      </c>
-      <c r="E80" s="12">
-        <v>120720000</v>
-      </c>
-      <c r="F80" s="8"/>
-      <c r="G80" s="9" t="s">
-        <v>43</v>
-      </c>
-      <c r="H80" s="9" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="81" spans="1:8" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A81" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="B81" s="10">
-        <v>46057</v>
-      </c>
-      <c r="C81" s="11" t="s">
-        <v>50</v>
-      </c>
-      <c r="D81" s="9" t="s">
-        <v>51</v>
-      </c>
-      <c r="E81" s="12">
-        <v>327286</v>
-      </c>
-      <c r="F81" s="8"/>
-      <c r="G81" s="9" t="s">
-        <v>43</v>
-      </c>
-      <c r="H81" s="9" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="82" spans="1:8" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A82" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="B82" s="10">
-        <v>46057</v>
-      </c>
-      <c r="C82" s="11" t="s">
-        <v>50</v>
-      </c>
-      <c r="D82" s="9" t="s">
-        <v>51</v>
-      </c>
-      <c r="E82" s="12">
-        <v>24302033</v>
-      </c>
-      <c r="F82" s="8"/>
-      <c r="G82" s="9" t="s">
-        <v>43</v>
-      </c>
-      <c r="H82" s="9" t="s">
-        <v>27</v>
-      </c>
+      <c r="B82" s="25"/>
+      <c r="C82" s="25"/>
+      <c r="D82" s="26"/>
+      <c r="E82" s="7"/>
+      <c r="F82" s="7"/>
+      <c r="G82" s="7"/>
+      <c r="H82" s="7"/>
     </row>
     <row r="83" spans="1:8" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A83" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="B83" s="10">
-        <v>46057</v>
-      </c>
-      <c r="C83" s="11" t="s">
-        <v>50</v>
-      </c>
-      <c r="D83" s="9" t="s">
-        <v>51</v>
-      </c>
-      <c r="E83" s="12">
-        <v>1911211</v>
-      </c>
-      <c r="F83" s="8"/>
-      <c r="G83" s="9" t="s">
-        <v>43</v>
-      </c>
-      <c r="H83" s="9" t="s">
-        <v>27</v>
-      </c>
+      <c r="A83" s="24" t="s">
+        <v>44</v>
+      </c>
+      <c r="B83" s="25"/>
+      <c r="C83" s="25"/>
+      <c r="D83" s="26"/>
+      <c r="E83" s="13">
+        <v>398650430</v>
+      </c>
+      <c r="F83" s="7"/>
+      <c r="G83" s="7"/>
+      <c r="H83" s="7"/>
     </row>
     <row r="84" spans="1:8" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A84" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="B84" s="10">
-        <v>46057</v>
-      </c>
-      <c r="C84" s="11" t="s">
-        <v>52</v>
-      </c>
-      <c r="D84" s="9" t="s">
-        <v>53</v>
-      </c>
-      <c r="E84" s="12">
-        <v>982850</v>
-      </c>
-      <c r="F84" s="8"/>
-      <c r="G84" s="9" t="s">
-        <v>43</v>
-      </c>
-      <c r="H84" s="9" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="85" spans="1:8" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A85" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="B85" s="10">
-        <v>46057</v>
-      </c>
-      <c r="C85" s="11" t="s">
-        <v>52</v>
-      </c>
-      <c r="D85" s="9" t="s">
-        <v>53</v>
-      </c>
-      <c r="E85" s="12">
-        <v>1203636</v>
-      </c>
-      <c r="F85" s="8"/>
-      <c r="G85" s="9" t="s">
-        <v>43</v>
-      </c>
-      <c r="H85" s="9" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="86" spans="1:8" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A86" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="B86" s="10">
-        <v>46057</v>
-      </c>
-      <c r="C86" s="11" t="s">
-        <v>52</v>
-      </c>
-      <c r="D86" s="9" t="s">
-        <v>53</v>
-      </c>
-      <c r="E86" s="12">
-        <v>1569701</v>
-      </c>
-      <c r="F86" s="8"/>
-      <c r="G86" s="9" t="s">
-        <v>43</v>
-      </c>
-      <c r="H86" s="9" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="87" spans="1:8" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A87" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="B87" s="10">
-        <v>46057</v>
-      </c>
-      <c r="C87" s="11" t="s">
-        <v>52</v>
-      </c>
-      <c r="D87" s="9" t="s">
-        <v>53</v>
-      </c>
-      <c r="E87" s="12">
-        <v>4233600</v>
-      </c>
-      <c r="F87" s="8"/>
-      <c r="G87" s="9" t="s">
-        <v>43</v>
-      </c>
-      <c r="H87" s="9" t="s">
-        <v>27</v>
-      </c>
+      <c r="A84" s="24" t="s">
+        <v>45</v>
+      </c>
+      <c r="B84" s="25"/>
+      <c r="C84" s="25"/>
+      <c r="D84" s="26"/>
+      <c r="E84" s="13">
+        <v>398650430</v>
+      </c>
+      <c r="F84" s="7"/>
+      <c r="G84" s="7"/>
+      <c r="H84" s="7"/>
+    </row>
+    <row r="85" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A85" s="21" t="s">
+        <v>46</v>
+      </c>
+      <c r="B85" s="22"/>
+      <c r="C85" s="22"/>
+      <c r="D85" s="22"/>
+      <c r="E85" s="22"/>
+      <c r="F85" s="22"/>
+      <c r="G85" s="22"/>
+      <c r="H85" s="23"/>
+    </row>
+    <row r="86" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A86" s="21" t="s">
+        <v>47</v>
+      </c>
+      <c r="B86" s="22"/>
+      <c r="C86" s="22"/>
+      <c r="D86" s="22"/>
+      <c r="E86" s="22"/>
+      <c r="F86" s="22"/>
+      <c r="G86" s="22"/>
+      <c r="H86" s="23"/>
+    </row>
+    <row r="87" spans="1:8" ht="18.149999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A87" s="21" t="s">
+        <v>48</v>
+      </c>
+      <c r="B87" s="22"/>
+      <c r="C87" s="22"/>
+      <c r="D87" s="22"/>
+      <c r="E87" s="22"/>
+      <c r="F87" s="22"/>
+      <c r="G87" s="22"/>
+      <c r="H87" s="23"/>
     </row>
     <row r="88" spans="1:8" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A88" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="B88" s="10">
-        <v>46057</v>
-      </c>
-      <c r="C88" s="11" t="s">
-        <v>52</v>
-      </c>
-      <c r="D88" s="9" t="s">
-        <v>53</v>
-      </c>
-      <c r="E88" s="12">
-        <v>1458662</v>
-      </c>
-      <c r="F88" s="8"/>
-      <c r="G88" s="9" t="s">
-        <v>43</v>
-      </c>
-      <c r="H88" s="9" t="s">
-        <v>27</v>
-      </c>
+      <c r="A88" s="24" t="s">
+        <v>22</v>
+      </c>
+      <c r="B88" s="25"/>
+      <c r="C88" s="25"/>
+      <c r="D88" s="26"/>
+      <c r="E88" s="7"/>
+      <c r="F88" s="7"/>
+      <c r="G88" s="7"/>
+      <c r="H88" s="7"/>
     </row>
     <row r="89" spans="1:8" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A89" s="9" t="s">
         <v>23</v>
       </c>
       <c r="B89" s="10">
-        <v>46057</v>
+        <v>46049</v>
       </c>
       <c r="C89" s="11" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="D89" s="9" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="E89" s="12">
-        <v>1309143</v>
+        <v>226782</v>
       </c>
       <c r="F89" s="8"/>
       <c r="G89" s="9" t="s">
-        <v>43</v>
+        <v>26</v>
       </c>
       <c r="H89" s="9" t="s">
         <v>27</v>
@@ -3923,20 +4211,20 @@
         <v>23</v>
       </c>
       <c r="B90" s="10">
-        <v>46057</v>
+        <v>46049</v>
       </c>
       <c r="C90" s="11" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="D90" s="9" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="E90" s="12">
-        <v>955606</v>
+        <v>25078749</v>
       </c>
       <c r="F90" s="8"/>
       <c r="G90" s="9" t="s">
-        <v>43</v>
+        <v>26</v>
       </c>
       <c r="H90" s="9" t="s">
         <v>27</v>
@@ -3947,20 +4235,20 @@
         <v>23</v>
       </c>
       <c r="B91" s="10">
-        <v>46057</v>
+        <v>46049</v>
       </c>
       <c r="C91" s="11" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="D91" s="9" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="E91" s="12">
-        <v>84257</v>
+        <v>1661736</v>
       </c>
       <c r="F91" s="8"/>
       <c r="G91" s="9" t="s">
-        <v>43</v>
+        <v>26</v>
       </c>
       <c r="H91" s="9" t="s">
         <v>27</v>
@@ -3971,20 +4259,20 @@
         <v>23</v>
       </c>
       <c r="B92" s="10">
-        <v>46058</v>
+        <v>46050</v>
       </c>
       <c r="C92" s="11" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="D92" s="9" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="E92" s="12">
-        <v>471581</v>
+        <v>1458662</v>
       </c>
       <c r="F92" s="8"/>
       <c r="G92" s="9" t="s">
-        <v>43</v>
+        <v>26</v>
       </c>
       <c r="H92" s="9" t="s">
         <v>27</v>
@@ -3995,20 +4283,20 @@
         <v>23</v>
       </c>
       <c r="B93" s="10">
-        <v>46060</v>
+        <v>46050</v>
       </c>
       <c r="C93" s="11" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="D93" s="9" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="E93" s="12">
-        <v>10286294</v>
+        <v>1522307</v>
       </c>
       <c r="F93" s="8"/>
       <c r="G93" s="9" t="s">
-        <v>43</v>
+        <v>26</v>
       </c>
       <c r="H93" s="9" t="s">
         <v>27</v>
@@ -4019,20 +4307,20 @@
         <v>23</v>
       </c>
       <c r="B94" s="10">
-        <v>46062</v>
+        <v>46050</v>
       </c>
       <c r="C94" s="11" t="s">
-        <v>59</v>
+        <v>51</v>
       </c>
       <c r="D94" s="9" t="s">
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="E94" s="12">
-        <v>1569701</v>
+        <v>1203636</v>
       </c>
       <c r="F94" s="8"/>
       <c r="G94" s="9" t="s">
-        <v>43</v>
+        <v>26</v>
       </c>
       <c r="H94" s="9" t="s">
         <v>27</v>
@@ -4043,20 +4331,20 @@
         <v>23</v>
       </c>
       <c r="B95" s="10">
-        <v>46062</v>
+        <v>46050</v>
       </c>
       <c r="C95" s="11" t="s">
-        <v>59</v>
+        <v>51</v>
       </c>
       <c r="D95" s="9" t="s">
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="E95" s="12">
-        <v>955605</v>
+        <v>1308084</v>
       </c>
       <c r="F95" s="8"/>
       <c r="G95" s="9" t="s">
-        <v>43</v>
+        <v>26</v>
       </c>
       <c r="H95" s="9" t="s">
         <v>27</v>
@@ -4067,20 +4355,20 @@
         <v>23</v>
       </c>
       <c r="B96" s="10">
-        <v>46063</v>
+        <v>46050</v>
       </c>
       <c r="C96" s="11" t="s">
-        <v>61</v>
+        <v>51</v>
       </c>
       <c r="D96" s="9" t="s">
-        <v>62</v>
-      </c>
-      <c r="E96" s="8"/>
-      <c r="F96" s="12">
-        <v>29678743</v>
-      </c>
+        <v>52</v>
+      </c>
+      <c r="E96" s="12">
+        <v>752742</v>
+      </c>
+      <c r="F96" s="8"/>
       <c r="G96" s="9" t="s">
-        <v>43</v>
+        <v>26</v>
       </c>
       <c r="H96" s="9" t="s">
         <v>27</v>
@@ -4091,20 +4379,20 @@
         <v>23</v>
       </c>
       <c r="B97" s="10">
-        <v>46065</v>
+        <v>46050</v>
       </c>
       <c r="C97" s="11" t="s">
-        <v>63</v>
+        <v>51</v>
       </c>
       <c r="D97" s="9" t="s">
-        <v>64</v>
+        <v>52</v>
       </c>
       <c r="E97" s="12">
-        <v>26240898</v>
+        <v>3363677</v>
       </c>
       <c r="F97" s="8"/>
       <c r="G97" s="9" t="s">
-        <v>43</v>
+        <v>26</v>
       </c>
       <c r="H97" s="9" t="s">
         <v>27</v>
@@ -4115,20 +4403,20 @@
         <v>23</v>
       </c>
       <c r="B98" s="10">
-        <v>46065</v>
+        <v>46050</v>
       </c>
       <c r="C98" s="11" t="s">
-        <v>63</v>
+        <v>51</v>
       </c>
       <c r="D98" s="9" t="s">
-        <v>64</v>
+        <v>52</v>
       </c>
       <c r="E98" s="12">
-        <v>1569701</v>
+        <v>226782</v>
       </c>
       <c r="F98" s="8"/>
       <c r="G98" s="9" t="s">
-        <v>43</v>
+        <v>26</v>
       </c>
       <c r="H98" s="9" t="s">
         <v>27</v>
@@ -4139,20 +4427,20 @@
         <v>23</v>
       </c>
       <c r="B99" s="10">
-        <v>46065</v>
+        <v>46050</v>
       </c>
       <c r="C99" s="11" t="s">
-        <v>63</v>
+        <v>51</v>
       </c>
       <c r="D99" s="9" t="s">
-        <v>64</v>
+        <v>52</v>
       </c>
       <c r="E99" s="12">
-        <v>313933</v>
+        <v>9373531</v>
       </c>
       <c r="F99" s="8"/>
       <c r="G99" s="9" t="s">
-        <v>43</v>
+        <v>26</v>
       </c>
       <c r="H99" s="9" t="s">
         <v>27</v>
@@ -4163,20 +4451,20 @@
         <v>23</v>
       </c>
       <c r="B100" s="10">
-        <v>46065</v>
+        <v>46050</v>
       </c>
       <c r="C100" s="11" t="s">
-        <v>63</v>
+        <v>51</v>
       </c>
       <c r="D100" s="9" t="s">
-        <v>64</v>
+        <v>52</v>
       </c>
       <c r="E100" s="12">
-        <v>1594619</v>
+        <v>2602365</v>
       </c>
       <c r="F100" s="8"/>
       <c r="G100" s="9" t="s">
-        <v>43</v>
+        <v>26</v>
       </c>
       <c r="H100" s="9" t="s">
         <v>27</v>
@@ -4187,20 +4475,20 @@
         <v>23</v>
       </c>
       <c r="B101" s="10">
-        <v>46065</v>
+        <v>46052</v>
       </c>
       <c r="C101" s="11" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="D101" s="9" t="s">
-        <v>64</v>
+        <v>52</v>
       </c>
       <c r="E101" s="12">
-        <v>31040898</v>
+        <v>1203636</v>
       </c>
       <c r="F101" s="8"/>
       <c r="G101" s="9" t="s">
-        <v>43</v>
+        <v>26</v>
       </c>
       <c r="H101" s="9" t="s">
         <v>27</v>
@@ -4211,20 +4499,20 @@
         <v>23</v>
       </c>
       <c r="B102" s="10">
-        <v>46065</v>
+        <v>46055</v>
       </c>
       <c r="C102" s="11" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="D102" s="9" t="s">
-        <v>64</v>
+        <v>55</v>
       </c>
       <c r="E102" s="12">
-        <v>1458662</v>
+        <v>4837767</v>
       </c>
       <c r="F102" s="8"/>
       <c r="G102" s="9" t="s">
-        <v>43</v>
+        <v>26</v>
       </c>
       <c r="H102" s="9" t="s">
         <v>27</v>
@@ -4235,20 +4523,20 @@
         <v>23</v>
       </c>
       <c r="B103" s="10">
-        <v>46065</v>
+        <v>46055</v>
       </c>
       <c r="C103" s="11" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="D103" s="9" t="s">
-        <v>64</v>
+        <v>55</v>
       </c>
       <c r="E103" s="12">
-        <v>60360000</v>
+        <v>29678743</v>
       </c>
       <c r="F103" s="8"/>
       <c r="G103" s="9" t="s">
-        <v>43</v>
+        <v>26</v>
       </c>
       <c r="H103" s="9" t="s">
         <v>27</v>
@@ -4259,20 +4547,20 @@
         <v>23</v>
       </c>
       <c r="B104" s="10">
-        <v>46077</v>
+        <v>46055</v>
       </c>
       <c r="C104" s="11" t="s">
-        <v>65</v>
+        <v>54</v>
       </c>
       <c r="D104" s="9" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="E104" s="12">
-        <v>30180000</v>
+        <v>46268766</v>
       </c>
       <c r="F104" s="8"/>
       <c r="G104" s="9" t="s">
-        <v>43</v>
+        <v>26</v>
       </c>
       <c r="H104" s="9" t="s">
         <v>27</v>
@@ -4283,20 +4571,20 @@
         <v>23</v>
       </c>
       <c r="B105" s="10">
-        <v>46080</v>
+        <v>46055</v>
       </c>
       <c r="C105" s="11" t="s">
-        <v>66</v>
+        <v>54</v>
       </c>
       <c r="D105" s="9" t="s">
-        <v>67</v>
+        <v>55</v>
       </c>
       <c r="E105" s="12">
-        <v>281672</v>
+        <v>58071188</v>
       </c>
       <c r="F105" s="8"/>
       <c r="G105" s="9" t="s">
-        <v>43</v>
+        <v>26</v>
       </c>
       <c r="H105" s="9" t="s">
         <v>27</v>
@@ -4307,20 +4595,20 @@
         <v>23</v>
       </c>
       <c r="B106" s="10">
-        <v>46081</v>
+        <v>46055</v>
       </c>
       <c r="C106" s="11" t="s">
-        <v>68</v>
+        <v>54</v>
       </c>
       <c r="D106" s="9" t="s">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="E106" s="12">
-        <v>816370</v>
+        <v>452700000</v>
       </c>
       <c r="F106" s="8"/>
       <c r="G106" s="9" t="s">
-        <v>43</v>
+        <v>26</v>
       </c>
       <c r="H106" s="9" t="s">
         <v>27</v>
@@ -4331,20 +4619,20 @@
         <v>23</v>
       </c>
       <c r="B107" s="10">
-        <v>46084</v>
+        <v>46055</v>
       </c>
       <c r="C107" s="11" t="s">
-        <v>69</v>
+        <v>54</v>
       </c>
       <c r="D107" s="9" t="s">
-        <v>70</v>
+        <v>55</v>
       </c>
       <c r="E107" s="12">
-        <v>1080600</v>
+        <v>24302032</v>
       </c>
       <c r="F107" s="8"/>
       <c r="G107" s="9" t="s">
-        <v>43</v>
+        <v>26</v>
       </c>
       <c r="H107" s="9" t="s">
         <v>27</v>
@@ -4355,20 +4643,20 @@
         <v>23</v>
       </c>
       <c r="B108" s="10">
-        <v>46084</v>
+        <v>46055</v>
       </c>
       <c r="C108" s="11" t="s">
-        <v>69</v>
+        <v>56</v>
       </c>
       <c r="D108" s="9" t="s">
-        <v>70</v>
-      </c>
-      <c r="E108" s="12">
-        <v>1196399</v>
+        <v>55</v>
+      </c>
+      <c r="E108" s="14">
+        <v>3</v>
       </c>
       <c r="F108" s="8"/>
       <c r="G108" s="9" t="s">
-        <v>43</v>
+        <v>26</v>
       </c>
       <c r="H108" s="9" t="s">
         <v>27</v>
@@ -4379,20 +4667,20 @@
         <v>23</v>
       </c>
       <c r="B109" s="10">
-        <v>46084</v>
+        <v>46055</v>
       </c>
       <c r="C109" s="11" t="s">
-        <v>69</v>
+        <v>56</v>
       </c>
       <c r="D109" s="9" t="s">
-        <v>70</v>
-      </c>
-      <c r="E109" s="12">
-        <v>819572</v>
+        <v>55</v>
+      </c>
+      <c r="E109" s="14">
+        <v>3</v>
       </c>
       <c r="F109" s="8"/>
       <c r="G109" s="9" t="s">
-        <v>43</v>
+        <v>26</v>
       </c>
       <c r="H109" s="9" t="s">
         <v>27</v>
@@ -4403,20 +4691,20 @@
         <v>23</v>
       </c>
       <c r="B110" s="10">
-        <v>46084</v>
+        <v>46055</v>
       </c>
       <c r="C110" s="11" t="s">
-        <v>69</v>
+        <v>56</v>
       </c>
       <c r="D110" s="9" t="s">
-        <v>70</v>
+        <v>55</v>
       </c>
       <c r="E110" s="12">
-        <v>1981095</v>
+        <v>29935698</v>
       </c>
       <c r="F110" s="8"/>
       <c r="G110" s="9" t="s">
-        <v>43</v>
+        <v>26</v>
       </c>
       <c r="H110" s="9" t="s">
         <v>27</v>
@@ -4427,20 +4715,20 @@
         <v>23</v>
       </c>
       <c r="B111" s="10">
-        <v>46084</v>
+        <v>46057</v>
       </c>
       <c r="C111" s="11" t="s">
-        <v>69</v>
+        <v>57</v>
       </c>
       <c r="D111" s="9" t="s">
-        <v>70</v>
+        <v>58</v>
       </c>
       <c r="E111" s="12">
-        <v>592787</v>
+        <v>327286</v>
       </c>
       <c r="F111" s="8"/>
       <c r="G111" s="9" t="s">
-        <v>43</v>
+        <v>26</v>
       </c>
       <c r="H111" s="9" t="s">
         <v>27</v>
@@ -4451,20 +4739,20 @@
         <v>23</v>
       </c>
       <c r="B112" s="10">
-        <v>46086</v>
+        <v>46057</v>
       </c>
       <c r="C112" s="11" t="s">
-        <v>71</v>
+        <v>57</v>
       </c>
       <c r="D112" s="9" t="s">
-        <v>72</v>
+        <v>58</v>
       </c>
       <c r="E112" s="12">
-        <v>1203636</v>
+        <v>1911211</v>
       </c>
       <c r="F112" s="8"/>
       <c r="G112" s="9" t="s">
-        <v>43</v>
+        <v>26</v>
       </c>
       <c r="H112" s="9" t="s">
         <v>27</v>
@@ -4475,20 +4763,20 @@
         <v>23</v>
       </c>
       <c r="B113" s="10">
-        <v>46086</v>
+        <v>46057</v>
       </c>
       <c r="C113" s="11" t="s">
-        <v>71</v>
+        <v>57</v>
       </c>
       <c r="D113" s="9" t="s">
-        <v>72</v>
+        <v>58</v>
       </c>
       <c r="E113" s="12">
-        <v>1092762</v>
+        <v>784850</v>
       </c>
       <c r="F113" s="8"/>
       <c r="G113" s="9" t="s">
-        <v>43</v>
+        <v>26</v>
       </c>
       <c r="H113" s="9" t="s">
         <v>27</v>
@@ -4499,20 +4787,20 @@
         <v>23</v>
       </c>
       <c r="B114" s="10">
-        <v>46086</v>
+        <v>46057</v>
       </c>
       <c r="C114" s="11" t="s">
-        <v>71</v>
+        <v>57</v>
       </c>
       <c r="D114" s="9" t="s">
-        <v>72</v>
+        <v>58</v>
       </c>
       <c r="E114" s="12">
-        <v>1080600</v>
+        <v>24302033</v>
       </c>
       <c r="F114" s="8"/>
       <c r="G114" s="9" t="s">
-        <v>43</v>
+        <v>26</v>
       </c>
       <c r="H114" s="9" t="s">
         <v>27</v>
@@ -4523,20 +4811,20 @@
         <v>23</v>
       </c>
       <c r="B115" s="10">
-        <v>46086</v>
+        <v>46057</v>
       </c>
       <c r="C115" s="11" t="s">
-        <v>71</v>
+        <v>57</v>
       </c>
       <c r="D115" s="9" t="s">
-        <v>72</v>
+        <v>58</v>
       </c>
       <c r="E115" s="12">
-        <v>5003674</v>
+        <v>120720000</v>
       </c>
       <c r="F115" s="8"/>
       <c r="G115" s="9" t="s">
-        <v>43</v>
+        <v>26</v>
       </c>
       <c r="H115" s="9" t="s">
         <v>27</v>
@@ -4547,20 +4835,20 @@
         <v>23</v>
       </c>
       <c r="B116" s="10">
-        <v>46086</v>
+        <v>46057</v>
       </c>
       <c r="C116" s="11" t="s">
-        <v>71</v>
+        <v>57</v>
       </c>
       <c r="D116" s="9" t="s">
-        <v>72</v>
+        <v>58</v>
       </c>
       <c r="E116" s="12">
-        <v>1794599</v>
+        <v>1458662</v>
       </c>
       <c r="F116" s="8"/>
       <c r="G116" s="9" t="s">
-        <v>43</v>
+        <v>26</v>
       </c>
       <c r="H116" s="9" t="s">
         <v>27</v>
@@ -4571,20 +4859,20 @@
         <v>23</v>
       </c>
       <c r="B117" s="10">
-        <v>46086</v>
+        <v>46057</v>
       </c>
       <c r="C117" s="11" t="s">
-        <v>71</v>
+        <v>57</v>
       </c>
       <c r="D117" s="9" t="s">
-        <v>72</v>
+        <v>58</v>
       </c>
       <c r="E117" s="12">
-        <v>1289143</v>
+        <v>302400</v>
       </c>
       <c r="F117" s="8"/>
       <c r="G117" s="9" t="s">
-        <v>43</v>
+        <v>26</v>
       </c>
       <c r="H117" s="9" t="s">
         <v>27</v>
@@ -4595,20 +4883,20 @@
         <v>23</v>
       </c>
       <c r="B118" s="10">
-        <v>46092</v>
+        <v>46057</v>
       </c>
       <c r="C118" s="11" t="s">
-        <v>73</v>
+        <v>57</v>
       </c>
       <c r="D118" s="9" t="s">
-        <v>74</v>
+        <v>58</v>
       </c>
       <c r="E118" s="12">
-        <v>849041</v>
+        <v>982851</v>
       </c>
       <c r="F118" s="8"/>
       <c r="G118" s="9" t="s">
-        <v>43</v>
+        <v>26</v>
       </c>
       <c r="H118" s="9" t="s">
         <v>27</v>
@@ -4619,20 +4907,20 @@
         <v>23</v>
       </c>
       <c r="B119" s="10">
-        <v>46092</v>
+        <v>46057</v>
       </c>
       <c r="C119" s="11" t="s">
-        <v>73</v>
+        <v>59</v>
       </c>
       <c r="D119" s="9" t="s">
-        <v>74</v>
+        <v>60</v>
       </c>
       <c r="E119" s="12">
-        <v>1289143</v>
+        <v>982850</v>
       </c>
       <c r="F119" s="8"/>
       <c r="G119" s="9" t="s">
-        <v>43</v>
+        <v>26</v>
       </c>
       <c r="H119" s="9" t="s">
         <v>27</v>
@@ -4643,20 +4931,20 @@
         <v>23</v>
       </c>
       <c r="B120" s="10">
-        <v>46092</v>
+        <v>46057</v>
       </c>
       <c r="C120" s="11" t="s">
-        <v>73</v>
+        <v>59</v>
       </c>
       <c r="D120" s="9" t="s">
-        <v>74</v>
+        <v>60</v>
       </c>
       <c r="E120" s="12">
-        <v>3005096</v>
+        <v>1309143</v>
       </c>
       <c r="F120" s="8"/>
       <c r="G120" s="9" t="s">
-        <v>43</v>
+        <v>26</v>
       </c>
       <c r="H120" s="9" t="s">
         <v>27</v>
@@ -4667,20 +4955,20 @@
         <v>23</v>
       </c>
       <c r="B121" s="10">
-        <v>46092</v>
+        <v>46057</v>
       </c>
       <c r="C121" s="11" t="s">
-        <v>73</v>
+        <v>59</v>
       </c>
       <c r="D121" s="9" t="s">
-        <v>74</v>
+        <v>60</v>
       </c>
       <c r="E121" s="12">
-        <v>261617</v>
+        <v>1569701</v>
       </c>
       <c r="F121" s="8"/>
       <c r="G121" s="9" t="s">
-        <v>43</v>
+        <v>26</v>
       </c>
       <c r="H121" s="9" t="s">
         <v>27</v>
@@ -4691,20 +4979,20 @@
         <v>23</v>
       </c>
       <c r="B122" s="10">
-        <v>46092</v>
+        <v>46057</v>
       </c>
       <c r="C122" s="11" t="s">
-        <v>73</v>
+        <v>59</v>
       </c>
       <c r="D122" s="9" t="s">
-        <v>74</v>
-      </c>
-      <c r="E122" s="14">
-        <v>3</v>
+        <v>60</v>
+      </c>
+      <c r="E122" s="12">
+        <v>4233600</v>
       </c>
       <c r="F122" s="8"/>
       <c r="G122" s="9" t="s">
-        <v>43</v>
+        <v>26</v>
       </c>
       <c r="H122" s="9" t="s">
         <v>27</v>
@@ -4715,20 +5003,20 @@
         <v>23</v>
       </c>
       <c r="B123" s="10">
-        <v>46092</v>
+        <v>46057</v>
       </c>
       <c r="C123" s="11" t="s">
-        <v>73</v>
+        <v>59</v>
       </c>
       <c r="D123" s="9" t="s">
-        <v>74</v>
+        <v>60</v>
       </c>
       <c r="E123" s="12">
-        <v>19957132</v>
+        <v>1458662</v>
       </c>
       <c r="F123" s="8"/>
       <c r="G123" s="9" t="s">
-        <v>43</v>
+        <v>26</v>
       </c>
       <c r="H123" s="9" t="s">
         <v>27</v>
@@ -4739,20 +5027,20 @@
         <v>23</v>
       </c>
       <c r="B124" s="10">
-        <v>46092</v>
+        <v>46057</v>
       </c>
       <c r="C124" s="11" t="s">
-        <v>73</v>
+        <v>59</v>
       </c>
       <c r="D124" s="9" t="s">
-        <v>74</v>
+        <v>60</v>
       </c>
       <c r="E124" s="12">
-        <v>833946</v>
+        <v>955606</v>
       </c>
       <c r="F124" s="8"/>
       <c r="G124" s="9" t="s">
-        <v>43</v>
+        <v>26</v>
       </c>
       <c r="H124" s="9" t="s">
         <v>27</v>
@@ -4763,20 +5051,20 @@
         <v>23</v>
       </c>
       <c r="B125" s="10">
-        <v>46092</v>
+        <v>46057</v>
       </c>
       <c r="C125" s="11" t="s">
-        <v>75</v>
+        <v>59</v>
       </c>
       <c r="D125" s="9" t="s">
-        <v>76</v>
+        <v>60</v>
       </c>
       <c r="E125" s="12">
-        <v>8946966</v>
+        <v>1203636</v>
       </c>
       <c r="F125" s="8"/>
       <c r="G125" s="9" t="s">
-        <v>43</v>
+        <v>26</v>
       </c>
       <c r="H125" s="9" t="s">
         <v>27</v>
@@ -4787,20 +5075,20 @@
         <v>23</v>
       </c>
       <c r="B126" s="10">
-        <v>46094</v>
+        <v>46057</v>
       </c>
       <c r="C126" s="11" t="s">
-        <v>77</v>
+        <v>61</v>
       </c>
       <c r="D126" s="9" t="s">
-        <v>70</v>
+        <v>62</v>
       </c>
       <c r="E126" s="12">
-        <v>1289143</v>
+        <v>84257</v>
       </c>
       <c r="F126" s="8"/>
       <c r="G126" s="9" t="s">
-        <v>43</v>
+        <v>26</v>
       </c>
       <c r="H126" s="9" t="s">
         <v>27</v>
@@ -4811,20 +5099,20 @@
         <v>23</v>
       </c>
       <c r="B127" s="10">
-        <v>46098</v>
+        <v>46058</v>
       </c>
       <c r="C127" s="11" t="s">
-        <v>78</v>
+        <v>63</v>
       </c>
       <c r="D127" s="9" t="s">
-        <v>70</v>
+        <v>52</v>
       </c>
       <c r="E127" s="12">
-        <v>273191</v>
+        <v>471581</v>
       </c>
       <c r="F127" s="8"/>
       <c r="G127" s="9" t="s">
-        <v>43</v>
+        <v>26</v>
       </c>
       <c r="H127" s="9" t="s">
         <v>27</v>
@@ -4835,20 +5123,20 @@
         <v>23</v>
       </c>
       <c r="B128" s="10">
-        <v>46101</v>
+        <v>46060</v>
       </c>
       <c r="C128" s="11" t="s">
-        <v>79</v>
+        <v>64</v>
       </c>
       <c r="D128" s="9" t="s">
-        <v>80</v>
-      </c>
-      <c r="E128" s="14">
-        <v>12</v>
+        <v>65</v>
+      </c>
+      <c r="E128" s="12">
+        <v>10286294</v>
       </c>
       <c r="F128" s="8"/>
       <c r="G128" s="9" t="s">
-        <v>43</v>
+        <v>26</v>
       </c>
       <c r="H128" s="9" t="s">
         <v>27</v>
@@ -4859,20 +5147,20 @@
         <v>23</v>
       </c>
       <c r="B129" s="10">
-        <v>46101</v>
+        <v>46062</v>
       </c>
       <c r="C129" s="11" t="s">
-        <v>79</v>
+        <v>66</v>
       </c>
       <c r="D129" s="9" t="s">
-        <v>80</v>
+        <v>67</v>
       </c>
       <c r="E129" s="12">
-        <v>674268</v>
+        <v>1569701</v>
       </c>
       <c r="F129" s="8"/>
       <c r="G129" s="9" t="s">
-        <v>43</v>
+        <v>26</v>
       </c>
       <c r="H129" s="9" t="s">
         <v>27</v>
@@ -4883,20 +5171,20 @@
         <v>23</v>
       </c>
       <c r="B130" s="10">
-        <v>46101</v>
+        <v>46062</v>
       </c>
       <c r="C130" s="11" t="s">
-        <v>79</v>
+        <v>66</v>
       </c>
       <c r="D130" s="9" t="s">
-        <v>80</v>
+        <v>67</v>
       </c>
       <c r="E130" s="12">
-        <v>1289141</v>
+        <v>955605</v>
       </c>
       <c r="F130" s="8"/>
       <c r="G130" s="9" t="s">
-        <v>43</v>
+        <v>26</v>
       </c>
       <c r="H130" s="9" t="s">
         <v>27</v>
@@ -4907,20 +5195,20 @@
         <v>23</v>
       </c>
       <c r="B131" s="10">
-        <v>46101</v>
+        <v>46063</v>
       </c>
       <c r="C131" s="11" t="s">
-        <v>79</v>
+        <v>68</v>
       </c>
       <c r="D131" s="9" t="s">
-        <v>80</v>
-      </c>
-      <c r="E131" s="12">
-        <v>277982</v>
-      </c>
-      <c r="F131" s="8"/>
+        <v>69</v>
+      </c>
+      <c r="E131" s="8"/>
+      <c r="F131" s="12">
+        <v>29678743</v>
+      </c>
       <c r="G131" s="9" t="s">
-        <v>43</v>
+        <v>26</v>
       </c>
       <c r="H131" s="9" t="s">
         <v>27</v>
@@ -4931,20 +5219,20 @@
         <v>23</v>
       </c>
       <c r="B132" s="10">
-        <v>46101</v>
+        <v>46065</v>
       </c>
       <c r="C132" s="11" t="s">
-        <v>79</v>
+        <v>70</v>
       </c>
       <c r="D132" s="9" t="s">
-        <v>80</v>
-      </c>
-      <c r="E132" s="14">
-        <v>21</v>
+        <v>71</v>
+      </c>
+      <c r="E132" s="12">
+        <v>1569701</v>
       </c>
       <c r="F132" s="8"/>
       <c r="G132" s="9" t="s">
-        <v>43</v>
+        <v>26</v>
       </c>
       <c r="H132" s="9" t="s">
         <v>27</v>
@@ -4955,20 +5243,20 @@
         <v>23</v>
       </c>
       <c r="B133" s="10">
-        <v>46101</v>
+        <v>46065</v>
       </c>
       <c r="C133" s="11" t="s">
-        <v>81</v>
+        <v>70</v>
       </c>
       <c r="D133" s="9" t="s">
-        <v>82</v>
+        <v>71</v>
       </c>
       <c r="E133" s="12">
-        <v>22162200</v>
+        <v>31040898</v>
       </c>
       <c r="F133" s="8"/>
       <c r="G133" s="9" t="s">
-        <v>43</v>
+        <v>26</v>
       </c>
       <c r="H133" s="9" t="s">
         <v>27</v>
@@ -4979,20 +5267,20 @@
         <v>23</v>
       </c>
       <c r="B134" s="10">
-        <v>46101</v>
+        <v>46065</v>
       </c>
       <c r="C134" s="11" t="s">
-        <v>81</v>
+        <v>70</v>
       </c>
       <c r="D134" s="9" t="s">
-        <v>82</v>
+        <v>71</v>
       </c>
       <c r="E134" s="12">
-        <v>22162200</v>
+        <v>26240898</v>
       </c>
       <c r="F134" s="8"/>
       <c r="G134" s="9" t="s">
-        <v>43</v>
+        <v>26</v>
       </c>
       <c r="H134" s="9" t="s">
         <v>27</v>
@@ -5003,20 +5291,20 @@
         <v>23</v>
       </c>
       <c r="B135" s="10">
-        <v>46101</v>
+        <v>46065</v>
       </c>
       <c r="C135" s="11" t="s">
-        <v>81</v>
+        <v>70</v>
       </c>
       <c r="D135" s="9" t="s">
-        <v>82</v>
+        <v>71</v>
       </c>
       <c r="E135" s="12">
-        <v>22162200</v>
+        <v>1458662</v>
       </c>
       <c r="F135" s="8"/>
       <c r="G135" s="9" t="s">
-        <v>43</v>
+        <v>26</v>
       </c>
       <c r="H135" s="9" t="s">
         <v>27</v>
@@ -5027,20 +5315,20 @@
         <v>23</v>
       </c>
       <c r="B136" s="10">
-        <v>46101</v>
+        <v>46065</v>
       </c>
       <c r="C136" s="11" t="s">
-        <v>81</v>
+        <v>70</v>
       </c>
       <c r="D136" s="9" t="s">
-        <v>82</v>
+        <v>71</v>
       </c>
       <c r="E136" s="12">
-        <v>74711444</v>
+        <v>313933</v>
       </c>
       <c r="F136" s="8"/>
       <c r="G136" s="9" t="s">
-        <v>43</v>
+        <v>26</v>
       </c>
       <c r="H136" s="9" t="s">
         <v>27</v>
@@ -5051,20 +5339,20 @@
         <v>23</v>
       </c>
       <c r="B137" s="10">
-        <v>46101</v>
+        <v>46065</v>
       </c>
       <c r="C137" s="11" t="s">
-        <v>81</v>
+        <v>70</v>
       </c>
       <c r="D137" s="9" t="s">
-        <v>82</v>
+        <v>71</v>
       </c>
       <c r="E137" s="12">
-        <v>22800000</v>
+        <v>60360000</v>
       </c>
       <c r="F137" s="8"/>
       <c r="G137" s="9" t="s">
-        <v>43</v>
+        <v>26</v>
       </c>
       <c r="H137" s="9" t="s">
         <v>27</v>
@@ -5075,20 +5363,20 @@
         <v>23</v>
       </c>
       <c r="B138" s="10">
-        <v>46101</v>
+        <v>46065</v>
       </c>
       <c r="C138" s="11" t="s">
-        <v>81</v>
+        <v>70</v>
       </c>
       <c r="D138" s="9" t="s">
-        <v>82</v>
+        <v>71</v>
       </c>
       <c r="E138" s="12">
-        <v>24862467</v>
+        <v>1594619</v>
       </c>
       <c r="F138" s="8"/>
       <c r="G138" s="9" t="s">
-        <v>43</v>
+        <v>26</v>
       </c>
       <c r="H138" s="9" t="s">
         <v>27</v>
@@ -5099,20 +5387,20 @@
         <v>23</v>
       </c>
       <c r="B139" s="10">
-        <v>46105</v>
+        <v>46077</v>
       </c>
       <c r="C139" s="11" t="s">
-        <v>83</v>
+        <v>72</v>
       </c>
       <c r="D139" s="9" t="s">
-        <v>84</v>
-      </c>
-      <c r="E139" s="8"/>
-      <c r="F139" s="14">
-        <v>3</v>
-      </c>
+        <v>60</v>
+      </c>
+      <c r="E139" s="12">
+        <v>30180000</v>
+      </c>
+      <c r="F139" s="8"/>
       <c r="G139" s="9" t="s">
-        <v>43</v>
+        <v>26</v>
       </c>
       <c r="H139" s="9" t="s">
         <v>27</v>
@@ -5123,20 +5411,20 @@
         <v>23</v>
       </c>
       <c r="B140" s="10">
-        <v>46105</v>
+        <v>46080</v>
       </c>
       <c r="C140" s="11" t="s">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="D140" s="9" t="s">
-        <v>84</v>
-      </c>
-      <c r="E140" s="8"/>
-      <c r="F140" s="14">
-        <v>1</v>
-      </c>
+        <v>74</v>
+      </c>
+      <c r="E140" s="12">
+        <v>281672</v>
+      </c>
+      <c r="F140" s="8"/>
       <c r="G140" s="9" t="s">
-        <v>43</v>
+        <v>26</v>
       </c>
       <c r="H140" s="9" t="s">
         <v>27</v>
@@ -5147,20 +5435,20 @@
         <v>23</v>
       </c>
       <c r="B141" s="10">
-        <v>46105</v>
+        <v>46081</v>
       </c>
       <c r="C141" s="11" t="s">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="D141" s="9" t="s">
-        <v>84</v>
-      </c>
-      <c r="E141" s="8"/>
-      <c r="F141" s="14">
-        <v>1</v>
-      </c>
+        <v>52</v>
+      </c>
+      <c r="E141" s="12">
+        <v>816370</v>
+      </c>
+      <c r="F141" s="8"/>
       <c r="G141" s="9" t="s">
-        <v>43</v>
+        <v>26</v>
       </c>
       <c r="H141" s="9" t="s">
         <v>27</v>
@@ -5171,20 +5459,20 @@
         <v>23</v>
       </c>
       <c r="B142" s="10">
-        <v>46105</v>
+        <v>46084</v>
       </c>
       <c r="C142" s="11" t="s">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="D142" s="9" t="s">
-        <v>84</v>
-      </c>
-      <c r="E142" s="8"/>
-      <c r="F142" s="14">
-        <v>3</v>
-      </c>
+        <v>77</v>
+      </c>
+      <c r="E142" s="12">
+        <v>592787</v>
+      </c>
+      <c r="F142" s="8"/>
       <c r="G142" s="9" t="s">
-        <v>43</v>
+        <v>26</v>
       </c>
       <c r="H142" s="9" t="s">
         <v>27</v>
@@ -5195,20 +5483,20 @@
         <v>23</v>
       </c>
       <c r="B143" s="10">
-        <v>46105</v>
+        <v>46084</v>
       </c>
       <c r="C143" s="11" t="s">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="D143" s="9" t="s">
-        <v>86</v>
-      </c>
-      <c r="E143" s="14">
-        <v>21</v>
+        <v>77</v>
+      </c>
+      <c r="E143" s="12">
+        <v>819572</v>
       </c>
       <c r="F143" s="8"/>
       <c r="G143" s="9" t="s">
-        <v>43</v>
+        <v>26</v>
       </c>
       <c r="H143" s="9" t="s">
         <v>27</v>
@@ -5219,20 +5507,20 @@
         <v>23</v>
       </c>
       <c r="B144" s="10">
-        <v>46106</v>
+        <v>46084</v>
       </c>
       <c r="C144" s="11" t="s">
-        <v>87</v>
+        <v>76</v>
       </c>
       <c r="D144" s="9" t="s">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="E144" s="12">
-        <v>2830136</v>
+        <v>1196399</v>
       </c>
       <c r="F144" s="8"/>
       <c r="G144" s="9" t="s">
-        <v>43</v>
+        <v>26</v>
       </c>
       <c r="H144" s="9" t="s">
         <v>27</v>
@@ -5243,20 +5531,20 @@
         <v>23</v>
       </c>
       <c r="B145" s="10">
-        <v>46106</v>
+        <v>46084</v>
       </c>
       <c r="C145" s="11" t="s">
-        <v>87</v>
+        <v>76</v>
       </c>
       <c r="D145" s="9" t="s">
-        <v>88</v>
-      </c>
-      <c r="E145" s="14">
-        <v>3</v>
+        <v>77</v>
+      </c>
+      <c r="E145" s="12">
+        <v>1981095</v>
       </c>
       <c r="F145" s="8"/>
       <c r="G145" s="9" t="s">
-        <v>43</v>
+        <v>26</v>
       </c>
       <c r="H145" s="9" t="s">
         <v>27</v>
@@ -5267,20 +5555,20 @@
         <v>23</v>
       </c>
       <c r="B146" s="10">
-        <v>46106</v>
+        <v>46084</v>
       </c>
       <c r="C146" s="11" t="s">
-        <v>87</v>
+        <v>76</v>
       </c>
       <c r="D146" s="9" t="s">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="E146" s="12">
-        <v>112378</v>
+        <v>1080600</v>
       </c>
       <c r="F146" s="8"/>
       <c r="G146" s="9" t="s">
-        <v>43</v>
+        <v>26</v>
       </c>
       <c r="H146" s="9" t="s">
         <v>27</v>
@@ -5291,20 +5579,20 @@
         <v>23</v>
       </c>
       <c r="B147" s="10">
-        <v>46106</v>
+        <v>46086</v>
       </c>
       <c r="C147" s="11" t="s">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="D147" s="9" t="s">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="E147" s="12">
-        <v>30826833</v>
+        <v>1092762</v>
       </c>
       <c r="F147" s="8"/>
       <c r="G147" s="9" t="s">
-        <v>43</v>
+        <v>26</v>
       </c>
       <c r="H147" s="9" t="s">
         <v>27</v>
@@ -5315,20 +5603,20 @@
         <v>23</v>
       </c>
       <c r="B148" s="10">
-        <v>46106</v>
+        <v>46086</v>
       </c>
       <c r="C148" s="11" t="s">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="D148" s="9" t="s">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="E148" s="12">
-        <v>31403986</v>
+        <v>1080600</v>
       </c>
       <c r="F148" s="8"/>
       <c r="G148" s="9" t="s">
-        <v>43</v>
+        <v>26</v>
       </c>
       <c r="H148" s="9" t="s">
         <v>27</v>
@@ -5339,20 +5627,20 @@
         <v>23</v>
       </c>
       <c r="B149" s="10">
-        <v>46106</v>
+        <v>46086</v>
       </c>
       <c r="C149" s="11" t="s">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="D149" s="9" t="s">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="E149" s="12">
-        <v>24653171</v>
+        <v>1794599</v>
       </c>
       <c r="F149" s="8"/>
       <c r="G149" s="9" t="s">
-        <v>43</v>
+        <v>26</v>
       </c>
       <c r="H149" s="9" t="s">
         <v>27</v>
@@ -5363,20 +5651,20 @@
         <v>23</v>
       </c>
       <c r="B150" s="10">
-        <v>46107</v>
+        <v>46086</v>
       </c>
       <c r="C150" s="11" t="s">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="D150" s="9" t="s">
-        <v>92</v>
-      </c>
-      <c r="E150" s="8"/>
-      <c r="F150" s="14">
-        <v>1</v>
-      </c>
+        <v>79</v>
+      </c>
+      <c r="E150" s="12">
+        <v>5003674</v>
+      </c>
+      <c r="F150" s="8"/>
       <c r="G150" s="9" t="s">
-        <v>43</v>
+        <v>26</v>
       </c>
       <c r="H150" s="9" t="s">
         <v>27</v>
@@ -5387,20 +5675,20 @@
         <v>23</v>
       </c>
       <c r="B151" s="10">
-        <v>46107</v>
+        <v>46086</v>
       </c>
       <c r="C151" s="11" t="s">
-        <v>93</v>
+        <v>78</v>
       </c>
       <c r="D151" s="9" t="s">
-        <v>94</v>
+        <v>79</v>
       </c>
       <c r="E151" s="12">
-        <v>910617</v>
+        <v>1203636</v>
       </c>
       <c r="F151" s="8"/>
       <c r="G151" s="9" t="s">
-        <v>43</v>
+        <v>26</v>
       </c>
       <c r="H151" s="9" t="s">
         <v>27</v>
@@ -5411,20 +5699,20 @@
         <v>23</v>
       </c>
       <c r="B152" s="10">
-        <v>46108</v>
+        <v>46086</v>
       </c>
       <c r="C152" s="11" t="s">
-        <v>95</v>
+        <v>78</v>
       </c>
       <c r="D152" s="9" t="s">
-        <v>96</v>
+        <v>79</v>
       </c>
       <c r="E152" s="12">
-        <v>9193198</v>
+        <v>1289143</v>
       </c>
       <c r="F152" s="8"/>
       <c r="G152" s="9" t="s">
-        <v>43</v>
+        <v>26</v>
       </c>
       <c r="H152" s="9" t="s">
         <v>27</v>
@@ -5435,20 +5723,20 @@
         <v>23</v>
       </c>
       <c r="B153" s="10">
-        <v>46108</v>
+        <v>46092</v>
       </c>
       <c r="C153" s="11" t="s">
-        <v>97</v>
+        <v>80</v>
       </c>
       <c r="D153" s="9" t="s">
-        <v>98</v>
-      </c>
-      <c r="E153" s="14">
-        <v>2</v>
+        <v>81</v>
+      </c>
+      <c r="E153" s="12">
+        <v>3005096</v>
       </c>
       <c r="F153" s="8"/>
       <c r="G153" s="9" t="s">
-        <v>43</v>
+        <v>26</v>
       </c>
       <c r="H153" s="9" t="s">
         <v>27</v>
@@ -5459,20 +5747,20 @@
         <v>23</v>
       </c>
       <c r="B154" s="10">
-        <v>46108</v>
+        <v>46092</v>
       </c>
       <c r="C154" s="11" t="s">
-        <v>97</v>
+        <v>80</v>
       </c>
       <c r="D154" s="9" t="s">
-        <v>98</v>
-      </c>
-      <c r="E154" s="14">
-        <v>3</v>
+        <v>81</v>
+      </c>
+      <c r="E154" s="12">
+        <v>1289143</v>
       </c>
       <c r="F154" s="8"/>
       <c r="G154" s="9" t="s">
-        <v>43</v>
+        <v>26</v>
       </c>
       <c r="H154" s="9" t="s">
         <v>27</v>
@@ -5483,20 +5771,20 @@
         <v>23</v>
       </c>
       <c r="B155" s="10">
-        <v>46108</v>
+        <v>46092</v>
       </c>
       <c r="C155" s="11" t="s">
-        <v>97</v>
+        <v>80</v>
       </c>
       <c r="D155" s="9" t="s">
-        <v>98</v>
-      </c>
-      <c r="E155" s="14">
-        <v>4</v>
+        <v>81</v>
+      </c>
+      <c r="E155" s="12">
+        <v>19957132</v>
       </c>
       <c r="F155" s="8"/>
       <c r="G155" s="9" t="s">
-        <v>43</v>
+        <v>26</v>
       </c>
       <c r="H155" s="9" t="s">
         <v>27</v>
@@ -5507,20 +5795,20 @@
         <v>23</v>
       </c>
       <c r="B156" s="10">
-        <v>46108</v>
+        <v>46092</v>
       </c>
       <c r="C156" s="11" t="s">
-        <v>97</v>
+        <v>80</v>
       </c>
       <c r="D156" s="9" t="s">
-        <v>98</v>
-      </c>
-      <c r="E156" s="14">
-        <v>3</v>
+        <v>81</v>
+      </c>
+      <c r="E156" s="12">
+        <v>849041</v>
       </c>
       <c r="F156" s="8"/>
       <c r="G156" s="9" t="s">
-        <v>43</v>
+        <v>26</v>
       </c>
       <c r="H156" s="9" t="s">
         <v>27</v>
@@ -5531,20 +5819,20 @@
         <v>23</v>
       </c>
       <c r="B157" s="10">
-        <v>46108</v>
+        <v>46092</v>
       </c>
       <c r="C157" s="11" t="s">
-        <v>97</v>
+        <v>80</v>
       </c>
       <c r="D157" s="9" t="s">
-        <v>98</v>
-      </c>
-      <c r="E157" s="14">
-        <v>1</v>
+        <v>81</v>
+      </c>
+      <c r="E157" s="12">
+        <v>833946</v>
       </c>
       <c r="F157" s="8"/>
       <c r="G157" s="9" t="s">
-        <v>43</v>
+        <v>26</v>
       </c>
       <c r="H157" s="9" t="s">
         <v>27</v>
@@ -5555,20 +5843,20 @@
         <v>23</v>
       </c>
       <c r="B158" s="10">
-        <v>46111</v>
+        <v>46092</v>
       </c>
       <c r="C158" s="11" t="s">
-        <v>99</v>
+        <v>80</v>
       </c>
       <c r="D158" s="9" t="s">
-        <v>76</v>
-      </c>
-      <c r="E158" s="12">
-        <v>6536560</v>
+        <v>81</v>
+      </c>
+      <c r="E158" s="14">
+        <v>3</v>
       </c>
       <c r="F158" s="8"/>
       <c r="G158" s="9" t="s">
-        <v>43</v>
+        <v>26</v>
       </c>
       <c r="H158" s="9" t="s">
         <v>27</v>
@@ -5579,16 +5867,16 @@
         <v>23</v>
       </c>
       <c r="B159" s="10">
-        <v>46113</v>
+        <v>46092</v>
       </c>
       <c r="C159" s="11" t="s">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="D159" s="9" t="s">
-        <v>101</v>
+        <v>81</v>
       </c>
       <c r="E159" s="12">
-        <v>337134</v>
+        <v>261617</v>
       </c>
       <c r="F159" s="8"/>
       <c r="G159" s="9" t="s">
@@ -5603,16 +5891,16 @@
         <v>23</v>
       </c>
       <c r="B160" s="10">
-        <v>46114</v>
+        <v>46092</v>
       </c>
       <c r="C160" s="11" t="s">
-        <v>102</v>
+        <v>82</v>
       </c>
       <c r="D160" s="9" t="s">
-        <v>101</v>
+        <v>83</v>
       </c>
       <c r="E160" s="12">
-        <v>910617</v>
+        <v>8946966</v>
       </c>
       <c r="F160" s="8"/>
       <c r="G160" s="9" t="s">
@@ -5627,16 +5915,16 @@
         <v>23</v>
       </c>
       <c r="B161" s="10">
-        <v>46118</v>
+        <v>46094</v>
       </c>
       <c r="C161" s="11" t="s">
-        <v>103</v>
+        <v>84</v>
       </c>
       <c r="D161" s="9" t="s">
-        <v>104</v>
+        <v>77</v>
       </c>
       <c r="E161" s="12">
-        <v>1132054</v>
+        <v>1289143</v>
       </c>
       <c r="F161" s="8"/>
       <c r="G161" s="9" t="s">
@@ -5651,16 +5939,16 @@
         <v>23</v>
       </c>
       <c r="B162" s="10">
-        <v>46118</v>
+        <v>46098</v>
       </c>
       <c r="C162" s="11" t="s">
-        <v>103</v>
+        <v>85</v>
       </c>
       <c r="D162" s="9" t="s">
-        <v>104</v>
+        <v>77</v>
       </c>
       <c r="E162" s="12">
-        <v>972439</v>
+        <v>273191</v>
       </c>
       <c r="F162" s="8"/>
       <c r="G162" s="9" t="s">
@@ -5675,16 +5963,16 @@
         <v>23</v>
       </c>
       <c r="B163" s="10">
-        <v>46118</v>
+        <v>46101</v>
       </c>
       <c r="C163" s="11" t="s">
-        <v>103</v>
+        <v>86</v>
       </c>
       <c r="D163" s="9" t="s">
-        <v>104</v>
+        <v>87</v>
       </c>
       <c r="E163" s="12">
-        <v>1080600</v>
+        <v>1289141</v>
       </c>
       <c r="F163" s="8"/>
       <c r="G163" s="9" t="s">
@@ -5699,16 +5987,16 @@
         <v>23</v>
       </c>
       <c r="B164" s="10">
-        <v>46118</v>
+        <v>46101</v>
       </c>
       <c r="C164" s="11" t="s">
-        <v>103</v>
+        <v>86</v>
       </c>
       <c r="D164" s="9" t="s">
-        <v>104</v>
-      </c>
-      <c r="E164" s="12">
-        <v>2458715</v>
+        <v>87</v>
+      </c>
+      <c r="E164" s="14">
+        <v>21</v>
       </c>
       <c r="F164" s="8"/>
       <c r="G164" s="9" t="s">
@@ -5723,16 +6011,16 @@
         <v>23</v>
       </c>
       <c r="B165" s="10">
-        <v>46118</v>
+        <v>46101</v>
       </c>
       <c r="C165" s="11" t="s">
-        <v>103</v>
+        <v>86</v>
       </c>
       <c r="D165" s="9" t="s">
-        <v>104</v>
+        <v>87</v>
       </c>
       <c r="E165" s="12">
-        <v>110704</v>
+        <v>277982</v>
       </c>
       <c r="F165" s="8"/>
       <c r="G165" s="9" t="s">
@@ -5747,16 +6035,16 @@
         <v>23</v>
       </c>
       <c r="B166" s="10">
-        <v>46118</v>
+        <v>46101</v>
       </c>
       <c r="C166" s="11" t="s">
-        <v>103</v>
+        <v>86</v>
       </c>
       <c r="D166" s="9" t="s">
-        <v>104</v>
+        <v>87</v>
       </c>
       <c r="E166" s="12">
-        <v>1667891</v>
+        <v>674268</v>
       </c>
       <c r="F166" s="8"/>
       <c r="G166" s="9" t="s">
@@ -5771,16 +6059,16 @@
         <v>23</v>
       </c>
       <c r="B167" s="10">
-        <v>46120</v>
+        <v>46101</v>
       </c>
       <c r="C167" s="11" t="s">
-        <v>105</v>
+        <v>86</v>
       </c>
       <c r="D167" s="9" t="s">
-        <v>106</v>
-      </c>
-      <c r="E167" s="12">
-        <v>8853834</v>
+        <v>87</v>
+      </c>
+      <c r="E167" s="14">
+        <v>12</v>
       </c>
       <c r="F167" s="8"/>
       <c r="G167" s="9" t="s">
@@ -5795,16 +6083,16 @@
         <v>23</v>
       </c>
       <c r="B168" s="10">
-        <v>46120</v>
+        <v>46101</v>
       </c>
       <c r="C168" s="11" t="s">
-        <v>107</v>
+        <v>88</v>
       </c>
       <c r="D168" s="9" t="s">
-        <v>108</v>
+        <v>89</v>
       </c>
       <c r="E168" s="12">
-        <v>51552815</v>
+        <v>22162200</v>
       </c>
       <c r="F168" s="8"/>
       <c r="G168" s="9" t="s">
@@ -5819,16 +6107,16 @@
         <v>23</v>
       </c>
       <c r="B169" s="10">
-        <v>46120</v>
+        <v>46101</v>
       </c>
       <c r="C169" s="11" t="s">
-        <v>109</v>
+        <v>88</v>
       </c>
       <c r="D169" s="9" t="s">
-        <v>104</v>
+        <v>89</v>
       </c>
       <c r="E169" s="12">
-        <v>910617</v>
+        <v>22162200</v>
       </c>
       <c r="F169" s="8"/>
       <c r="G169" s="9" t="s">
@@ -5843,16 +6131,16 @@
         <v>23</v>
       </c>
       <c r="B170" s="10">
-        <v>46120</v>
+        <v>46101</v>
       </c>
       <c r="C170" s="11" t="s">
-        <v>110</v>
+        <v>88</v>
       </c>
       <c r="D170" s="9" t="s">
-        <v>108</v>
-      </c>
-      <c r="E170" s="14">
-        <v>3</v>
+        <v>89</v>
+      </c>
+      <c r="E170" s="12">
+        <v>24862467</v>
       </c>
       <c r="F170" s="8"/>
       <c r="G170" s="9" t="s">
@@ -5867,16 +6155,16 @@
         <v>23</v>
       </c>
       <c r="B171" s="10">
-        <v>46120</v>
+        <v>46101</v>
       </c>
       <c r="C171" s="11" t="s">
-        <v>110</v>
+        <v>88</v>
       </c>
       <c r="D171" s="9" t="s">
-        <v>108</v>
-      </c>
-      <c r="E171" s="14">
-        <v>3</v>
+        <v>89</v>
+      </c>
+      <c r="E171" s="12">
+        <v>22162200</v>
       </c>
       <c r="F171" s="8"/>
       <c r="G171" s="9" t="s">
@@ -5891,16 +6179,16 @@
         <v>23</v>
       </c>
       <c r="B172" s="10">
-        <v>46120</v>
+        <v>46101</v>
       </c>
       <c r="C172" s="11" t="s">
-        <v>110</v>
+        <v>88</v>
       </c>
       <c r="D172" s="9" t="s">
-        <v>108</v>
-      </c>
-      <c r="E172" s="14">
-        <v>2</v>
+        <v>89</v>
+      </c>
+      <c r="E172" s="12">
+        <v>74711444</v>
       </c>
       <c r="F172" s="8"/>
       <c r="G172" s="9" t="s">
@@ -5915,16 +6203,16 @@
         <v>23</v>
       </c>
       <c r="B173" s="10">
-        <v>46120</v>
+        <v>46101</v>
       </c>
       <c r="C173" s="11" t="s">
-        <v>111</v>
+        <v>88</v>
       </c>
       <c r="D173" s="9" t="s">
-        <v>108</v>
-      </c>
-      <c r="E173" s="14">
-        <v>15</v>
+        <v>89</v>
+      </c>
+      <c r="E173" s="12">
+        <v>22800000</v>
       </c>
       <c r="F173" s="8"/>
       <c r="G173" s="9" t="s">
@@ -5939,18 +6227,18 @@
         <v>23</v>
       </c>
       <c r="B174" s="10">
-        <v>46120</v>
+        <v>46105</v>
       </c>
       <c r="C174" s="11" t="s">
-        <v>111</v>
+        <v>90</v>
       </c>
       <c r="D174" s="9" t="s">
-        <v>108</v>
-      </c>
-      <c r="E174" s="12">
-        <v>10467995</v>
-      </c>
-      <c r="F174" s="8"/>
+        <v>91</v>
+      </c>
+      <c r="E174" s="8"/>
+      <c r="F174" s="14">
+        <v>1</v>
+      </c>
       <c r="G174" s="9" t="s">
         <v>26</v>
       </c>
@@ -5963,18 +6251,18 @@
         <v>23</v>
       </c>
       <c r="B175" s="10">
-        <v>46120</v>
+        <v>46105</v>
       </c>
       <c r="C175" s="11" t="s">
-        <v>112</v>
+        <v>90</v>
       </c>
       <c r="D175" s="9" t="s">
-        <v>106</v>
-      </c>
-      <c r="E175" s="12">
-        <v>2243711</v>
-      </c>
-      <c r="F175" s="8"/>
+        <v>91</v>
+      </c>
+      <c r="E175" s="8"/>
+      <c r="F175" s="14">
+        <v>3</v>
+      </c>
       <c r="G175" s="9" t="s">
         <v>26</v>
       </c>
@@ -5987,18 +6275,18 @@
         <v>23</v>
       </c>
       <c r="B176" s="10">
-        <v>46121</v>
+        <v>46105</v>
       </c>
       <c r="C176" s="11" t="s">
-        <v>113</v>
+        <v>90</v>
       </c>
       <c r="D176" s="9" t="s">
-        <v>114</v>
-      </c>
-      <c r="E176" s="14">
-        <v>12</v>
-      </c>
-      <c r="F176" s="8"/>
+        <v>91</v>
+      </c>
+      <c r="E176" s="8"/>
+      <c r="F176" s="14">
+        <v>1</v>
+      </c>
       <c r="G176" s="9" t="s">
         <v>26</v>
       </c>
@@ -6011,18 +6299,18 @@
         <v>23</v>
       </c>
       <c r="B177" s="10">
-        <v>46121</v>
+        <v>46105</v>
       </c>
       <c r="C177" s="11" t="s">
-        <v>113</v>
+        <v>90</v>
       </c>
       <c r="D177" s="9" t="s">
-        <v>114</v>
-      </c>
-      <c r="E177" s="14">
+        <v>91</v>
+      </c>
+      <c r="E177" s="8"/>
+      <c r="F177" s="14">
         <v>3</v>
       </c>
-      <c r="F177" s="8"/>
       <c r="G177" s="9" t="s">
         <v>26</v>
       </c>
@@ -6035,16 +6323,16 @@
         <v>23</v>
       </c>
       <c r="B178" s="10">
-        <v>46121</v>
+        <v>46105</v>
       </c>
       <c r="C178" s="11" t="s">
-        <v>115</v>
+        <v>92</v>
       </c>
       <c r="D178" s="9" t="s">
-        <v>106</v>
-      </c>
-      <c r="E178" s="12">
-        <v>2991580</v>
+        <v>93</v>
+      </c>
+      <c r="E178" s="14">
+        <v>21</v>
       </c>
       <c r="F178" s="8"/>
       <c r="G178" s="9" t="s">
@@ -6059,16 +6347,16 @@
         <v>23</v>
       </c>
       <c r="B179" s="10">
-        <v>46121</v>
+        <v>46106</v>
       </c>
       <c r="C179" s="11" t="s">
-        <v>116</v>
+        <v>94</v>
       </c>
       <c r="D179" s="9" t="s">
-        <v>117</v>
-      </c>
-      <c r="E179" s="12">
-        <v>2243711</v>
+        <v>95</v>
+      </c>
+      <c r="E179" s="14">
+        <v>3</v>
       </c>
       <c r="F179" s="8"/>
       <c r="G179" s="9" t="s">
@@ -6083,18 +6371,18 @@
         <v>23</v>
       </c>
       <c r="B180" s="10">
-        <v>46122</v>
+        <v>46106</v>
       </c>
       <c r="C180" s="11" t="s">
-        <v>118</v>
+        <v>94</v>
       </c>
       <c r="D180" s="9" t="s">
-        <v>119</v>
-      </c>
-      <c r="E180" s="8"/>
-      <c r="F180" s="14">
-        <v>3</v>
-      </c>
+        <v>95</v>
+      </c>
+      <c r="E180" s="12">
+        <v>112378</v>
+      </c>
+      <c r="F180" s="8"/>
       <c r="G180" s="9" t="s">
         <v>26</v>
       </c>
@@ -6107,18 +6395,18 @@
         <v>23</v>
       </c>
       <c r="B181" s="10">
-        <v>46122</v>
+        <v>46106</v>
       </c>
       <c r="C181" s="11" t="s">
-        <v>118</v>
+        <v>94</v>
       </c>
       <c r="D181" s="9" t="s">
-        <v>119</v>
-      </c>
-      <c r="E181" s="8"/>
-      <c r="F181" s="14">
-        <v>1</v>
-      </c>
+        <v>95</v>
+      </c>
+      <c r="E181" s="12">
+        <v>2830136</v>
+      </c>
+      <c r="F181" s="8"/>
       <c r="G181" s="9" t="s">
         <v>26</v>
       </c>
@@ -6131,18 +6419,18 @@
         <v>23</v>
       </c>
       <c r="B182" s="10">
-        <v>46122</v>
+        <v>46106</v>
       </c>
       <c r="C182" s="11" t="s">
-        <v>118</v>
+        <v>96</v>
       </c>
       <c r="D182" s="9" t="s">
-        <v>119</v>
-      </c>
-      <c r="E182" s="8"/>
-      <c r="F182" s="14">
-        <v>1</v>
-      </c>
+        <v>97</v>
+      </c>
+      <c r="E182" s="12">
+        <v>24653171</v>
+      </c>
+      <c r="F182" s="8"/>
       <c r="G182" s="9" t="s">
         <v>26</v>
       </c>
@@ -6155,18 +6443,18 @@
         <v>23</v>
       </c>
       <c r="B183" s="10">
-        <v>46122</v>
+        <v>46106</v>
       </c>
       <c r="C183" s="11" t="s">
-        <v>118</v>
+        <v>96</v>
       </c>
       <c r="D183" s="9" t="s">
-        <v>119</v>
-      </c>
-      <c r="E183" s="8"/>
-      <c r="F183" s="14">
-        <v>9</v>
-      </c>
+        <v>97</v>
+      </c>
+      <c r="E183" s="12">
+        <v>30826833</v>
+      </c>
+      <c r="F183" s="8"/>
       <c r="G183" s="9" t="s">
         <v>26</v>
       </c>
@@ -6179,18 +6467,18 @@
         <v>23</v>
       </c>
       <c r="B184" s="10">
-        <v>46122</v>
+        <v>46106</v>
       </c>
       <c r="C184" s="11" t="s">
-        <v>118</v>
+        <v>96</v>
       </c>
       <c r="D184" s="9" t="s">
-        <v>119</v>
-      </c>
-      <c r="E184" s="8"/>
-      <c r="F184" s="14">
-        <v>2</v>
-      </c>
+        <v>97</v>
+      </c>
+      <c r="E184" s="12">
+        <v>31403986</v>
+      </c>
+      <c r="F184" s="8"/>
       <c r="G184" s="9" t="s">
         <v>26</v>
       </c>
@@ -6203,17 +6491,17 @@
         <v>23</v>
       </c>
       <c r="B185" s="10">
-        <v>46122</v>
+        <v>46107</v>
       </c>
       <c r="C185" s="11" t="s">
-        <v>118</v>
+        <v>98</v>
       </c>
       <c r="D185" s="9" t="s">
-        <v>119</v>
+        <v>99</v>
       </c>
       <c r="E185" s="8"/>
       <c r="F185" s="14">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G185" s="9" t="s">
         <v>26</v>
@@ -6227,18 +6515,18 @@
         <v>23</v>
       </c>
       <c r="B186" s="10">
-        <v>46122</v>
+        <v>46107</v>
       </c>
       <c r="C186" s="11" t="s">
-        <v>118</v>
+        <v>100</v>
       </c>
       <c r="D186" s="9" t="s">
-        <v>119</v>
-      </c>
-      <c r="E186" s="8"/>
-      <c r="F186" s="14">
-        <v>1</v>
-      </c>
+        <v>101</v>
+      </c>
+      <c r="E186" s="12">
+        <v>910617</v>
+      </c>
+      <c r="F186" s="8"/>
       <c r="G186" s="9" t="s">
         <v>26</v>
       </c>
@@ -6251,16 +6539,16 @@
         <v>23</v>
       </c>
       <c r="B187" s="10">
-        <v>46122</v>
+        <v>46108</v>
       </c>
       <c r="C187" s="11" t="s">
-        <v>120</v>
+        <v>102</v>
       </c>
       <c r="D187" s="9" t="s">
-        <v>114</v>
-      </c>
-      <c r="E187" s="14">
-        <v>3</v>
+        <v>103</v>
+      </c>
+      <c r="E187" s="12">
+        <v>9193198</v>
       </c>
       <c r="F187" s="8"/>
       <c r="G187" s="9" t="s">
@@ -6275,16 +6563,16 @@
         <v>23</v>
       </c>
       <c r="B188" s="10">
-        <v>46122</v>
+        <v>46108</v>
       </c>
       <c r="C188" s="11" t="s">
-        <v>120</v>
+        <v>104</v>
       </c>
       <c r="D188" s="9" t="s">
-        <v>114</v>
+        <v>105</v>
       </c>
       <c r="E188" s="14">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F188" s="8"/>
       <c r="G188" s="9" t="s">
@@ -6299,13 +6587,13 @@
         <v>23</v>
       </c>
       <c r="B189" s="10">
-        <v>46125</v>
+        <v>46108</v>
       </c>
       <c r="C189" s="11" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="D189" s="9" t="s">
-        <v>122</v>
+        <v>105</v>
       </c>
       <c r="E189" s="14">
         <v>1</v>
@@ -6323,16 +6611,16 @@
         <v>23</v>
       </c>
       <c r="B190" s="10">
-        <v>46125</v>
+        <v>46108</v>
       </c>
       <c r="C190" s="11" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="D190" s="9" t="s">
-        <v>122</v>
-      </c>
-      <c r="E190" s="12">
-        <v>3396163</v>
+        <v>105</v>
+      </c>
+      <c r="E190" s="14">
+        <v>3</v>
       </c>
       <c r="F190" s="8"/>
       <c r="G190" s="9" t="s">
@@ -6347,13 +6635,13 @@
         <v>23</v>
       </c>
       <c r="B191" s="10">
-        <v>46125</v>
+        <v>46108</v>
       </c>
       <c r="C191" s="11" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="D191" s="9" t="s">
-        <v>122</v>
+        <v>105</v>
       </c>
       <c r="E191" s="14">
         <v>2</v>
@@ -6371,16 +6659,16 @@
         <v>23</v>
       </c>
       <c r="B192" s="10">
-        <v>46125</v>
+        <v>46108</v>
       </c>
       <c r="C192" s="11" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="D192" s="9" t="s">
-        <v>122</v>
+        <v>105</v>
       </c>
       <c r="E192" s="14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F192" s="8"/>
       <c r="G192" s="9" t="s">
@@ -6395,16 +6683,16 @@
         <v>23</v>
       </c>
       <c r="B193" s="10">
-        <v>46125</v>
+        <v>46111</v>
       </c>
       <c r="C193" s="11" t="s">
-        <v>123</v>
+        <v>106</v>
       </c>
       <c r="D193" s="9" t="s">
-        <v>104</v>
-      </c>
-      <c r="E193" s="14">
-        <v>3</v>
+        <v>83</v>
+      </c>
+      <c r="E193" s="12">
+        <v>6536560</v>
       </c>
       <c r="F193" s="8"/>
       <c r="G193" s="9" t="s">
@@ -6419,16 +6707,16 @@
         <v>23</v>
       </c>
       <c r="B194" s="10">
-        <v>46134</v>
+        <v>46113</v>
       </c>
       <c r="C194" s="11" t="s">
-        <v>124</v>
+        <v>107</v>
       </c>
       <c r="D194" s="9" t="s">
-        <v>101</v>
+        <v>108</v>
       </c>
       <c r="E194" s="12">
-        <v>408600</v>
+        <v>337134</v>
       </c>
       <c r="F194" s="8"/>
       <c r="G194" s="9" t="s">
@@ -6443,16 +6731,16 @@
         <v>23</v>
       </c>
       <c r="B195" s="10">
-        <v>46134</v>
+        <v>46114</v>
       </c>
       <c r="C195" s="11" t="s">
-        <v>124</v>
+        <v>109</v>
       </c>
       <c r="D195" s="9" t="s">
-        <v>101</v>
+        <v>108</v>
       </c>
       <c r="E195" s="12">
-        <v>4553086</v>
+        <v>910617</v>
       </c>
       <c r="F195" s="8"/>
       <c r="G195" s="9" t="s">
@@ -6467,16 +6755,16 @@
         <v>23</v>
       </c>
       <c r="B196" s="10">
-        <v>46134</v>
+        <v>46118</v>
       </c>
       <c r="C196" s="11" t="s">
-        <v>124</v>
+        <v>110</v>
       </c>
       <c r="D196" s="9" t="s">
-        <v>101</v>
+        <v>111</v>
       </c>
       <c r="E196" s="12">
-        <v>994207</v>
+        <v>1080600</v>
       </c>
       <c r="F196" s="8"/>
       <c r="G196" s="9" t="s">
@@ -6491,16 +6779,16 @@
         <v>23</v>
       </c>
       <c r="B197" s="10">
-        <v>46134</v>
+        <v>46118</v>
       </c>
       <c r="C197" s="11" t="s">
-        <v>124</v>
+        <v>110</v>
       </c>
       <c r="D197" s="9" t="s">
-        <v>101</v>
-      </c>
-      <c r="E197" s="14">
-        <v>3</v>
+        <v>111</v>
+      </c>
+      <c r="E197" s="12">
+        <v>972439</v>
       </c>
       <c r="F197" s="8"/>
       <c r="G197" s="9" t="s">
@@ -6515,16 +6803,16 @@
         <v>23</v>
       </c>
       <c r="B198" s="10">
-        <v>46134</v>
+        <v>46118</v>
       </c>
       <c r="C198" s="11" t="s">
-        <v>124</v>
+        <v>110</v>
       </c>
       <c r="D198" s="9" t="s">
-        <v>101</v>
-      </c>
-      <c r="E198" s="14">
-        <v>2</v>
+        <v>111</v>
+      </c>
+      <c r="E198" s="12">
+        <v>110704</v>
       </c>
       <c r="F198" s="8"/>
       <c r="G198" s="9" t="s">
@@ -6539,16 +6827,16 @@
         <v>23</v>
       </c>
       <c r="B199" s="10">
-        <v>46134</v>
+        <v>46118</v>
       </c>
       <c r="C199" s="11" t="s">
-        <v>124</v>
+        <v>110</v>
       </c>
       <c r="D199" s="9" t="s">
-        <v>101</v>
+        <v>111</v>
       </c>
       <c r="E199" s="12">
-        <v>655148</v>
+        <v>2458715</v>
       </c>
       <c r="F199" s="8"/>
       <c r="G199" s="9" t="s">
@@ -6563,16 +6851,16 @@
         <v>23</v>
       </c>
       <c r="B200" s="10">
-        <v>46134</v>
+        <v>46118</v>
       </c>
       <c r="C200" s="11" t="s">
-        <v>124</v>
+        <v>110</v>
       </c>
       <c r="D200" s="9" t="s">
-        <v>101</v>
+        <v>111</v>
       </c>
       <c r="E200" s="12">
-        <v>553912</v>
+        <v>1667891</v>
       </c>
       <c r="F200" s="8"/>
       <c r="G200" s="9" t="s">
@@ -6587,16 +6875,16 @@
         <v>23</v>
       </c>
       <c r="B201" s="10">
-        <v>46134</v>
+        <v>46118</v>
       </c>
       <c r="C201" s="11" t="s">
-        <v>124</v>
+        <v>110</v>
       </c>
       <c r="D201" s="9" t="s">
-        <v>101</v>
-      </c>
-      <c r="E201" s="14">
-        <v>3</v>
+        <v>111</v>
+      </c>
+      <c r="E201" s="12">
+        <v>1132054</v>
       </c>
       <c r="F201" s="8"/>
       <c r="G201" s="9" t="s">
@@ -6611,18 +6899,18 @@
         <v>23</v>
       </c>
       <c r="B202" s="10">
-        <v>46136</v>
+        <v>46120</v>
       </c>
       <c r="C202" s="11" t="s">
-        <v>125</v>
+        <v>112</v>
       </c>
       <c r="D202" s="9" t="s">
-        <v>126</v>
-      </c>
-      <c r="E202" s="8"/>
-      <c r="F202" s="14">
-        <v>1</v>
-      </c>
+        <v>113</v>
+      </c>
+      <c r="E202" s="12">
+        <v>8853834</v>
+      </c>
+      <c r="F202" s="8"/>
       <c r="G202" s="9" t="s">
         <v>26</v>
       </c>
@@ -6635,18 +6923,18 @@
         <v>23</v>
       </c>
       <c r="B203" s="10">
-        <v>46140</v>
+        <v>46120</v>
       </c>
       <c r="C203" s="11" t="s">
-        <v>127</v>
+        <v>114</v>
       </c>
       <c r="D203" s="9" t="s">
-        <v>128</v>
-      </c>
-      <c r="E203" s="8"/>
-      <c r="F203" s="14">
-        <v>2</v>
-      </c>
+        <v>115</v>
+      </c>
+      <c r="E203" s="12">
+        <v>51552815</v>
+      </c>
+      <c r="F203" s="8"/>
       <c r="G203" s="9" t="s">
         <v>26</v>
       </c>
@@ -6659,18 +6947,18 @@
         <v>23</v>
       </c>
       <c r="B204" s="10">
-        <v>46140</v>
+        <v>46120</v>
       </c>
       <c r="C204" s="11" t="s">
-        <v>127</v>
+        <v>116</v>
       </c>
       <c r="D204" s="9" t="s">
-        <v>128</v>
-      </c>
-      <c r="E204" s="8"/>
-      <c r="F204" s="14">
-        <v>1</v>
-      </c>
+        <v>111</v>
+      </c>
+      <c r="E204" s="12">
+        <v>910617</v>
+      </c>
+      <c r="F204" s="8"/>
       <c r="G204" s="9" t="s">
         <v>26</v>
       </c>
@@ -6683,18 +6971,18 @@
         <v>23</v>
       </c>
       <c r="B205" s="10">
-        <v>46140</v>
+        <v>46120</v>
       </c>
       <c r="C205" s="11" t="s">
-        <v>127</v>
+        <v>117</v>
       </c>
       <c r="D205" s="9" t="s">
-        <v>128</v>
-      </c>
-      <c r="E205" s="8"/>
-      <c r="F205" s="14">
-        <v>1</v>
-      </c>
+        <v>115</v>
+      </c>
+      <c r="E205" s="14">
+        <v>3</v>
+      </c>
+      <c r="F205" s="8"/>
       <c r="G205" s="9" t="s">
         <v>26</v>
       </c>
@@ -6707,18 +6995,18 @@
         <v>23</v>
       </c>
       <c r="B206" s="10">
-        <v>46140</v>
+        <v>46120</v>
       </c>
       <c r="C206" s="11" t="s">
-        <v>127</v>
+        <v>117</v>
       </c>
       <c r="D206" s="9" t="s">
-        <v>128</v>
-      </c>
-      <c r="E206" s="8"/>
-      <c r="F206" s="14">
-        <v>3</v>
-      </c>
+        <v>115</v>
+      </c>
+      <c r="E206" s="14">
+        <v>2</v>
+      </c>
+      <c r="F206" s="8"/>
       <c r="G206" s="9" t="s">
         <v>26</v>
       </c>
@@ -6731,18 +7019,18 @@
         <v>23</v>
       </c>
       <c r="B207" s="10">
-        <v>46140</v>
+        <v>46120</v>
       </c>
       <c r="C207" s="11" t="s">
-        <v>129</v>
+        <v>117</v>
       </c>
       <c r="D207" s="9" t="s">
-        <v>128</v>
-      </c>
-      <c r="E207" s="8"/>
-      <c r="F207" s="14">
-        <v>1</v>
-      </c>
+        <v>115</v>
+      </c>
+      <c r="E207" s="14">
+        <v>3</v>
+      </c>
+      <c r="F207" s="8"/>
       <c r="G207" s="9" t="s">
         <v>26</v>
       </c>
@@ -6755,204 +7043,330 @@
         <v>23</v>
       </c>
       <c r="B208" s="10">
-        <v>46140</v>
+        <v>46120</v>
       </c>
       <c r="C208" s="11" t="s">
-        <v>129</v>
+        <v>118</v>
       </c>
       <c r="D208" s="9" t="s">
-        <v>128</v>
-      </c>
-      <c r="E208" s="8"/>
-      <c r="F208" s="14">
+        <v>115</v>
+      </c>
+      <c r="E208" s="12">
+        <v>10467995</v>
+      </c>
+      <c r="F208" s="8"/>
+      <c r="G208" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="H208" s="9" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="209" spans="1:8" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A209" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="B209" s="10">
+        <v>46120</v>
+      </c>
+      <c r="C209" s="11" t="s">
+        <v>118</v>
+      </c>
+      <c r="D209" s="9" t="s">
+        <v>115</v>
+      </c>
+      <c r="E209" s="14">
+        <v>15</v>
+      </c>
+      <c r="F209" s="8"/>
+      <c r="G209" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="H209" s="9" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="210" spans="1:8" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A210" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="B210" s="10">
+        <v>46120</v>
+      </c>
+      <c r="C210" s="11" t="s">
+        <v>119</v>
+      </c>
+      <c r="D210" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="E210" s="12">
+        <v>2243711</v>
+      </c>
+      <c r="F210" s="8"/>
+      <c r="G210" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="H210" s="9" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="211" spans="1:8" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A211" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="B211" s="10">
+        <v>46121</v>
+      </c>
+      <c r="C211" s="11" t="s">
+        <v>120</v>
+      </c>
+      <c r="D211" s="9" t="s">
+        <v>121</v>
+      </c>
+      <c r="E211" s="14">
+        <v>3</v>
+      </c>
+      <c r="F211" s="8"/>
+      <c r="G211" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="H211" s="9" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="212" spans="1:8" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A212" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="B212" s="10">
+        <v>46121</v>
+      </c>
+      <c r="C212" s="11" t="s">
+        <v>120</v>
+      </c>
+      <c r="D212" s="9" t="s">
+        <v>121</v>
+      </c>
+      <c r="E212" s="14">
+        <v>12</v>
+      </c>
+      <c r="F212" s="8"/>
+      <c r="G212" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="H212" s="9" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="213" spans="1:8" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A213" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="B213" s="10">
+        <v>46121</v>
+      </c>
+      <c r="C213" s="11" t="s">
+        <v>122</v>
+      </c>
+      <c r="D213" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="E213" s="12">
+        <v>2991580</v>
+      </c>
+      <c r="F213" s="8"/>
+      <c r="G213" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="H213" s="9" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="214" spans="1:8" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A214" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="B214" s="10">
+        <v>46121</v>
+      </c>
+      <c r="C214" s="11" t="s">
+        <v>123</v>
+      </c>
+      <c r="D214" s="9" t="s">
+        <v>124</v>
+      </c>
+      <c r="E214" s="12">
+        <v>2243711</v>
+      </c>
+      <c r="F214" s="8"/>
+      <c r="G214" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="H214" s="9" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="215" spans="1:8" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A215" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="B215" s="10">
+        <v>46122</v>
+      </c>
+      <c r="C215" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="D215" s="9" t="s">
+        <v>126</v>
+      </c>
+      <c r="E215" s="8"/>
+      <c r="F215" s="14">
+        <v>3</v>
+      </c>
+      <c r="G215" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="H215" s="9" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="216" spans="1:8" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A216" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="B216" s="10">
+        <v>46122</v>
+      </c>
+      <c r="C216" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="D216" s="9" t="s">
+        <v>126</v>
+      </c>
+      <c r="E216" s="8"/>
+      <c r="F216" s="14">
         <v>1</v>
       </c>
-      <c r="G208" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="H208" s="9" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="209" spans="1:8" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A209" s="26" t="s">
-        <v>30</v>
-      </c>
-      <c r="B209" s="27"/>
-      <c r="C209" s="27"/>
-      <c r="D209" s="28"/>
-      <c r="E209" s="13">
-        <v>1475408160</v>
-      </c>
-      <c r="F209" s="13">
-        <v>29678782</v>
-      </c>
-      <c r="G209" s="7"/>
-      <c r="H209" s="7"/>
-    </row>
-    <row r="210" spans="1:8" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A210" s="26" t="s">
-        <v>31</v>
-      </c>
-      <c r="B210" s="27"/>
-      <c r="C210" s="27"/>
-      <c r="D210" s="28"/>
-      <c r="E210" s="13">
-        <v>1445729378</v>
-      </c>
-      <c r="F210" s="7"/>
-      <c r="G210" s="7"/>
-      <c r="H210" s="7"/>
-    </row>
-    <row r="211" spans="1:8" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A211" s="26" t="s">
-        <v>32</v>
-      </c>
-      <c r="B211" s="27"/>
-      <c r="C211" s="27"/>
-      <c r="D211" s="28"/>
-      <c r="E211" s="7"/>
-      <c r="F211" s="7"/>
-      <c r="G211" s="7"/>
-      <c r="H211" s="7"/>
-    </row>
-    <row r="212" spans="1:8" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A212" s="26" t="s">
-        <v>33</v>
-      </c>
-      <c r="B212" s="27"/>
-      <c r="C212" s="27"/>
-      <c r="D212" s="28"/>
-      <c r="E212" s="13">
-        <v>1475408160</v>
-      </c>
-      <c r="F212" s="13">
-        <v>29678782</v>
-      </c>
-      <c r="G212" s="7"/>
-      <c r="H212" s="7"/>
-    </row>
-    <row r="213" spans="1:8" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A213" s="26" t="s">
-        <v>34</v>
-      </c>
-      <c r="B213" s="27"/>
-      <c r="C213" s="27"/>
-      <c r="D213" s="28"/>
-      <c r="E213" s="13">
-        <v>1445729378</v>
-      </c>
-      <c r="F213" s="7"/>
-      <c r="G213" s="7"/>
-      <c r="H213" s="7"/>
-    </row>
-    <row r="214" spans="1:8" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A214" s="26" t="s">
-        <v>35</v>
-      </c>
-      <c r="B214" s="27"/>
-      <c r="C214" s="27"/>
-      <c r="D214" s="28"/>
-      <c r="E214" s="7"/>
-      <c r="F214" s="7"/>
-      <c r="G214" s="7"/>
-      <c r="H214" s="7"/>
-    </row>
-    <row r="215" spans="1:8" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A215" s="26" t="s">
-        <v>36</v>
-      </c>
-      <c r="B215" s="27"/>
-      <c r="C215" s="27"/>
-      <c r="D215" s="28"/>
-      <c r="E215" s="13">
-        <v>1475408160</v>
-      </c>
-      <c r="F215" s="13">
-        <v>29678782</v>
-      </c>
-      <c r="G215" s="7"/>
-      <c r="H215" s="7"/>
-    </row>
-    <row r="216" spans="1:8" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A216" s="26" t="s">
-        <v>37</v>
-      </c>
-      <c r="B216" s="27"/>
-      <c r="C216" s="27"/>
-      <c r="D216" s="28"/>
-      <c r="E216" s="13">
-        <v>1445729378</v>
-      </c>
-      <c r="F216" s="7"/>
-      <c r="G216" s="7"/>
-      <c r="H216" s="7"/>
-    </row>
-    <row r="217" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A217" s="21" t="s">
-        <v>130</v>
-      </c>
-      <c r="B217" s="22"/>
-      <c r="C217" s="22"/>
-      <c r="D217" s="22"/>
-      <c r="E217" s="22"/>
-      <c r="F217" s="22"/>
-      <c r="G217" s="22"/>
-      <c r="H217" s="23"/>
-    </row>
-    <row r="218" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A218" s="21" t="s">
-        <v>131</v>
-      </c>
-      <c r="B218" s="22"/>
-      <c r="C218" s="22"/>
-      <c r="D218" s="22"/>
-      <c r="E218" s="22"/>
-      <c r="F218" s="22"/>
-      <c r="G218" s="22"/>
-      <c r="H218" s="23"/>
-    </row>
-    <row r="219" spans="1:8" ht="18.149999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A219" s="21" t="s">
-        <v>40</v>
-      </c>
-      <c r="B219" s="22"/>
-      <c r="C219" s="22"/>
-      <c r="D219" s="22"/>
-      <c r="E219" s="22"/>
-      <c r="F219" s="22"/>
-      <c r="G219" s="22"/>
-      <c r="H219" s="23"/>
+      <c r="G216" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="H216" s="9" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="217" spans="1:8" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A217" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="B217" s="10">
+        <v>46122</v>
+      </c>
+      <c r="C217" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="D217" s="9" t="s">
+        <v>126</v>
+      </c>
+      <c r="E217" s="8"/>
+      <c r="F217" s="14">
+        <v>2</v>
+      </c>
+      <c r="G217" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="H217" s="9" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="218" spans="1:8" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A218" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="B218" s="10">
+        <v>46122</v>
+      </c>
+      <c r="C218" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="D218" s="9" t="s">
+        <v>126</v>
+      </c>
+      <c r="E218" s="8"/>
+      <c r="F218" s="14">
+        <v>3</v>
+      </c>
+      <c r="G218" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="H218" s="9" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="219" spans="1:8" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A219" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="B219" s="10">
+        <v>46122</v>
+      </c>
+      <c r="C219" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="D219" s="9" t="s">
+        <v>126</v>
+      </c>
+      <c r="E219" s="8"/>
+      <c r="F219" s="14">
+        <v>9</v>
+      </c>
+      <c r="G219" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="H219" s="9" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="220" spans="1:8" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A220" s="26" t="s">
-        <v>22</v>
-      </c>
-      <c r="B220" s="27"/>
-      <c r="C220" s="27"/>
-      <c r="D220" s="28"/>
-      <c r="E220" s="7"/>
-      <c r="F220" s="7"/>
-      <c r="G220" s="7"/>
-      <c r="H220" s="7"/>
+      <c r="A220" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="B220" s="10">
+        <v>46122</v>
+      </c>
+      <c r="C220" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="D220" s="9" t="s">
+        <v>126</v>
+      </c>
+      <c r="E220" s="8"/>
+      <c r="F220" s="14">
+        <v>1</v>
+      </c>
+      <c r="G220" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="H220" s="9" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="221" spans="1:8" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A221" s="9" t="s">
         <v>23</v>
       </c>
       <c r="B221" s="10">
-        <v>46136</v>
+        <v>46122</v>
       </c>
       <c r="C221" s="11" t="s">
-        <v>132</v>
+        <v>125</v>
       </c>
       <c r="D221" s="9" t="s">
-        <v>133</v>
-      </c>
-      <c r="E221" s="12">
-        <v>138000</v>
-      </c>
-      <c r="F221" s="8"/>
+        <v>126</v>
+      </c>
+      <c r="E221" s="8"/>
+      <c r="F221" s="14">
+        <v>1</v>
+      </c>
       <c r="G221" s="9" t="s">
         <v>26</v>
       </c>
@@ -6965,16 +7379,16 @@
         <v>23</v>
       </c>
       <c r="B222" s="10">
-        <v>46136</v>
+        <v>46122</v>
       </c>
       <c r="C222" s="11" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="D222" s="9" t="s">
-        <v>133</v>
-      </c>
-      <c r="E222" s="12">
-        <v>1557808</v>
+        <v>121</v>
+      </c>
+      <c r="E222" s="14">
+        <v>3</v>
       </c>
       <c r="F222" s="8"/>
       <c r="G222" s="9" t="s">
@@ -6989,16 +7403,16 @@
         <v>23</v>
       </c>
       <c r="B223" s="10">
-        <v>46136</v>
+        <v>46122</v>
       </c>
       <c r="C223" s="11" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="D223" s="9" t="s">
-        <v>133</v>
-      </c>
-      <c r="E223" s="12">
-        <v>617400</v>
+        <v>121</v>
+      </c>
+      <c r="E223" s="14">
+        <v>1</v>
       </c>
       <c r="F223" s="8"/>
       <c r="G223" s="9" t="s">
@@ -7013,16 +7427,16 @@
         <v>23</v>
       </c>
       <c r="B224" s="10">
-        <v>46136</v>
+        <v>46125</v>
       </c>
       <c r="C224" s="11" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="D224" s="9" t="s">
-        <v>133</v>
-      </c>
-      <c r="E224" s="12">
-        <v>3307500</v>
+        <v>129</v>
+      </c>
+      <c r="E224" s="14">
+        <v>4</v>
       </c>
       <c r="F224" s="8"/>
       <c r="G224" s="9" t="s">
@@ -7037,16 +7451,16 @@
         <v>23</v>
       </c>
       <c r="B225" s="10">
-        <v>46136</v>
+        <v>46125</v>
       </c>
       <c r="C225" s="11" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="D225" s="9" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="E225" s="12">
-        <v>18021675</v>
+        <v>3396163</v>
       </c>
       <c r="F225" s="8"/>
       <c r="G225" s="9" t="s">
@@ -7061,16 +7475,16 @@
         <v>23</v>
       </c>
       <c r="B226" s="10">
-        <v>46136</v>
+        <v>46125</v>
       </c>
       <c r="C226" s="11" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="D226" s="9" t="s">
-        <v>133</v>
-      </c>
-      <c r="E226" s="12">
-        <v>800232</v>
+        <v>129</v>
+      </c>
+      <c r="E226" s="14">
+        <v>1</v>
       </c>
       <c r="F226" s="8"/>
       <c r="G226" s="9" t="s">
@@ -7085,16 +7499,16 @@
         <v>23</v>
       </c>
       <c r="B227" s="10">
-        <v>46136</v>
+        <v>46125</v>
       </c>
       <c r="C227" s="11" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="D227" s="9" t="s">
-        <v>133</v>
-      </c>
-      <c r="E227" s="12">
-        <v>4445278</v>
+        <v>129</v>
+      </c>
+      <c r="E227" s="14">
+        <v>2</v>
       </c>
       <c r="F227" s="8"/>
       <c r="G227" s="9" t="s">
@@ -7109,16 +7523,16 @@
         <v>23</v>
       </c>
       <c r="B228" s="10">
-        <v>46136</v>
+        <v>46125</v>
       </c>
       <c r="C228" s="11" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="D228" s="9" t="s">
-        <v>133</v>
-      </c>
-      <c r="E228" s="12">
-        <v>28173630</v>
+        <v>111</v>
+      </c>
+      <c r="E228" s="14">
+        <v>3</v>
       </c>
       <c r="F228" s="8"/>
       <c r="G228" s="9" t="s">
@@ -7133,16 +7547,16 @@
         <v>23</v>
       </c>
       <c r="B229" s="10">
-        <v>46136</v>
+        <v>46134</v>
       </c>
       <c r="C229" s="11" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D229" s="9" t="s">
-        <v>133</v>
-      </c>
-      <c r="E229" s="12">
-        <v>23503565</v>
+        <v>108</v>
+      </c>
+      <c r="E229" s="14">
+        <v>3</v>
       </c>
       <c r="F229" s="8"/>
       <c r="G229" s="9" t="s">
@@ -7157,16 +7571,16 @@
         <v>23</v>
       </c>
       <c r="B230" s="10">
-        <v>46141</v>
+        <v>46134</v>
       </c>
       <c r="C230" s="11" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="D230" s="9" t="s">
-        <v>135</v>
+        <v>108</v>
       </c>
       <c r="E230" s="12">
-        <v>20596200</v>
+        <v>994207</v>
       </c>
       <c r="F230" s="8"/>
       <c r="G230" s="9" t="s">
@@ -7181,16 +7595,16 @@
         <v>23</v>
       </c>
       <c r="B231" s="10">
-        <v>46141</v>
+        <v>46134</v>
       </c>
       <c r="C231" s="11" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="D231" s="9" t="s">
-        <v>135</v>
-      </c>
-      <c r="E231" s="12">
-        <v>3780000</v>
+        <v>108</v>
+      </c>
+      <c r="E231" s="14">
+        <v>3</v>
       </c>
       <c r="F231" s="8"/>
       <c r="G231" s="9" t="s">
@@ -7205,16 +7619,16 @@
         <v>23</v>
       </c>
       <c r="B232" s="10">
-        <v>46141</v>
+        <v>46134</v>
       </c>
       <c r="C232" s="11" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="D232" s="9" t="s">
-        <v>135</v>
+        <v>108</v>
       </c>
       <c r="E232" s="12">
-        <v>705600</v>
+        <v>655148</v>
       </c>
       <c r="F232" s="8"/>
       <c r="G232" s="9" t="s">
@@ -7229,16 +7643,16 @@
         <v>23</v>
       </c>
       <c r="B233" s="10">
-        <v>46141</v>
+        <v>46134</v>
       </c>
       <c r="C233" s="11" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="D233" s="9" t="s">
-        <v>135</v>
+        <v>108</v>
       </c>
       <c r="E233" s="12">
-        <v>5080318</v>
+        <v>4553086</v>
       </c>
       <c r="F233" s="8"/>
       <c r="G233" s="9" t="s">
@@ -7253,16 +7667,16 @@
         <v>23</v>
       </c>
       <c r="B234" s="10">
-        <v>46141</v>
+        <v>46134</v>
       </c>
       <c r="C234" s="11" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="D234" s="9" t="s">
-        <v>135</v>
+        <v>108</v>
       </c>
       <c r="E234" s="12">
-        <v>1780352</v>
+        <v>408600</v>
       </c>
       <c r="F234" s="8"/>
       <c r="G234" s="9" t="s">
@@ -7277,16 +7691,16 @@
         <v>23</v>
       </c>
       <c r="B235" s="10">
-        <v>46141</v>
+        <v>46134</v>
       </c>
       <c r="C235" s="11" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="D235" s="9" t="s">
-        <v>135</v>
+        <v>108</v>
       </c>
       <c r="E235" s="12">
-        <v>800232</v>
+        <v>553912</v>
       </c>
       <c r="F235" s="8"/>
       <c r="G235" s="9" t="s">
@@ -7301,16 +7715,16 @@
         <v>23</v>
       </c>
       <c r="B236" s="10">
-        <v>46141</v>
+        <v>46134</v>
       </c>
       <c r="C236" s="11" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="D236" s="9" t="s">
-        <v>135</v>
-      </c>
-      <c r="E236" s="12">
-        <v>527987</v>
+        <v>108</v>
+      </c>
+      <c r="E236" s="14">
+        <v>2</v>
       </c>
       <c r="F236" s="8"/>
       <c r="G236" s="9" t="s">
@@ -7325,18 +7739,18 @@
         <v>23</v>
       </c>
       <c r="B237" s="10">
-        <v>46141</v>
+        <v>46136</v>
       </c>
       <c r="C237" s="11" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="D237" s="9" t="s">
-        <v>135</v>
-      </c>
-      <c r="E237" s="12">
-        <v>32198434</v>
-      </c>
-      <c r="F237" s="8"/>
+        <v>133</v>
+      </c>
+      <c r="E237" s="8"/>
+      <c r="F237" s="14">
+        <v>1</v>
+      </c>
       <c r="G237" s="9" t="s">
         <v>26</v>
       </c>
@@ -7349,7 +7763,7 @@
         <v>23</v>
       </c>
       <c r="B238" s="10">
-        <v>46141</v>
+        <v>46140</v>
       </c>
       <c r="C238" s="11" t="s">
         <v>134</v>
@@ -7357,10 +7771,10 @@
       <c r="D238" s="9" t="s">
         <v>135</v>
       </c>
-      <c r="E238" s="12">
-        <v>26446116</v>
-      </c>
-      <c r="F238" s="8"/>
+      <c r="E238" s="8"/>
+      <c r="F238" s="14">
+        <v>3</v>
+      </c>
       <c r="G238" s="9" t="s">
         <v>26</v>
       </c>
@@ -7369,100 +7783,168 @@
       </c>
     </row>
     <row r="239" spans="1:8" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A239" s="26" t="s">
-        <v>30</v>
-      </c>
-      <c r="B239" s="27"/>
-      <c r="C239" s="27"/>
-      <c r="D239" s="28"/>
-      <c r="E239" s="13">
-        <v>172480327</v>
-      </c>
-      <c r="F239" s="7"/>
-      <c r="G239" s="7"/>
-      <c r="H239" s="7"/>
+      <c r="A239" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="B239" s="10">
+        <v>46140</v>
+      </c>
+      <c r="C239" s="11" t="s">
+        <v>134</v>
+      </c>
+      <c r="D239" s="9" t="s">
+        <v>135</v>
+      </c>
+      <c r="E239" s="8"/>
+      <c r="F239" s="14">
+        <v>1</v>
+      </c>
+      <c r="G239" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="H239" s="9" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="240" spans="1:8" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A240" s="26" t="s">
-        <v>31</v>
-      </c>
-      <c r="B240" s="27"/>
-      <c r="C240" s="27"/>
-      <c r="D240" s="28"/>
-      <c r="E240" s="13">
-        <v>172480327</v>
-      </c>
-      <c r="F240" s="7"/>
-      <c r="G240" s="7"/>
-      <c r="H240" s="7"/>
-    </row>
-    <row r="241" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A241" s="21" t="s">
-        <v>19</v>
-      </c>
-      <c r="B241" s="22"/>
-      <c r="C241" s="22"/>
-      <c r="D241" s="22"/>
-      <c r="E241" s="22"/>
-      <c r="F241" s="22"/>
-      <c r="G241" s="22"/>
-      <c r="H241" s="23"/>
+      <c r="A240" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="B240" s="10">
+        <v>46140</v>
+      </c>
+      <c r="C240" s="11" t="s">
+        <v>134</v>
+      </c>
+      <c r="D240" s="9" t="s">
+        <v>135</v>
+      </c>
+      <c r="E240" s="8"/>
+      <c r="F240" s="14">
+        <v>1</v>
+      </c>
+      <c r="G240" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="H240" s="9" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="241" spans="1:8" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A241" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="B241" s="10">
+        <v>46140</v>
+      </c>
+      <c r="C241" s="11" t="s">
+        <v>134</v>
+      </c>
+      <c r="D241" s="9" t="s">
+        <v>135</v>
+      </c>
+      <c r="E241" s="8"/>
+      <c r="F241" s="14">
+        <v>2</v>
+      </c>
+      <c r="G241" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="H241" s="9" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="242" spans="1:8" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A242" s="21" t="s">
-        <v>20</v>
-      </c>
-      <c r="B242" s="22"/>
-      <c r="C242" s="22"/>
-      <c r="D242" s="22"/>
-      <c r="E242" s="22"/>
-      <c r="F242" s="22"/>
-      <c r="G242" s="22"/>
-      <c r="H242" s="23"/>
-    </row>
-    <row r="243" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A243" s="21" t="s">
-        <v>21</v>
-      </c>
-      <c r="B243" s="22"/>
-      <c r="C243" s="22"/>
-      <c r="D243" s="22"/>
-      <c r="E243" s="22"/>
-      <c r="F243" s="22"/>
-      <c r="G243" s="22"/>
-      <c r="H243" s="23"/>
-    </row>
-    <row r="244" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A244" s="26" t="s">
-        <v>22</v>
-      </c>
-      <c r="B244" s="27"/>
-      <c r="C244" s="27"/>
-      <c r="D244" s="28"/>
-      <c r="E244" s="7"/>
-      <c r="F244" s="7"/>
-      <c r="G244" s="7"/>
-      <c r="H244" s="7"/>
+      <c r="A242" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="B242" s="10">
+        <v>46140</v>
+      </c>
+      <c r="C242" s="11" t="s">
+        <v>136</v>
+      </c>
+      <c r="D242" s="9" t="s">
+        <v>135</v>
+      </c>
+      <c r="E242" s="8"/>
+      <c r="F242" s="14">
+        <v>1</v>
+      </c>
+      <c r="G242" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="H242" s="9" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="243" spans="1:8" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A243" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="B243" s="10">
+        <v>46140</v>
+      </c>
+      <c r="C243" s="11" t="s">
+        <v>136</v>
+      </c>
+      <c r="D243" s="9" t="s">
+        <v>135</v>
+      </c>
+      <c r="E243" s="8"/>
+      <c r="F243" s="14">
+        <v>1</v>
+      </c>
+      <c r="G243" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="H243" s="9" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="244" spans="1:8" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A244" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="B244" s="10">
+        <v>46146</v>
+      </c>
+      <c r="C244" s="11" t="s">
+        <v>137</v>
+      </c>
+      <c r="D244" s="9" t="s">
+        <v>138</v>
+      </c>
+      <c r="E244" s="14">
+        <v>6</v>
+      </c>
+      <c r="F244" s="8"/>
+      <c r="G244" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="H244" s="9" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="245" spans="1:8" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A245" s="9" t="s">
         <v>23</v>
       </c>
       <c r="B245" s="10">
-        <v>46141</v>
+        <v>46146</v>
       </c>
       <c r="C245" s="11" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="D245" s="9" t="s">
-        <v>25</v>
+        <v>138</v>
       </c>
       <c r="E245" s="12">
-        <v>280600</v>
+        <v>1945873</v>
       </c>
       <c r="F245" s="8"/>
       <c r="G245" s="9" t="s">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="H245" s="9" t="s">
         <v>27</v>
@@ -7473,263 +7955,2103 @@
         <v>23</v>
       </c>
       <c r="B246" s="10">
-        <v>46141</v>
+        <v>46146</v>
       </c>
       <c r="C246" s="11" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="D246" s="9" t="s">
-        <v>25</v>
+        <v>138</v>
       </c>
       <c r="E246" s="12">
-        <v>5617204</v>
+        <v>1981095</v>
       </c>
       <c r="F246" s="8"/>
       <c r="G246" s="9" t="s">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="H246" s="9" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="247" spans="1:8" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A247" s="26" t="s">
-        <v>30</v>
-      </c>
-      <c r="B247" s="27"/>
-      <c r="C247" s="27"/>
-      <c r="D247" s="28"/>
-      <c r="E247" s="13">
-        <v>5897804</v>
-      </c>
-      <c r="F247" s="7"/>
-      <c r="G247" s="7"/>
-      <c r="H247" s="7"/>
+      <c r="A247" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="B247" s="10">
+        <v>46146</v>
+      </c>
+      <c r="C247" s="11" t="s">
+        <v>137</v>
+      </c>
+      <c r="D247" s="9" t="s">
+        <v>138</v>
+      </c>
+      <c r="E247" s="12">
+        <v>1778362</v>
+      </c>
+      <c r="F247" s="8"/>
+      <c r="G247" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="H247" s="9" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="248" spans="1:8" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A248" s="26" t="s">
-        <v>31</v>
-      </c>
-      <c r="B248" s="27"/>
-      <c r="C248" s="27"/>
-      <c r="D248" s="28"/>
-      <c r="E248" s="13">
-        <v>5897804</v>
-      </c>
-      <c r="F248" s="7"/>
-      <c r="G248" s="7"/>
-      <c r="H248" s="7"/>
+      <c r="A248" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="B248" s="10">
+        <v>46146</v>
+      </c>
+      <c r="C248" s="11" t="s">
+        <v>137</v>
+      </c>
+      <c r="D248" s="9" t="s">
+        <v>138</v>
+      </c>
+      <c r="E248" s="14">
+        <v>6</v>
+      </c>
+      <c r="F248" s="8"/>
+      <c r="G248" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="H248" s="9" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="249" spans="1:8" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A249" s="26" t="s">
-        <v>32</v>
-      </c>
-      <c r="B249" s="27"/>
-      <c r="C249" s="27"/>
-      <c r="D249" s="28"/>
-      <c r="E249" s="7"/>
-      <c r="F249" s="7"/>
-      <c r="G249" s="7"/>
-      <c r="H249" s="7"/>
+      <c r="A249" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="B249" s="10">
+        <v>46146</v>
+      </c>
+      <c r="C249" s="11" t="s">
+        <v>137</v>
+      </c>
+      <c r="D249" s="9" t="s">
+        <v>138</v>
+      </c>
+      <c r="E249" s="12">
+        <v>235791</v>
+      </c>
+      <c r="F249" s="8"/>
+      <c r="G249" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="H249" s="9" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="250" spans="1:8" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A250" s="26" t="s">
+      <c r="A250" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="B250" s="10">
+        <v>46146</v>
+      </c>
+      <c r="C250" s="11" t="s">
+        <v>137</v>
+      </c>
+      <c r="D250" s="9" t="s">
+        <v>138</v>
+      </c>
+      <c r="E250" s="14">
+        <v>3</v>
+      </c>
+      <c r="F250" s="8"/>
+      <c r="G250" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="B250" s="27"/>
-      <c r="C250" s="27"/>
-      <c r="D250" s="28"/>
-      <c r="E250" s="13">
-        <v>178378131</v>
-      </c>
-      <c r="F250" s="7"/>
-      <c r="G250" s="7"/>
-      <c r="H250" s="7"/>
+      <c r="H250" s="9" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="251" spans="1:8" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A251" s="26" t="s">
-        <v>34</v>
-      </c>
-      <c r="B251" s="27"/>
-      <c r="C251" s="27"/>
-      <c r="D251" s="28"/>
-      <c r="E251" s="13">
-        <v>178378131</v>
-      </c>
-      <c r="F251" s="7"/>
-      <c r="G251" s="7"/>
-      <c r="H251" s="7"/>
+      <c r="A251" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="B251" s="10">
+        <v>46148</v>
+      </c>
+      <c r="C251" s="11" t="s">
+        <v>139</v>
+      </c>
+      <c r="D251" s="9" t="s">
+        <v>140</v>
+      </c>
+      <c r="E251" s="12">
+        <v>819572</v>
+      </c>
+      <c r="F251" s="8"/>
+      <c r="G251" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="H251" s="9" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="252" spans="1:8" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A252" s="26" t="s">
-        <v>35</v>
-      </c>
-      <c r="B252" s="27"/>
-      <c r="C252" s="27"/>
-      <c r="D252" s="28"/>
-      <c r="E252" s="7"/>
-      <c r="F252" s="7"/>
-      <c r="G252" s="7"/>
-      <c r="H252" s="7"/>
-    </row>
-    <row r="253" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A253" s="26" t="s">
-        <v>36</v>
-      </c>
-      <c r="B253" s="27"/>
-      <c r="C253" s="27"/>
-      <c r="D253" s="28"/>
-      <c r="E253" s="13">
-        <v>178378131</v>
-      </c>
-      <c r="F253" s="7"/>
-      <c r="G253" s="7"/>
-      <c r="H253" s="7"/>
-    </row>
-    <row r="254" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A254" s="26" t="s">
-        <v>37</v>
-      </c>
-      <c r="B254" s="27"/>
-      <c r="C254" s="27"/>
-      <c r="D254" s="28"/>
-      <c r="E254" s="13">
-        <v>178378131</v>
-      </c>
-      <c r="F254" s="7"/>
-      <c r="G254" s="7"/>
-      <c r="H254" s="7"/>
-    </row>
-    <row r="255" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A255" s="15"/>
-    </row>
-    <row r="256" spans="1:8" ht="11.55" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A256" s="15"/>
-    </row>
-    <row r="257" spans="1:5" ht="11.55" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A257" s="15"/>
-    </row>
-    <row r="258" spans="1:5" ht="11.55" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A258" s="16" t="s">
+      <c r="A252" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="B252" s="10">
+        <v>46150</v>
+      </c>
+      <c r="C252" s="11" t="s">
+        <v>141</v>
+      </c>
+      <c r="D252" s="9" t="s">
+        <v>142</v>
+      </c>
+      <c r="E252" s="14">
+        <v>3</v>
+      </c>
+      <c r="F252" s="8"/>
+      <c r="G252" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="H252" s="9" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="253" spans="1:8" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A253" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="B253" s="10">
+        <v>46150</v>
+      </c>
+      <c r="C253" s="11" t="s">
+        <v>141</v>
+      </c>
+      <c r="D253" s="9" t="s">
+        <v>142</v>
+      </c>
+      <c r="E253" s="14">
+        <v>3</v>
+      </c>
+      <c r="F253" s="8"/>
+      <c r="G253" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="H253" s="9" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="254" spans="1:8" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A254" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="B254" s="10">
+        <v>46154</v>
+      </c>
+      <c r="C254" s="11" t="s">
+        <v>143</v>
+      </c>
+      <c r="D254" s="9" t="s">
+        <v>144</v>
+      </c>
+      <c r="E254" s="14">
+        <v>3</v>
+      </c>
+      <c r="F254" s="8"/>
+      <c r="G254" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="H254" s="9" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="255" spans="1:8" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A255" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="B255" s="10">
+        <v>46154</v>
+      </c>
+      <c r="C255" s="11" t="s">
+        <v>143</v>
+      </c>
+      <c r="D255" s="9" t="s">
+        <v>144</v>
+      </c>
+      <c r="E255" s="14">
+        <v>2</v>
+      </c>
+      <c r="F255" s="8"/>
+      <c r="G255" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="H255" s="9" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="256" spans="1:8" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A256" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="B256" s="10">
+        <v>46154</v>
+      </c>
+      <c r="C256" s="11" t="s">
+        <v>143</v>
+      </c>
+      <c r="D256" s="9" t="s">
+        <v>144</v>
+      </c>
+      <c r="E256" s="14">
+        <v>3</v>
+      </c>
+      <c r="F256" s="8"/>
+      <c r="G256" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="H256" s="9" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="257" spans="1:8" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A257" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="B257" s="10">
+        <v>46154</v>
+      </c>
+      <c r="C257" s="11" t="s">
+        <v>143</v>
+      </c>
+      <c r="D257" s="9" t="s">
+        <v>144</v>
+      </c>
+      <c r="E257" s="12">
+        <v>1481968</v>
+      </c>
+      <c r="F257" s="8"/>
+      <c r="G257" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="H257" s="9" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="258" spans="1:8" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A258" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="B258" s="10">
+        <v>46154</v>
+      </c>
+      <c r="C258" s="11" t="s">
+        <v>143</v>
+      </c>
+      <c r="D258" s="9" t="s">
+        <v>144</v>
+      </c>
+      <c r="E258" s="12">
+        <v>1415068</v>
+      </c>
+      <c r="F258" s="8"/>
+      <c r="G258" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="H258" s="9" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="259" spans="1:8" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A259" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="B259" s="10">
+        <v>46155</v>
+      </c>
+      <c r="C259" s="11" t="s">
+        <v>145</v>
+      </c>
+      <c r="D259" s="9" t="s">
+        <v>146</v>
+      </c>
+      <c r="E259" s="8"/>
+      <c r="F259" s="14">
+        <v>17</v>
+      </c>
+      <c r="G259" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="H259" s="9" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="260" spans="1:8" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A260" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="B260" s="10">
+        <v>46155</v>
+      </c>
+      <c r="C260" s="11" t="s">
+        <v>145</v>
+      </c>
+      <c r="D260" s="9" t="s">
+        <v>146</v>
+      </c>
+      <c r="E260" s="8"/>
+      <c r="F260" s="14">
+        <v>3</v>
+      </c>
+      <c r="G260" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="H260" s="9" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="261" spans="1:8" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A261" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="B261" s="10">
+        <v>46155</v>
+      </c>
+      <c r="C261" s="11" t="s">
+        <v>145</v>
+      </c>
+      <c r="D261" s="9" t="s">
+        <v>146</v>
+      </c>
+      <c r="E261" s="8"/>
+      <c r="F261" s="14">
+        <v>6</v>
+      </c>
+      <c r="G261" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="H261" s="9" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="262" spans="1:8" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A262" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="B262" s="10">
+        <v>46155</v>
+      </c>
+      <c r="C262" s="11" t="s">
+        <v>145</v>
+      </c>
+      <c r="D262" s="9" t="s">
+        <v>146</v>
+      </c>
+      <c r="E262" s="8"/>
+      <c r="F262" s="14">
+        <v>3</v>
+      </c>
+      <c r="G262" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="H262" s="9" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="263" spans="1:8" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A263" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="B263" s="10">
+        <v>46155</v>
+      </c>
+      <c r="C263" s="11" t="s">
+        <v>145</v>
+      </c>
+      <c r="D263" s="9" t="s">
+        <v>146</v>
+      </c>
+      <c r="E263" s="8"/>
+      <c r="F263" s="14">
+        <v>6</v>
+      </c>
+      <c r="G263" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="H263" s="9" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="264" spans="1:8" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A264" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="B264" s="10">
+        <v>46155</v>
+      </c>
+      <c r="C264" s="11" t="s">
+        <v>145</v>
+      </c>
+      <c r="D264" s="9" t="s">
+        <v>146</v>
+      </c>
+      <c r="E264" s="8"/>
+      <c r="F264" s="14">
+        <v>3</v>
+      </c>
+      <c r="G264" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="H264" s="9" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="265" spans="1:8" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A265" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="B265" s="10">
+        <v>46155</v>
+      </c>
+      <c r="C265" s="11" t="s">
+        <v>145</v>
+      </c>
+      <c r="D265" s="9" t="s">
+        <v>146</v>
+      </c>
+      <c r="E265" s="8"/>
+      <c r="F265" s="14">
+        <v>2</v>
+      </c>
+      <c r="G265" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="H265" s="9" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="266" spans="1:8" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A266" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="B266" s="10">
+        <v>46155</v>
+      </c>
+      <c r="C266" s="11" t="s">
+        <v>145</v>
+      </c>
+      <c r="D266" s="9" t="s">
+        <v>146</v>
+      </c>
+      <c r="E266" s="8"/>
+      <c r="F266" s="14">
+        <v>15</v>
+      </c>
+      <c r="G266" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="H266" s="9" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="267" spans="1:8" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A267" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="B267" s="10">
+        <v>46155</v>
+      </c>
+      <c r="C267" s="11" t="s">
+        <v>145</v>
+      </c>
+      <c r="D267" s="9" t="s">
+        <v>146</v>
+      </c>
+      <c r="E267" s="8"/>
+      <c r="F267" s="14">
+        <v>3</v>
+      </c>
+      <c r="G267" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="H267" s="9" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="268" spans="1:8" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A268" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="B268" s="10">
+        <v>46155</v>
+      </c>
+      <c r="C268" s="11" t="s">
+        <v>147</v>
+      </c>
+      <c r="D268" s="9" t="s">
+        <v>146</v>
+      </c>
+      <c r="E268" s="8"/>
+      <c r="F268" s="14">
+        <v>6</v>
+      </c>
+      <c r="G268" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="H268" s="9" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="269" spans="1:8" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A269" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="B269" s="10">
+        <v>46155</v>
+      </c>
+      <c r="C269" s="11" t="s">
+        <v>147</v>
+      </c>
+      <c r="D269" s="9" t="s">
+        <v>146</v>
+      </c>
+      <c r="E269" s="8"/>
+      <c r="F269" s="14">
+        <v>25</v>
+      </c>
+      <c r="G269" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="H269" s="9" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="270" spans="1:8" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A270" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="B270" s="10">
+        <v>46155</v>
+      </c>
+      <c r="C270" s="11" t="s">
+        <v>147</v>
+      </c>
+      <c r="D270" s="9" t="s">
+        <v>146</v>
+      </c>
+      <c r="E270" s="8"/>
+      <c r="F270" s="14">
+        <v>7</v>
+      </c>
+      <c r="G270" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="H270" s="9" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="271" spans="1:8" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A271" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="B271" s="10">
+        <v>46155</v>
+      </c>
+      <c r="C271" s="11" t="s">
+        <v>147</v>
+      </c>
+      <c r="D271" s="9" t="s">
+        <v>146</v>
+      </c>
+      <c r="E271" s="8"/>
+      <c r="F271" s="14">
+        <v>1</v>
+      </c>
+      <c r="G271" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="H271" s="9" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="272" spans="1:8" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A272" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="B272" s="10">
+        <v>46155</v>
+      </c>
+      <c r="C272" s="11" t="s">
+        <v>147</v>
+      </c>
+      <c r="D272" s="9" t="s">
+        <v>146</v>
+      </c>
+      <c r="E272" s="8"/>
+      <c r="F272" s="14">
+        <v>11</v>
+      </c>
+      <c r="G272" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="H272" s="9" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="273" spans="1:8" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A273" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="B273" s="10">
+        <v>46157</v>
+      </c>
+      <c r="C273" s="11" t="s">
+        <v>148</v>
+      </c>
+      <c r="D273" s="9" t="s">
+        <v>149</v>
+      </c>
+      <c r="E273" s="8"/>
+      <c r="F273" s="14">
+        <v>6</v>
+      </c>
+      <c r="G273" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="H273" s="9" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="274" spans="1:8" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A274" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="B274" s="10">
+        <v>46160</v>
+      </c>
+      <c r="C274" s="11" t="s">
+        <v>150</v>
+      </c>
+      <c r="D274" s="9" t="s">
+        <v>151</v>
+      </c>
+      <c r="E274" s="12">
+        <v>30180000</v>
+      </c>
+      <c r="F274" s="8"/>
+      <c r="G274" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="H274" s="9" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="275" spans="1:8" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A275" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="B275" s="10">
+        <v>46162</v>
+      </c>
+      <c r="C275" s="11" t="s">
+        <v>152</v>
+      </c>
+      <c r="D275" s="9" t="s">
+        <v>101</v>
+      </c>
+      <c r="E275" s="12">
+        <v>9525650</v>
+      </c>
+      <c r="F275" s="8"/>
+      <c r="G275" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="H275" s="9" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="276" spans="1:8" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A276" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="B276" s="10">
+        <v>46162</v>
+      </c>
+      <c r="C276" s="11" t="s">
+        <v>152</v>
+      </c>
+      <c r="D276" s="9" t="s">
+        <v>101</v>
+      </c>
+      <c r="E276" s="12">
+        <v>1698083</v>
+      </c>
+      <c r="F276" s="8"/>
+      <c r="G276" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="H276" s="9" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="277" spans="1:8" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A277" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="B277" s="10">
+        <v>46162</v>
+      </c>
+      <c r="C277" s="11" t="s">
+        <v>152</v>
+      </c>
+      <c r="D277" s="9" t="s">
+        <v>101</v>
+      </c>
+      <c r="E277" s="12">
+        <v>841347</v>
+      </c>
+      <c r="F277" s="8"/>
+      <c r="G277" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="H277" s="9" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="278" spans="1:8" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A278" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="B278" s="10">
+        <v>46162</v>
+      </c>
+      <c r="C278" s="11" t="s">
+        <v>152</v>
+      </c>
+      <c r="D278" s="9" t="s">
+        <v>101</v>
+      </c>
+      <c r="E278" s="12">
+        <v>5335086</v>
+      </c>
+      <c r="F278" s="8"/>
+      <c r="G278" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="H278" s="9" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="279" spans="1:8" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A279" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="B279" s="10">
+        <v>46162</v>
+      </c>
+      <c r="C279" s="11" t="s">
+        <v>152</v>
+      </c>
+      <c r="D279" s="9" t="s">
+        <v>101</v>
+      </c>
+      <c r="E279" s="12">
+        <v>11064619</v>
+      </c>
+      <c r="F279" s="8"/>
+      <c r="G279" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="H279" s="9" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="280" spans="1:8" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A280" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="B280" s="10">
+        <v>46164</v>
+      </c>
+      <c r="C280" s="11" t="s">
+        <v>153</v>
+      </c>
+      <c r="D280" s="9" t="s">
+        <v>154</v>
+      </c>
+      <c r="E280" s="14">
+        <v>6</v>
+      </c>
+      <c r="F280" s="8"/>
+      <c r="G280" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="H280" s="9" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="281" spans="1:8" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A281" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="B281" s="10">
+        <v>46169</v>
+      </c>
+      <c r="C281" s="11" t="s">
+        <v>155</v>
+      </c>
+      <c r="D281" s="9" t="s">
+        <v>156</v>
+      </c>
+      <c r="E281" s="12">
+        <v>24600000</v>
+      </c>
+      <c r="F281" s="8"/>
+      <c r="G281" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="H281" s="9" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="282" spans="1:8" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A282" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="B282" s="10">
+        <v>46169</v>
+      </c>
+      <c r="C282" s="11" t="s">
+        <v>155</v>
+      </c>
+      <c r="D282" s="9" t="s">
+        <v>156</v>
+      </c>
+      <c r="E282" s="12">
+        <v>52800000</v>
+      </c>
+      <c r="F282" s="8"/>
+      <c r="G282" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="H282" s="9" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="283" spans="1:8" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A283" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="B283" s="10">
+        <v>46169</v>
+      </c>
+      <c r="C283" s="11" t="s">
+        <v>155</v>
+      </c>
+      <c r="D283" s="9" t="s">
+        <v>156</v>
+      </c>
+      <c r="E283" s="12">
+        <v>368940000</v>
+      </c>
+      <c r="F283" s="8"/>
+      <c r="G283" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="H283" s="9" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="284" spans="1:8" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A284" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="B284" s="10">
+        <v>46169</v>
+      </c>
+      <c r="C284" s="11" t="s">
+        <v>155</v>
+      </c>
+      <c r="D284" s="9" t="s">
+        <v>156</v>
+      </c>
+      <c r="E284" s="12">
+        <v>25500000</v>
+      </c>
+      <c r="F284" s="8"/>
+      <c r="G284" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="H284" s="9" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="285" spans="1:8" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A285" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="B285" s="10">
+        <v>46169</v>
+      </c>
+      <c r="C285" s="11" t="s">
+        <v>155</v>
+      </c>
+      <c r="D285" s="9" t="s">
+        <v>156</v>
+      </c>
+      <c r="E285" s="12">
+        <v>22800000</v>
+      </c>
+      <c r="F285" s="8"/>
+      <c r="G285" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="H285" s="9" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="286" spans="1:8" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A286" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="B286" s="10">
+        <v>46169</v>
+      </c>
+      <c r="C286" s="11" t="s">
+        <v>155</v>
+      </c>
+      <c r="D286" s="9" t="s">
+        <v>156</v>
+      </c>
+      <c r="E286" s="12">
+        <v>24000000</v>
+      </c>
+      <c r="F286" s="8"/>
+      <c r="G286" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="H286" s="9" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="287" spans="1:8" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A287" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="B287" s="10">
+        <v>46169</v>
+      </c>
+      <c r="C287" s="11" t="s">
+        <v>155</v>
+      </c>
+      <c r="D287" s="9" t="s">
+        <v>156</v>
+      </c>
+      <c r="E287" s="12">
+        <v>22500000</v>
+      </c>
+      <c r="F287" s="8"/>
+      <c r="G287" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="H287" s="9" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="288" spans="1:8" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A288" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="B288" s="10">
+        <v>46169</v>
+      </c>
+      <c r="C288" s="11" t="s">
+        <v>155</v>
+      </c>
+      <c r="D288" s="9" t="s">
+        <v>156</v>
+      </c>
+      <c r="E288" s="12">
+        <v>26400000</v>
+      </c>
+      <c r="F288" s="8"/>
+      <c r="G288" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="H288" s="9" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="289" spans="1:8" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A289" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="B289" s="10">
+        <v>46169</v>
+      </c>
+      <c r="C289" s="11" t="s">
+        <v>155</v>
+      </c>
+      <c r="D289" s="9" t="s">
+        <v>156</v>
+      </c>
+      <c r="E289" s="12">
+        <v>22500000</v>
+      </c>
+      <c r="F289" s="8"/>
+      <c r="G289" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="H289" s="9" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="290" spans="1:8" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A290" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="B290" s="10">
+        <v>46169</v>
+      </c>
+      <c r="C290" s="11" t="s">
+        <v>155</v>
+      </c>
+      <c r="D290" s="9" t="s">
+        <v>156</v>
+      </c>
+      <c r="E290" s="12">
+        <v>24903814</v>
+      </c>
+      <c r="F290" s="8"/>
+      <c r="G290" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="H290" s="9" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="291" spans="1:8" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A291" s="24" t="s">
+        <v>38</v>
+      </c>
+      <c r="B291" s="25"/>
+      <c r="C291" s="25"/>
+      <c r="D291" s="26"/>
+      <c r="E291" s="13">
+        <v>2158654523</v>
+      </c>
+      <c r="F291" s="13">
+        <v>29678896</v>
+      </c>
+      <c r="G291" s="7"/>
+      <c r="H291" s="7"/>
+    </row>
+    <row r="292" spans="1:8" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A292" s="24" t="s">
+        <v>39</v>
+      </c>
+      <c r="B292" s="25"/>
+      <c r="C292" s="25"/>
+      <c r="D292" s="26"/>
+      <c r="E292" s="13">
+        <v>2128975627</v>
+      </c>
+      <c r="F292" s="7"/>
+      <c r="G292" s="7"/>
+      <c r="H292" s="7"/>
+    </row>
+    <row r="293" spans="1:8" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A293" s="24" t="s">
+        <v>40</v>
+      </c>
+      <c r="B293" s="25"/>
+      <c r="C293" s="25"/>
+      <c r="D293" s="26"/>
+      <c r="E293" s="7"/>
+      <c r="F293" s="7"/>
+      <c r="G293" s="7"/>
+      <c r="H293" s="7"/>
+    </row>
+    <row r="294" spans="1:8" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A294" s="24" t="s">
+        <v>41</v>
+      </c>
+      <c r="B294" s="25"/>
+      <c r="C294" s="25"/>
+      <c r="D294" s="26"/>
+      <c r="E294" s="13">
+        <v>2158654523</v>
+      </c>
+      <c r="F294" s="13">
+        <v>29678896</v>
+      </c>
+      <c r="G294" s="7"/>
+      <c r="H294" s="7"/>
+    </row>
+    <row r="295" spans="1:8" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A295" s="24" t="s">
+        <v>42</v>
+      </c>
+      <c r="B295" s="25"/>
+      <c r="C295" s="25"/>
+      <c r="D295" s="26"/>
+      <c r="E295" s="13">
+        <v>2128975627</v>
+      </c>
+      <c r="F295" s="7"/>
+      <c r="G295" s="7"/>
+      <c r="H295" s="7"/>
+    </row>
+    <row r="296" spans="1:8" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A296" s="24" t="s">
+        <v>43</v>
+      </c>
+      <c r="B296" s="25"/>
+      <c r="C296" s="25"/>
+      <c r="D296" s="26"/>
+      <c r="E296" s="7"/>
+      <c r="F296" s="7"/>
+      <c r="G296" s="7"/>
+      <c r="H296" s="7"/>
+    </row>
+    <row r="297" spans="1:8" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A297" s="24" t="s">
+        <v>44</v>
+      </c>
+      <c r="B297" s="25"/>
+      <c r="C297" s="25"/>
+      <c r="D297" s="26"/>
+      <c r="E297" s="13">
+        <v>2158654523</v>
+      </c>
+      <c r="F297" s="13">
+        <v>29678896</v>
+      </c>
+      <c r="G297" s="7"/>
+      <c r="H297" s="7"/>
+    </row>
+    <row r="298" spans="1:8" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A298" s="24" t="s">
+        <v>45</v>
+      </c>
+      <c r="B298" s="25"/>
+      <c r="C298" s="25"/>
+      <c r="D298" s="26"/>
+      <c r="E298" s="13">
+        <v>2128975627</v>
+      </c>
+      <c r="F298" s="7"/>
+      <c r="G298" s="7"/>
+      <c r="H298" s="7"/>
+    </row>
+    <row r="299" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A299" s="21" t="s">
+        <v>157</v>
+      </c>
+      <c r="B299" s="22"/>
+      <c r="C299" s="22"/>
+      <c r="D299" s="22"/>
+      <c r="E299" s="22"/>
+      <c r="F299" s="22"/>
+      <c r="G299" s="22"/>
+      <c r="H299" s="23"/>
+    </row>
+    <row r="300" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A300" s="21" t="s">
+        <v>158</v>
+      </c>
+      <c r="B300" s="22"/>
+      <c r="C300" s="22"/>
+      <c r="D300" s="22"/>
+      <c r="E300" s="22"/>
+      <c r="F300" s="22"/>
+      <c r="G300" s="22"/>
+      <c r="H300" s="23"/>
+    </row>
+    <row r="301" spans="1:8" ht="18.149999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A301" s="21" t="s">
+        <v>48</v>
+      </c>
+      <c r="B301" s="22"/>
+      <c r="C301" s="22"/>
+      <c r="D301" s="22"/>
+      <c r="E301" s="22"/>
+      <c r="F301" s="22"/>
+      <c r="G301" s="22"/>
+      <c r="H301" s="23"/>
+    </row>
+    <row r="302" spans="1:8" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A302" s="24" t="s">
         <v>22</v>
       </c>
-      <c r="B258" s="7"/>
-      <c r="C258" s="7"/>
-      <c r="D258" s="7"/>
-      <c r="E258" s="7"/>
-    </row>
-    <row r="259" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A259" s="16" t="s">
-        <v>30</v>
-      </c>
-      <c r="B259" s="13">
-        <v>1756914319</v>
-      </c>
-      <c r="C259" s="13">
-        <v>29678782</v>
-      </c>
-      <c r="D259" s="7"/>
-      <c r="E259" s="7"/>
-    </row>
-    <row r="260" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A260" s="16" t="s">
-        <v>31</v>
-      </c>
-      <c r="B260" s="13">
-        <v>1727235537</v>
-      </c>
-      <c r="C260" s="7"/>
-      <c r="D260" s="7"/>
-      <c r="E260" s="7"/>
-    </row>
-    <row r="261" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="262" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="263" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A263" s="29"/>
-      <c r="B263" s="29"/>
-      <c r="C263" s="17" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="264" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A264" s="4" t="s">
-        <v>138</v>
-      </c>
-      <c r="B264" s="1"/>
-      <c r="C264" s="4" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="265" spans="1:5" ht="12.15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A265" s="18" t="s">
-        <v>140</v>
-      </c>
-      <c r="B265" s="6"/>
-      <c r="C265" s="18" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="267" spans="1:5" ht="20.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A267" s="19" t="s">
-        <v>142</v>
-      </c>
-      <c r="B267" s="20" t="s">
-        <v>143</v>
+      <c r="B302" s="25"/>
+      <c r="C302" s="25"/>
+      <c r="D302" s="26"/>
+      <c r="E302" s="7"/>
+      <c r="F302" s="7"/>
+      <c r="G302" s="7"/>
+      <c r="H302" s="7"/>
+    </row>
+    <row r="303" spans="1:8" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A303" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="B303" s="10">
+        <v>46136</v>
+      </c>
+      <c r="C303" s="11" t="s">
+        <v>159</v>
+      </c>
+      <c r="D303" s="9" t="s">
+        <v>160</v>
+      </c>
+      <c r="E303" s="12">
+        <v>1557808</v>
+      </c>
+      <c r="F303" s="8"/>
+      <c r="G303" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="H303" s="9" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="304" spans="1:8" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A304" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="B304" s="10">
+        <v>46136</v>
+      </c>
+      <c r="C304" s="11" t="s">
+        <v>159</v>
+      </c>
+      <c r="D304" s="9" t="s">
+        <v>160</v>
+      </c>
+      <c r="E304" s="12">
+        <v>617400</v>
+      </c>
+      <c r="F304" s="8"/>
+      <c r="G304" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="H304" s="9" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="305" spans="1:8" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A305" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="B305" s="10">
+        <v>46136</v>
+      </c>
+      <c r="C305" s="11" t="s">
+        <v>159</v>
+      </c>
+      <c r="D305" s="9" t="s">
+        <v>160</v>
+      </c>
+      <c r="E305" s="12">
+        <v>23503565</v>
+      </c>
+      <c r="F305" s="8"/>
+      <c r="G305" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="H305" s="9" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="306" spans="1:8" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A306" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="B306" s="10">
+        <v>46136</v>
+      </c>
+      <c r="C306" s="11" t="s">
+        <v>159</v>
+      </c>
+      <c r="D306" s="9" t="s">
+        <v>160</v>
+      </c>
+      <c r="E306" s="12">
+        <v>3307500</v>
+      </c>
+      <c r="F306" s="8"/>
+      <c r="G306" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="H306" s="9" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="307" spans="1:8" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A307" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="B307" s="10">
+        <v>46136</v>
+      </c>
+      <c r="C307" s="11" t="s">
+        <v>159</v>
+      </c>
+      <c r="D307" s="9" t="s">
+        <v>160</v>
+      </c>
+      <c r="E307" s="12">
+        <v>800232</v>
+      </c>
+      <c r="F307" s="8"/>
+      <c r="G307" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="H307" s="9" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="308" spans="1:8" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A308" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="B308" s="10">
+        <v>46136</v>
+      </c>
+      <c r="C308" s="11" t="s">
+        <v>159</v>
+      </c>
+      <c r="D308" s="9" t="s">
+        <v>160</v>
+      </c>
+      <c r="E308" s="12">
+        <v>138000</v>
+      </c>
+      <c r="F308" s="8"/>
+      <c r="G308" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="H308" s="9" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="309" spans="1:8" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A309" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="B309" s="10">
+        <v>46136</v>
+      </c>
+      <c r="C309" s="11" t="s">
+        <v>159</v>
+      </c>
+      <c r="D309" s="9" t="s">
+        <v>160</v>
+      </c>
+      <c r="E309" s="12">
+        <v>28173630</v>
+      </c>
+      <c r="F309" s="8"/>
+      <c r="G309" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="H309" s="9" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="310" spans="1:8" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A310" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="B310" s="10">
+        <v>46136</v>
+      </c>
+      <c r="C310" s="11" t="s">
+        <v>159</v>
+      </c>
+      <c r="D310" s="9" t="s">
+        <v>160</v>
+      </c>
+      <c r="E310" s="12">
+        <v>4445278</v>
+      </c>
+      <c r="F310" s="8"/>
+      <c r="G310" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="H310" s="9" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="311" spans="1:8" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A311" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="B311" s="10">
+        <v>46136</v>
+      </c>
+      <c r="C311" s="11" t="s">
+        <v>159</v>
+      </c>
+      <c r="D311" s="9" t="s">
+        <v>160</v>
+      </c>
+      <c r="E311" s="12">
+        <v>18021675</v>
+      </c>
+      <c r="F311" s="8"/>
+      <c r="G311" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="H311" s="9" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="312" spans="1:8" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A312" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="B312" s="10">
+        <v>46141</v>
+      </c>
+      <c r="C312" s="11" t="s">
+        <v>161</v>
+      </c>
+      <c r="D312" s="9" t="s">
+        <v>162</v>
+      </c>
+      <c r="E312" s="12">
+        <v>3780000</v>
+      </c>
+      <c r="F312" s="8"/>
+      <c r="G312" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="H312" s="9" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="313" spans="1:8" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A313" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="B313" s="10">
+        <v>46141</v>
+      </c>
+      <c r="C313" s="11" t="s">
+        <v>161</v>
+      </c>
+      <c r="D313" s="9" t="s">
+        <v>162</v>
+      </c>
+      <c r="E313" s="12">
+        <v>527987</v>
+      </c>
+      <c r="F313" s="8"/>
+      <c r="G313" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="H313" s="9" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="314" spans="1:8" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A314" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="B314" s="10">
+        <v>46141</v>
+      </c>
+      <c r="C314" s="11" t="s">
+        <v>161</v>
+      </c>
+      <c r="D314" s="9" t="s">
+        <v>162</v>
+      </c>
+      <c r="E314" s="12">
+        <v>20596200</v>
+      </c>
+      <c r="F314" s="8"/>
+      <c r="G314" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="H314" s="9" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="315" spans="1:8" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A315" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="B315" s="10">
+        <v>46141</v>
+      </c>
+      <c r="C315" s="11" t="s">
+        <v>161</v>
+      </c>
+      <c r="D315" s="9" t="s">
+        <v>162</v>
+      </c>
+      <c r="E315" s="12">
+        <v>5080318</v>
+      </c>
+      <c r="F315" s="8"/>
+      <c r="G315" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="H315" s="9" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="316" spans="1:8" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A316" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="B316" s="10">
+        <v>46141</v>
+      </c>
+      <c r="C316" s="11" t="s">
+        <v>161</v>
+      </c>
+      <c r="D316" s="9" t="s">
+        <v>162</v>
+      </c>
+      <c r="E316" s="12">
+        <v>32198434</v>
+      </c>
+      <c r="F316" s="8"/>
+      <c r="G316" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="H316" s="9" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="317" spans="1:8" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A317" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="B317" s="10">
+        <v>46141</v>
+      </c>
+      <c r="C317" s="11" t="s">
+        <v>161</v>
+      </c>
+      <c r="D317" s="9" t="s">
+        <v>162</v>
+      </c>
+      <c r="E317" s="12">
+        <v>1780352</v>
+      </c>
+      <c r="F317" s="8"/>
+      <c r="G317" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="H317" s="9" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="318" spans="1:8" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A318" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="B318" s="10">
+        <v>46141</v>
+      </c>
+      <c r="C318" s="11" t="s">
+        <v>161</v>
+      </c>
+      <c r="D318" s="9" t="s">
+        <v>162</v>
+      </c>
+      <c r="E318" s="12">
+        <v>800232</v>
+      </c>
+      <c r="F318" s="8"/>
+      <c r="G318" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="H318" s="9" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="319" spans="1:8" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A319" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="B319" s="10">
+        <v>46141</v>
+      </c>
+      <c r="C319" s="11" t="s">
+        <v>161</v>
+      </c>
+      <c r="D319" s="9" t="s">
+        <v>162</v>
+      </c>
+      <c r="E319" s="12">
+        <v>705600</v>
+      </c>
+      <c r="F319" s="8"/>
+      <c r="G319" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="H319" s="9" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="320" spans="1:8" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A320" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="B320" s="10">
+        <v>46141</v>
+      </c>
+      <c r="C320" s="11" t="s">
+        <v>161</v>
+      </c>
+      <c r="D320" s="9" t="s">
+        <v>162</v>
+      </c>
+      <c r="E320" s="12">
+        <v>26446116</v>
+      </c>
+      <c r="F320" s="8"/>
+      <c r="G320" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="H320" s="9" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="321" spans="1:8" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A321" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="B321" s="10">
+        <v>46148</v>
+      </c>
+      <c r="C321" s="11" t="s">
+        <v>163</v>
+      </c>
+      <c r="D321" s="9" t="s">
+        <v>164</v>
+      </c>
+      <c r="E321" s="12">
+        <v>15447150</v>
+      </c>
+      <c r="F321" s="8"/>
+      <c r="G321" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="H321" s="9" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="322" spans="1:8" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A322" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="B322" s="10">
+        <v>46148</v>
+      </c>
+      <c r="C322" s="11" t="s">
+        <v>163</v>
+      </c>
+      <c r="D322" s="9" t="s">
+        <v>164</v>
+      </c>
+      <c r="E322" s="12">
+        <v>19834587</v>
+      </c>
+      <c r="F322" s="8"/>
+      <c r="G322" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="H322" s="9" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="323" spans="1:8" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A323" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="B323" s="10">
+        <v>46148</v>
+      </c>
+      <c r="C323" s="11" t="s">
+        <v>163</v>
+      </c>
+      <c r="D323" s="9" t="s">
+        <v>164</v>
+      </c>
+      <c r="E323" s="12">
+        <v>1335264</v>
+      </c>
+      <c r="F323" s="8"/>
+      <c r="G323" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="H323" s="9" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="324" spans="1:8" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A324" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="B324" s="10">
+        <v>46148</v>
+      </c>
+      <c r="C324" s="11" t="s">
+        <v>163</v>
+      </c>
+      <c r="D324" s="9" t="s">
+        <v>164</v>
+      </c>
+      <c r="E324" s="12">
+        <v>24148825</v>
+      </c>
+      <c r="F324" s="8"/>
+      <c r="G324" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="H324" s="9" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="325" spans="1:8" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A325" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="B325" s="10">
+        <v>46148</v>
+      </c>
+      <c r="C325" s="11" t="s">
+        <v>163</v>
+      </c>
+      <c r="D325" s="9" t="s">
+        <v>164</v>
+      </c>
+      <c r="E325" s="12">
+        <v>800232</v>
+      </c>
+      <c r="F325" s="8"/>
+      <c r="G325" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="H325" s="9" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="326" spans="1:8" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A326" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="B326" s="10">
+        <v>46148</v>
+      </c>
+      <c r="C326" s="11" t="s">
+        <v>163</v>
+      </c>
+      <c r="D326" s="9" t="s">
+        <v>164</v>
+      </c>
+      <c r="E326" s="12">
+        <v>529200</v>
+      </c>
+      <c r="F326" s="8"/>
+      <c r="G326" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="H326" s="9" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="327" spans="1:8" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A327" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="B327" s="10">
+        <v>46148</v>
+      </c>
+      <c r="C327" s="11" t="s">
+        <v>163</v>
+      </c>
+      <c r="D327" s="9" t="s">
+        <v>164</v>
+      </c>
+      <c r="E327" s="12">
+        <v>2835000</v>
+      </c>
+      <c r="F327" s="8"/>
+      <c r="G327" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="H327" s="9" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="328" spans="1:8" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A328" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="B328" s="10">
+        <v>46167</v>
+      </c>
+      <c r="C328" s="11" t="s">
+        <v>165</v>
+      </c>
+      <c r="D328" s="9" t="s">
+        <v>166</v>
+      </c>
+      <c r="E328" s="8"/>
+      <c r="F328" s="12">
+        <v>138000</v>
+      </c>
+      <c r="G328" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="H328" s="9" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="329" spans="1:8" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A329" s="24" t="s">
+        <v>38</v>
+      </c>
+      <c r="B329" s="25"/>
+      <c r="C329" s="25"/>
+      <c r="D329" s="26"/>
+      <c r="E329" s="13">
+        <v>237410585</v>
+      </c>
+      <c r="F329" s="13">
+        <v>138000</v>
+      </c>
+      <c r="G329" s="7"/>
+      <c r="H329" s="7"/>
+    </row>
+    <row r="330" spans="1:8" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A330" s="24" t="s">
+        <v>39</v>
+      </c>
+      <c r="B330" s="25"/>
+      <c r="C330" s="25"/>
+      <c r="D330" s="26"/>
+      <c r="E330" s="13">
+        <v>237272585</v>
+      </c>
+      <c r="F330" s="7"/>
+      <c r="G330" s="7"/>
+      <c r="H330" s="7"/>
+    </row>
+    <row r="331" spans="1:8" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A331" s="24" t="s">
+        <v>40</v>
+      </c>
+      <c r="B331" s="25"/>
+      <c r="C331" s="25"/>
+      <c r="D331" s="26"/>
+      <c r="E331" s="7"/>
+      <c r="F331" s="7"/>
+      <c r="G331" s="7"/>
+      <c r="H331" s="7"/>
+    </row>
+    <row r="332" spans="1:8" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A332" s="24" t="s">
+        <v>41</v>
+      </c>
+      <c r="B332" s="25"/>
+      <c r="C332" s="25"/>
+      <c r="D332" s="26"/>
+      <c r="E332" s="13">
+        <v>237410585</v>
+      </c>
+      <c r="F332" s="13">
+        <v>138000</v>
+      </c>
+      <c r="G332" s="7"/>
+      <c r="H332" s="7"/>
+    </row>
+    <row r="333" spans="1:8" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A333" s="24" t="s">
+        <v>42</v>
+      </c>
+      <c r="B333" s="25"/>
+      <c r="C333" s="25"/>
+      <c r="D333" s="26"/>
+      <c r="E333" s="13">
+        <v>237272585</v>
+      </c>
+      <c r="F333" s="7"/>
+      <c r="G333" s="7"/>
+      <c r="H333" s="7"/>
+    </row>
+    <row r="334" spans="1:8" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A334" s="24" t="s">
+        <v>43</v>
+      </c>
+      <c r="B334" s="25"/>
+      <c r="C334" s="25"/>
+      <c r="D334" s="26"/>
+      <c r="E334" s="7"/>
+      <c r="F334" s="7"/>
+      <c r="G334" s="7"/>
+      <c r="H334" s="7"/>
+    </row>
+    <row r="335" spans="1:8" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A335" s="24" t="s">
+        <v>44</v>
+      </c>
+      <c r="B335" s="25"/>
+      <c r="C335" s="25"/>
+      <c r="D335" s="26"/>
+      <c r="E335" s="13">
+        <v>237410585</v>
+      </c>
+      <c r="F335" s="13">
+        <v>138000</v>
+      </c>
+      <c r="G335" s="7"/>
+      <c r="H335" s="7"/>
+    </row>
+    <row r="336" spans="1:8" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A336" s="24" t="s">
+        <v>45</v>
+      </c>
+      <c r="B336" s="25"/>
+      <c r="C336" s="25"/>
+      <c r="D336" s="26"/>
+      <c r="E336" s="13">
+        <v>237272585</v>
+      </c>
+      <c r="F336" s="7"/>
+      <c r="G336" s="7"/>
+      <c r="H336" s="7"/>
+    </row>
+    <row r="337" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A337" s="27"/>
+    </row>
+    <row r="338" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A338" s="27"/>
+    </row>
+    <row r="339" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A339" s="27"/>
+    </row>
+    <row r="340" spans="1:5" ht="11.55" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A340" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="B340" s="7"/>
+      <c r="C340" s="7"/>
+      <c r="D340" s="7"/>
+      <c r="E340" s="7"/>
+    </row>
+    <row r="341" spans="1:5" ht="11.55" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A341" s="28" t="s">
+        <v>38</v>
+      </c>
+      <c r="B341" s="13">
+        <v>2794715538</v>
+      </c>
+      <c r="C341" s="13">
+        <v>29816896</v>
+      </c>
+      <c r="D341" s="7"/>
+      <c r="E341" s="7"/>
+    </row>
+    <row r="342" spans="1:5" ht="11.55" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A342" s="28" t="s">
+        <v>39</v>
+      </c>
+      <c r="B342" s="13">
+        <v>2764898642</v>
+      </c>
+      <c r="C342" s="7"/>
+      <c r="D342" s="7"/>
+      <c r="E342" s="7"/>
+    </row>
+    <row r="345" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A345" s="31"/>
+      <c r="B345" s="31"/>
+      <c r="C345" s="29" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="346" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A346" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="B346" s="1"/>
+      <c r="C346" s="4" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="347" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A347" s="30" t="s">
+        <v>170</v>
+      </c>
+      <c r="B347" s="6"/>
+      <c r="C347" s="30" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="349" spans="1:5" ht="12.15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A349" s="32" t="s">
+        <v>172</v>
+      </c>
+      <c r="B349" s="33" t="s">
+        <v>173</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="51">
-    <mergeCell ref="A43:D43"/>
-    <mergeCell ref="A44:D44"/>
-    <mergeCell ref="A45:D45"/>
-    <mergeCell ref="A52:H52"/>
-    <mergeCell ref="A53:D53"/>
-    <mergeCell ref="A209:D209"/>
-    <mergeCell ref="A48:D48"/>
+  <mergeCells count="45">
+    <mergeCell ref="A336:D336"/>
+    <mergeCell ref="A345:B345"/>
+    <mergeCell ref="A12:H12"/>
+    <mergeCell ref="A330:D330"/>
+    <mergeCell ref="A331:D331"/>
+    <mergeCell ref="A332:D332"/>
+    <mergeCell ref="A333:D333"/>
+    <mergeCell ref="A334:D334"/>
+    <mergeCell ref="A335:D335"/>
+    <mergeCell ref="A298:D298"/>
+    <mergeCell ref="A299:H299"/>
+    <mergeCell ref="A300:H300"/>
+    <mergeCell ref="A301:H301"/>
+    <mergeCell ref="A302:D302"/>
+    <mergeCell ref="A329:D329"/>
+    <mergeCell ref="A292:D292"/>
+    <mergeCell ref="A293:D293"/>
+    <mergeCell ref="A294:D294"/>
+    <mergeCell ref="A295:D295"/>
+    <mergeCell ref="A296:D296"/>
+    <mergeCell ref="A297:D297"/>
+    <mergeCell ref="A84:D84"/>
+    <mergeCell ref="A85:H85"/>
+    <mergeCell ref="A86:H86"/>
+    <mergeCell ref="A87:H87"/>
+    <mergeCell ref="A88:D88"/>
+    <mergeCell ref="A291:D291"/>
+    <mergeCell ref="A78:D78"/>
+    <mergeCell ref="A79:D79"/>
+    <mergeCell ref="A80:D80"/>
+    <mergeCell ref="A81:D81"/>
+    <mergeCell ref="A82:D82"/>
+    <mergeCell ref="A83:D83"/>
     <mergeCell ref="H13:H14"/>
     <mergeCell ref="A15:H15"/>
     <mergeCell ref="A16:H16"/>
     <mergeCell ref="A17:H17"/>
     <mergeCell ref="A18:D18"/>
-    <mergeCell ref="A42:D42"/>
+    <mergeCell ref="A77:D77"/>
     <mergeCell ref="A13:A14"/>
     <mergeCell ref="B13:B14"/>
     <mergeCell ref="C13:C14"/>
     <mergeCell ref="D13:D14"/>
     <mergeCell ref="E13:F13"/>
     <mergeCell ref="G13:G14"/>
-    <mergeCell ref="A254:D254"/>
-    <mergeCell ref="A263:B263"/>
-    <mergeCell ref="A240:D240"/>
-    <mergeCell ref="A243:H243"/>
-    <mergeCell ref="A244:D244"/>
-    <mergeCell ref="A247:D247"/>
-    <mergeCell ref="A248:D248"/>
-    <mergeCell ref="A249:D249"/>
-    <mergeCell ref="A241:H241"/>
-    <mergeCell ref="A253:D253"/>
-    <mergeCell ref="A216:D216"/>
-    <mergeCell ref="A217:H217"/>
-    <mergeCell ref="A218:H218"/>
-    <mergeCell ref="A219:H219"/>
-    <mergeCell ref="A220:D220"/>
-    <mergeCell ref="A239:D239"/>
-    <mergeCell ref="A242:H242"/>
-    <mergeCell ref="A12:H12"/>
-    <mergeCell ref="A250:D250"/>
-    <mergeCell ref="A251:D251"/>
-    <mergeCell ref="A252:D252"/>
-    <mergeCell ref="A210:D210"/>
-    <mergeCell ref="A211:D211"/>
-    <mergeCell ref="A212:D212"/>
-    <mergeCell ref="A213:D213"/>
-    <mergeCell ref="A214:D214"/>
-    <mergeCell ref="A46:D46"/>
-    <mergeCell ref="A47:D47"/>
-    <mergeCell ref="A215:D215"/>
-    <mergeCell ref="A49:D49"/>
-    <mergeCell ref="A50:H50"/>
-    <mergeCell ref="A51:H51"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
